--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -827,6 +827,4070 @@
       <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Indian Super League</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Jamshedpur FC</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Indian Super League</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Punjab FC</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Mumbai City FC</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I3" t="n">
+        <v>870</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Indian Super League</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Inter Kashi</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Quess East Bengal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>600</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Indian Super League</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mohun Bagan Super Giants</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sporting Club Delhi</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>870</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>500</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Swedish Allsvenskan</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Elfsborg</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Mjallby</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Al-Hazm (KSA)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Al-Taawoun Buraidah</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Al Riyadh SC</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Al-Akhdoud</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NEOM Sports Club</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Al-Ettifaq</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Al-Feiha</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Al-Hilal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>13</v>
+      </c>
+      <c r="G10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="J10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Dhamk</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>32</v>
+      </c>
+      <c r="J11" t="n">
+        <v>12</v>
+      </c>
+      <c r="K11" t="n">
+        <v>17</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Al-Kholood Club</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Al-Fateh (KSA)</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Al-Ittihad</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Al-Quadisiya (KSA)</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Belgian Pro League</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Yellow-Red Mechelen</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>200</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Belgian Pro League</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Gent</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Union St Gilloise</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Belgian Pro League</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Anderlecht</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sint Truiden</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:12:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Deportivo La Guaira</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>160</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>16</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-05-19 02:12:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="G2" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="H2" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K2" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="G3" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="H3" t="n">
-        <v>2.82</v>
+        <v>1.36</v>
       </c>
       <c r="I3" t="n">
         <v>870</v>
@@ -1126,7 +1126,7 @@
         <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>500</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>600</v>
+        <v>12.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="I4" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="J4" t="n">
         <v>4.2</v>
       </c>
       <c r="K4" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="H5" t="n">
-        <v>10.5</v>
+        <v>1.15</v>
       </c>
       <c r="I5" t="n">
-        <v>870</v>
+        <v>21</v>
       </c>
       <c r="J5" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="K5" t="n">
-        <v>500</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.18</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q6" t="n">
         <v>2.2</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="G7" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="H7" t="n">
         <v>1.8</v>
       </c>
       <c r="I7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K7" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         <v>7.6</v>
       </c>
       <c r="I8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="J8" t="n">
         <v>4.9</v>
@@ -2414,7 +2414,7 @@
         <v>2.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="Q10" t="n">
         <v>1.44</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -3146,10 +3146,10 @@
         <v>1.13</v>
       </c>
       <c r="G11" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="H11" t="n">
-        <v>10.5</v>
+        <v>1.09</v>
       </c>
       <c r="I11" t="n">
         <v>32</v>
@@ -3158,7 +3158,7 @@
         <v>12</v>
       </c>
       <c r="K11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
         <v>2.72</v>
       </c>
       <c r="H12" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I12" t="n">
         <v>2.96</v>
@@ -3412,7 +3412,7 @@
         <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3430,7 +3430,7 @@
         <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="G13" t="n">
         <v>2.72</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
         <v>200</v>
       </c>
       <c r="AK14" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AL14" t="n">
         <v>70</v>
@@ -4007,7 +4007,7 @@
         <v>85</v>
       </c>
       <c r="AN14" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO14" t="n">
         <v>4.5</v>
@@ -4040,7 +4040,7 @@
         <v>7.4</v>
       </c>
       <c r="AY14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AZ14" t="n">
         <v>16</v>
@@ -4049,16 +4049,16 @@
         <v>18.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC14" t="n">
         <v>7.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF14" t="n">
         <v>7.4</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="G15" t="n">
         <v>5.4</v>
@@ -4168,13 +4168,13 @@
         <v>1.77</v>
       </c>
       <c r="I15" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="J15" t="n">
         <v>3.7</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4201,10 +4201,10 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -4246,7 +4246,7 @@
         <v>25</v>
       </c>
       <c r="AI15" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AJ15" t="n">
         <v>150</v>
@@ -4255,7 +4255,7 @@
         <v>80</v>
       </c>
       <c r="AL15" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AM15" t="n">
         <v>140</v>
@@ -4270,7 +4270,7 @@
         <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AR15" t="n">
         <v>8.199999999999999</v>
@@ -4291,7 +4291,7 @@
         <v>14.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AY15" t="n">
         <v>14</v>
@@ -4315,7 +4315,7 @@
         <v>4.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BG15" t="n">
         <v>9.4</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>
@@ -4673,16 +4673,16 @@
         <v>5.4</v>
       </c>
       <c r="H17" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J17" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K17" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4697,7 +4697,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q17" t="n">
         <v>2.46</v>
@@ -4709,7 +4709,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U17" t="n">
         <v>1.75</v>
@@ -4721,7 +4721,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="Y17" t="n">
         <v>7.8</v>
@@ -4772,7 +4772,7 @@
         <v>160</v>
       </c>
       <c r="AO17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP17" t="n">
         <v>8.4</v>
@@ -4793,37 +4793,37 @@
         <v>6.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW17" t="n">
         <v>18.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AY17" t="n">
         <v>16.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BG17" t="n">
         <v>16</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-19 02:12:42</t>
+          <t>2026-05-19 04:24:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>870</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
         <v>500</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -1374,10 +1374,10 @@
         <v>1.38</v>
       </c>
       <c r="I4" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="K4" t="n">
         <v>6.2</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="G5" t="n">
         <v>1.27</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         <v>1.74</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -2130,19 +2130,19 @@
         <v>4.2</v>
       </c>
       <c r="G7" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="I7" t="n">
         <v>1.91</v>
       </c>
       <c r="J7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>10.5</v>
       </c>
       <c r="J8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
         <v>6.2</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7</v>
+        <v>2.94</v>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K9" t="n">
         <v>5.3</v>
@@ -2665,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="Q9" t="n">
         <v>1.45</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         <v>12</v>
       </c>
       <c r="K11" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G12" t="n">
         <v>2.72</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="G13" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="H13" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="I13" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="J13" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K13" t="n">
         <v>4.4</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="Q13" t="n">
         <v>1.54</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -3962,19 +3962,19 @@
         <v>42</v>
       </c>
       <c r="Y14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z14" t="n">
         <v>12.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AB14" t="n">
         <v>44</v>
       </c>
       <c r="AC14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AD14" t="n">
         <v>12.5</v>
@@ -3989,7 +3989,7 @@
         <v>32</v>
       </c>
       <c r="AH14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
         <v>25</v>
@@ -4013,7 +4013,7 @@
         <v>4.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ14" t="n">
         <v>12</v>
@@ -4025,7 +4025,7 @@
         <v>12</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU14" t="n">
         <v>12.5</v>
@@ -4037,10 +4037,10 @@
         <v>12</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY14" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ14" t="n">
         <v>16</v>
@@ -4049,19 +4049,19 @@
         <v>18.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG14" t="n">
         <v>3.95</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -4201,10 +4201,10 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="U15" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -4267,22 +4267,22 @@
         <v>15.5</v>
       </c>
       <c r="AP15" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AT15" t="n">
         <v>12</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AV15" t="n">
         <v>7.6</v>
@@ -4291,28 +4291,28 @@
         <v>14.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AY15" t="n">
         <v>14</v>
       </c>
       <c r="AZ15" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BD15" t="n">
         <v>4.1</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF15" t="n">
         <v>4.1</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
         <v>2.4</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
         <v>3.35</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>
@@ -4670,16 +4670,16 @@
         <v>4.7</v>
       </c>
       <c r="G17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H17" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="I17" t="n">
         <v>1.99</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
         <v>3.7</v>
@@ -4697,7 +4697,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q17" t="n">
         <v>2.46</v>
@@ -4733,10 +4733,10 @@
         <v>28</v>
       </c>
       <c r="AB17" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD17" t="n">
         <v>13</v>
@@ -4781,7 +4781,7 @@
         <v>5.8</v>
       </c>
       <c r="AR17" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AS17" t="n">
         <v>17</v>
@@ -4790,7 +4790,7 @@
         <v>11.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
         <v>9.6</v>
@@ -4799,31 +4799,31 @@
         <v>18.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AY17" t="n">
         <v>16.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BB17" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BD17" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG17" t="n">
         <v>16</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-19 04:24:52</t>
+          <t>2026-05-19 06:37:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB17"/>
+  <dimension ref="A1:CB18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,7 +843,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -857,34 +857,34 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G2" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="H2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K2" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P2" t="n">
         <v>2.28</v>
@@ -893,194 +893,194 @@
         <v>1.64</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-19 06:37:02</t>
+          <t>2026-05-19 08:49:57</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="G3" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="H3" t="n">
-        <v>1.36</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
-        <v>870</v>
+        <v>5.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>500</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-19 06:37:02</t>
+          <t>2026-05-19 08:49:57</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="G4" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="H4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I4" t="n">
         <v>1.38</v>
       </c>
-      <c r="I4" t="n">
-        <v>1.47</v>
-      </c>
       <c r="J4" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="K4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-19 06:37:02</t>
+          <t>2026-05-19 08:49:57</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="G5" t="n">
         <v>1.27</v>
       </c>
       <c r="H5" t="n">
-        <v>1.15</v>
+        <v>16.5</v>
       </c>
       <c r="I5" t="n">
         <v>21</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-19 06:37:02</t>
+          <t>2026-05-19 08:49:57</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,36 +1859,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>FC Spaeri</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mjallby</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.96</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.74</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-19 06:37:02</t>
+          <t>2026-05-19 08:49:57</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,36 +2113,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Al-Hazm (KSA)</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="G7" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="H7" t="n">
-        <v>1.77</v>
+        <v>2.66</v>
       </c>
       <c r="I7" t="n">
-        <v>1.91</v>
+        <v>2.68</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.42</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.6</v>
+        <v>2.18</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-19 06:37:02</t>
+          <t>2026-05-19 08:49:57</t>
         </is>
       </c>
     </row>
@@ -2372,31 +2372,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>Al-Ittihad</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al-Akhdoud</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.41</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="n">
-        <v>1.48</v>
+        <v>2.74</v>
       </c>
       <c r="H8" t="n">
-        <v>7.6</v>
+        <v>2.56</v>
       </c>
       <c r="I8" t="n">
-        <v>10.5</v>
+        <v>2.78</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="K8" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-19 06:37:02</t>
+          <t>2026-05-19 08:49:57</t>
         </is>
       </c>
     </row>
@@ -2626,31 +2626,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NEOM Sports Club</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Al-Fateh (KSA)</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.87</v>
+        <v>2.42</v>
       </c>
       <c r="G9" t="n">
-        <v>2.12</v>
+        <v>2.72</v>
       </c>
       <c r="H9" t="n">
-        <v>2.94</v>
+        <v>2.64</v>
       </c>
       <c r="I9" t="n">
-        <v>4.6</v>
+        <v>2.96</v>
       </c>
       <c r="J9" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-19 06:37:02</t>
+          <t>2026-05-19 08:49:57</t>
         </is>
       </c>
     </row>
@@ -2880,31 +2880,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Al-Feiha</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>1.13</v>
       </c>
       <c r="G10" t="n">
-        <v>17.5</v>
+        <v>1.15</v>
       </c>
       <c r="H10" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="I10" t="n">
-        <v>1.29</v>
+        <v>32</v>
       </c>
       <c r="J10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K10" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.92</v>
+        <v>3.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-19 06:37:02</t>
+          <t>2026-05-19 08:49:57</t>
         </is>
       </c>
     </row>
@@ -3134,31 +3134,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>NEOM Sports Club</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al-Ettifaq</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.13</v>
+        <v>1.87</v>
       </c>
       <c r="G11" t="n">
-        <v>1.15</v>
+        <v>2.06</v>
       </c>
       <c r="H11" t="n">
-        <v>1.09</v>
+        <v>3.1</v>
       </c>
       <c r="I11" t="n">
-        <v>32</v>
+        <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>12</v>
+        <v>3.85</v>
       </c>
       <c r="K11" t="n">
-        <v>17</v>
+        <v>5.2</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.65</v>
+        <v>2.82</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-19 06:37:02</t>
+          <t>2026-05-19 08:49:57</t>
         </is>
       </c>
     </row>
@@ -3388,31 +3388,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Al-Kholood Club</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al-Fateh (KSA)</t>
+          <t>Al-Akhdoud</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.42</v>
+        <v>1.41</v>
       </c>
       <c r="G12" t="n">
-        <v>2.72</v>
+        <v>1.48</v>
       </c>
       <c r="H12" t="n">
-        <v>2.64</v>
+        <v>7.6</v>
       </c>
       <c r="I12" t="n">
-        <v>2.96</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-19 06:37:02</t>
+          <t>2026-05-19 08:49:57</t>
         </is>
       </c>
     </row>
@@ -3642,31 +3642,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="G13" t="n">
-        <v>2.74</v>
+        <v>5.6</v>
       </c>
       <c r="H13" t="n">
-        <v>2.56</v>
+        <v>1.78</v>
       </c>
       <c r="I13" t="n">
-        <v>2.78</v>
+        <v>1.91</v>
       </c>
       <c r="J13" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-19 06:37:02</t>
+          <t>2026-05-19 08:49:57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,42 +3891,42 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Yellow-Red Mechelen</t>
+          <t>Al-Feiha</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Al-Hilal</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>8.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="H14" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="I14" t="n">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="J14" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="K14" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3947,10 +3947,10 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3959,112 +3959,112 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-19 06:37:02</t>
+          <t>2026-05-19 08:49:57</t>
         </is>
       </c>
     </row>
@@ -4150,37 +4150,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Gent</t>
+          <t>Anderlecht</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Union St Gilloise</t>
+          <t>Sint Truiden</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.6</v>
+        <v>2.24</v>
       </c>
       <c r="G15" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="H15" t="n">
-        <v>1.77</v>
+        <v>3.1</v>
       </c>
       <c r="I15" t="n">
-        <v>1.91</v>
+        <v>3.35</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.91</v>
+        <v>1.52</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4201,10 +4201,10 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -4213,112 +4213,112 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-19 06:37:02</t>
+          <t>2026-05-19 08:49:57</t>
         </is>
       </c>
     </row>
@@ -4404,49 +4404,49 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Anderlecht</t>
+          <t>Yellow-Red Mechelen</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sint Truiden</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.24</v>
+        <v>7.6</v>
       </c>
       <c r="G16" t="n">
-        <v>2.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
         <v>3</v>
       </c>
-      <c r="I16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.36</v>
-      </c>
       <c r="Q16" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4455,10 +4455,10 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -4467,112 +4467,112 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BH16" t="n">
         <v>0</v>
@@ -4636,261 +4636,515 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-19 06:37:02</t>
+          <t>2026-05-19 08:49:57</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Belgian Pro League</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Gent</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Union St Gilloise</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-05-19 08:49:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Deportivo La Guaira</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Independiente Rivadavia</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F18" t="n">
         <v>4.7</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G18" t="n">
         <v>5.3</v>
       </c>
-      <c r="H17" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="J17" t="n">
+      <c r="H18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
         <v>3.4</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K18" t="n">
         <v>3.7</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1.11</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q18" t="n">
         <v>2.46</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.18</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>1.75</v>
       </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Y18" t="n">
         <v>7.8</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="Z18" t="n">
         <v>12.5</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AA18" t="n">
         <v>28</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AB18" t="n">
         <v>15.5</v>
       </c>
-      <c r="AC17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD17" t="n">
+      <c r="AC18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD18" t="n">
         <v>13</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AE18" t="n">
         <v>32</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AF18" t="n">
         <v>44</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AG18" t="n">
         <v>25</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AH18" t="n">
         <v>29</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AI18" t="n">
         <v>65</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AJ18" t="n">
         <v>170</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AK18" t="n">
         <v>110</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AL18" t="n">
         <v>120</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AM18" t="n">
         <v>220</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AN18" t="n">
         <v>160</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AO18" t="n">
         <v>26</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AP18" t="n">
         <v>8.4</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AQ18" t="n">
         <v>5.8</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="AR18" t="n">
         <v>9</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="AS18" t="n">
         <v>17</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="AT18" t="n">
         <v>11.5</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="AU18" t="n">
         <v>7.2</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="AV18" t="n">
         <v>9.6</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="AW18" t="n">
         <v>18.5</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="AX18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>4.6</v>
       </c>
-      <c r="AY17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG17" t="n">
+      <c r="BA18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG18" t="n">
         <v>16</v>
       </c>
-      <c r="BH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB17" t="inlineStr">
-        <is>
-          <t>2026-05-19 06:37:02</t>
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-05-19 08:49:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB18"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Indian Super League</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,60 +843,60 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Jamshedpur FC</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Kolos Kovalyovka</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.37</v>
+        <v>1.05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="H2" t="n">
-        <v>8.6</v>
+        <v>2.54</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>870</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5</v>
+        <v>1.09</v>
       </c>
       <c r="K2" t="n">
-        <v>5.9</v>
+        <v>500</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>4.7</v>
+        <v>1.24</v>
       </c>
       <c r="O2" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="R2" t="n">
-        <v>1.49</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -905,10 +905,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>2.96</v>
+        <v>2.36</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Indian Super League</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Punjab FC</t>
+          <t>FC Spaeri</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mumbai City FC</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="G3" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="I3" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Indian Super League</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,36 +1351,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>FC Rustavi</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Quess East Bengal</t>
+          <t>Samgurali Tskaltubo</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10.5</v>
+        <v>1.98</v>
       </c>
       <c r="G4" t="n">
-        <v>15.5</v>
+        <v>2.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.31</v>
+        <v>2.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1.38</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.24</v>
+        <v>1.79</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Indian Super League</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,36 +1605,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mohun Bagan Super Giants</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sporting Club Delhi</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.2</v>
+        <v>3.05</v>
       </c>
       <c r="G5" t="n">
-        <v>1.27</v>
+        <v>3.1</v>
       </c>
       <c r="H5" t="n">
-        <v>16.5</v>
+        <v>2.66</v>
       </c>
       <c r="I5" t="n">
-        <v>21</v>
+        <v>2.68</v>
       </c>
       <c r="J5" t="n">
-        <v>6.6</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>8.199999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.56</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Georgian Umaglesi Liga</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,36 +1859,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FC Spaeri</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>1.91</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>2.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,36 +2113,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mjallby</t>
+          <t>Al-Akhdoud</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1</v>
+        <v>1.48</v>
       </c>
       <c r="H7" t="n">
-        <v>2.66</v>
+        <v>3.15</v>
       </c>
       <c r="I7" t="n">
-        <v>2.68</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.18</v>
+        <v>1.45</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -2372,31 +2372,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>NEOM Sports Club</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Al-Ettifaq</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="G8" t="n">
-        <v>2.74</v>
+        <v>2.04</v>
       </c>
       <c r="H8" t="n">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="I8" t="n">
-        <v>2.78</v>
+        <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -2626,31 +2626,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Al-Kholood Club</t>
+          <t>Al-Feiha</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al-Fateh (KSA)</t>
+          <t>Al-Hilal</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.42</v>
+        <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>2.72</v>
+        <v>17.5</v>
       </c>
       <c r="H9" t="n">
-        <v>2.64</v>
+        <v>1.23</v>
       </c>
       <c r="I9" t="n">
-        <v>2.96</v>
+        <v>1.27</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>7</v>
       </c>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.4</v>
+        <v>2.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="G10" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="H10" t="n">
-        <v>1.09</v>
+        <v>9.4</v>
       </c>
       <c r="I10" t="n">
         <v>32</v>
@@ -2904,7 +2904,7 @@
         <v>12</v>
       </c>
       <c r="K10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -3134,31 +3134,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NEOM Sports Club</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Al-Fateh (KSA)</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="G11" t="n">
-        <v>2.06</v>
+        <v>2.72</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1</v>
+        <v>2.64</v>
       </c>
       <c r="I11" t="n">
-        <v>4.7</v>
+        <v>2.96</v>
       </c>
       <c r="J11" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K11" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -3388,50 +3388,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>Al-Ittihad</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al-Akhdoud</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.41</v>
+        <v>2.46</v>
       </c>
       <c r="G12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Q12" t="n">
         <v>1.48</v>
       </c>
-      <c r="H12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="I12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.58</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Belgian Pro League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,42 +3637,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Al-Hazm (KSA)</t>
+          <t>Yellow-Red Mechelen</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.55</v>
+        <v>7.6</v>
       </c>
       <c r="G13" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="H13" t="n">
-        <v>1.78</v>
+        <v>1.39</v>
       </c>
       <c r="I13" t="n">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="K13" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3693,10 +3693,10 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -3705,112 +3705,112 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Belgian Pro League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,180 +3891,180 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Al-Feiha</t>
+          <t>Gent</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Union St Gilloise</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>4.6</v>
       </c>
       <c r="G14" t="n">
-        <v>17.5</v>
+        <v>5.4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.23</v>
+        <v>1.77</v>
       </c>
       <c r="I14" t="n">
-        <v>1.27</v>
+        <v>1.91</v>
       </c>
       <c r="J14" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="K14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR14" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
         <v>2.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,42 +4399,42 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Yellow-Red Mechelen</t>
+          <t>Deportivo La Guaira</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>7.6</v>
+        <v>4.7</v>
       </c>
       <c r="G16" t="n">
-        <v>8.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="H16" t="n">
-        <v>1.39</v>
+        <v>1.86</v>
       </c>
       <c r="I16" t="n">
-        <v>1.45</v>
+        <v>1.99</v>
       </c>
       <c r="J16" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="K16" t="n">
-        <v>6.4</v>
+        <v>3.75</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3</v>
+        <v>1.59</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.41</v>
+        <v>2.46</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4455,10 +4455,10 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.67</v>
+        <v>2.18</v>
       </c>
       <c r="U16" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -4467,113 +4467,113 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>42</v>
+        <v>11.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>15.5</v>
+        <v>7.8</v>
       </c>
       <c r="Z16" t="n">
         <v>12.5</v>
       </c>
       <c r="AA16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB16" t="n">
         <v>15.5</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AC16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF16" t="n">
         <v>44</v>
       </c>
-      <c r="AC16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>75</v>
-      </c>
       <c r="AG16" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AH16" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AI16" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AJ16" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AK16" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AL16" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AM16" t="n">
-        <v>85</v>
+        <v>220</v>
       </c>
       <c r="AN16" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AO16" t="n">
-        <v>4.5</v>
+        <v>26</v>
       </c>
       <c r="AP16" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12</v>
+        <v>5.8</v>
       </c>
       <c r="AR16" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AS16" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AT16" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>12.5</v>
+        <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="AY16" t="n">
-        <v>6.6</v>
+        <v>17</v>
       </c>
       <c r="AZ16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG16" t="n">
         <v>16</v>
       </c>
-      <c r="BA16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BH16" t="n">
         <v>0</v>
       </c>
@@ -4636,515 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-19 08:49:57</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Belgian Pro League</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>15:30:00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Gent</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Union St Gilloise</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="G17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>150</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>95</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB17" t="inlineStr">
-        <is>
-          <t>2026-05-19 08:49:57</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CONMEBOL Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Deportivo La Guaira</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Independiente Rivadavia</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G18" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>170</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>160</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>16</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB18" t="inlineStr">
-        <is>
-          <t>2026-05-19 08:49:57</t>
+          <t>2026-05-19 11:03:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB16"/>
+  <dimension ref="A1:CB26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,16 +860,16 @@
         <v>1.05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="H2" t="n">
-        <v>2.54</v>
+        <v>2.82</v>
       </c>
       <c r="I2" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>2.92</v>
       </c>
       <c r="K2" t="n">
         <v>500</v>
@@ -881,16 +881,16 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="O2" t="n">
         <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
@@ -899,16 +899,16 @@
         <v>1.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>2.36</v>
+        <v>2.84</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1022,72 +1022,72 @@
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Georgian Umaglesi Liga</t>
+          <t>Indian Super League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FC Spaeri</t>
+          <t>Jamshedpur FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.91</v>
+        <v>1.38</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3</v>
+        <v>1.49</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9</v>
+        <v>8.6</v>
       </c>
       <c r="I3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X3" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>370</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR3" t="n">
         <v>4.9</v>
       </c>
-      <c r="J3" t="n">
+      <c r="AS3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Georgian Umaglesi Liga</t>
+          <t>Indian Super League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FC Rustavi</t>
+          <t>Punjab FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Samgurali Tskaltubo</t>
+          <t>Mumbai City FC</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="H4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="X4" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI4" t="n">
         <v>2.7</v>
       </c>
-      <c r="I4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="BJ4" t="n">
+        <v>970</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>970</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS4" t="n">
         <v>4.4</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>0</v>
-      </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Indian Super League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,234 +1605,234 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mjallby</t>
+          <t>Quess East Bengal</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.05</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1</v>
+        <v>13.5</v>
       </c>
       <c r="H5" t="n">
-        <v>2.66</v>
+        <v>1.33</v>
       </c>
       <c r="I5" t="n">
-        <v>2.68</v>
+        <v>1.41</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="K5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V5" t="n">
         <v>3.4</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Indian Super League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,234 +1859,234 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Al-Hazm (KSA)</t>
+          <t>Mohun Bagan Super Giants</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>Sporting Club Delhi</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.55</v>
+        <v>1.21</v>
       </c>
       <c r="G6" t="n">
-        <v>5.6</v>
+        <v>1.27</v>
       </c>
       <c r="H6" t="n">
-        <v>1.78</v>
+        <v>16.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.91</v>
+        <v>21</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P6" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,234 +2113,234 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>FC Spaeri</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al-Akhdoud</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="G7" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="H7" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J7" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P7" t="n">
-        <v>2.22</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.45</v>
+        <v>1.76</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,55 +2367,55 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NEOM Sports Club</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>870</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1.87</v>
       </c>
-      <c r="G8" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.45</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Al-Feiha</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>17.5</v>
+        <v>990</v>
       </c>
       <c r="H9" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>1.27</v>
+        <v>990</v>
       </c>
       <c r="J9" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="K9" t="n">
-        <v>8.199999999999999</v>
+        <v>500</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>2.92</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,36 +2875,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.14</v>
+        <v>2.54</v>
       </c>
       <c r="G10" t="n">
-        <v>1.17</v>
+        <v>3.2</v>
       </c>
       <c r="H10" t="n">
-        <v>9.4</v>
+        <v>2.86</v>
       </c>
       <c r="I10" t="n">
-        <v>32</v>
+        <v>3.5</v>
       </c>
       <c r="J10" t="n">
-        <v>12</v>
+        <v>3.15</v>
       </c>
       <c r="K10" t="n">
-        <v>16.5</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,36 +3129,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Al-Kholood Club</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al-Fateh (KSA)</t>
+          <t>Athlitiki Enosi Larissa</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.72</v>
+        <v>2.48</v>
       </c>
       <c r="H11" t="n">
-        <v>2.64</v>
+        <v>3.3</v>
       </c>
       <c r="I11" t="n">
-        <v>2.96</v>
+        <v>3.85</v>
       </c>
       <c r="J11" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.59</v>
+        <v>2.04</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,36 +3383,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.46</v>
+        <v>3.05</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="H12" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="I12" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="J12" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="K12" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.72</v>
+        <v>1.77</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.48</v>
+        <v>2.16</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,251 +3637,251 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Yellow-Red Mechelen</t>
+          <t>Rigas Futbola Skola</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>FK Jelgava</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.39</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>1.45</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="K13" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T13" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,42 +3891,42 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Gent</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Union St Gilloise</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="G14" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.77</v>
+        <v>3.65</v>
       </c>
       <c r="I14" t="n">
-        <v>1.91</v>
+        <v>4.5</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7</v>
+        <v>2.76</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.88</v>
+        <v>1.47</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.81</v>
+        <v>2.78</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3947,10 +3947,10 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3959,112 +3959,112 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,36 +4145,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Anderlecht</t>
+          <t>FC Rustavi</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sint Truiden</t>
+          <t>Samgurali Tskaltubo</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.24</v>
+        <v>1.98</v>
       </c>
       <c r="G15" t="n">
         <v>2.4</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="I15" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.36</v>
+        <v>1.79</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,261 +4382,2801 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-19 11:03:12</t>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Al-Hazm (KSA)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Al-Taawoun Buraidah</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-05-19 13:16:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Al Riyadh SC</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Al-Akhdoud</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>24</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>11</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-05-19 13:16:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NEOM Sports Club</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Al-Ettifaq</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-05-19 13:16:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Al-Feiha</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Al-Hilal</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>13</v>
+      </c>
+      <c r="G19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="J19" t="n">
+        <v>7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-05-19 13:16:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Dhamk</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H20" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-05-19 13:16:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Al-Kholood Club</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Al-Fateh (KSA)</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-05-19 13:16:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Al-Ittihad</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Al-Quadisiya (KSA)</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-05-19 13:16:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Belgian Pro League</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Anderlecht</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sint Truiden</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-05-19 13:16:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Belgian Pro League</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Yellow-Red Mechelen</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-05-19 13:16:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Belgian Pro League</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Gent</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Union St Gilloise</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-05-19 13:16:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Deportivo La Guaira</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Independiente Rivadavia</t>
         </is>
       </c>
-      <c r="F16" t="n">
+      <c r="F26" t="n">
         <v>4.7</v>
       </c>
-      <c r="G16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="J16" t="n">
+      <c r="G26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="J26" t="n">
         <v>3.4</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K26" t="n">
         <v>3.75</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>1.11</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
         <v>1.59</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q26" t="n">
         <v>2.46</v>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
         <v>2.18</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U26" t="n">
         <v>1.73</v>
       </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Y26" t="n">
         <v>7.8</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="Z26" t="n">
         <v>12.5</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AA26" t="n">
         <v>28</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AB26" t="n">
         <v>15.5</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AC26" t="n">
         <v>8.4</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AD26" t="n">
         <v>13</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AE26" t="n">
         <v>32</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AF26" t="n">
         <v>44</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AG26" t="n">
         <v>25</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AH26" t="n">
         <v>29</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AI26" t="n">
         <v>65</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AJ26" t="n">
         <v>170</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AK26" t="n">
         <v>110</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AL26" t="n">
         <v>120</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AM26" t="n">
         <v>220</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AN26" t="n">
         <v>160</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AO26" t="n">
         <v>26</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AP26" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AQ26" t="n">
         <v>5.8</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="AR26" t="n">
         <v>9</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="AS26" t="n">
         <v>17</v>
       </c>
-      <c r="AT16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV16" t="n">
+      <c r="AT26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV26" t="n">
         <v>9.6</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="AW26" t="n">
         <v>18.5</v>
       </c>
-      <c r="AX16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY16" t="n">
+      <c r="AX26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY26" t="n">
         <v>17</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="AZ26" t="n">
         <v>4.6</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BA26" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BB26" t="n">
         <v>5</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BC26" t="n">
         <v>4.9</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BD26" t="n">
         <v>5</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BE26" t="n">
         <v>5.1</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BF26" t="n">
         <v>5</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BG26" t="n">
         <v>16</v>
       </c>
-      <c r="BH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB16" t="inlineStr">
-        <is>
-          <t>2026-05-19 11:03:12</t>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-05-19 13:16:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB26"/>
+  <dimension ref="A1:CB30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,16 +860,16 @@
         <v>1.05</v>
       </c>
       <c r="G2" t="n">
-        <v>1.54</v>
+        <v>990</v>
       </c>
       <c r="H2" t="n">
-        <v>2.82</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
         <v>990</v>
       </c>
       <c r="J2" t="n">
-        <v>2.92</v>
+        <v>1.09</v>
       </c>
       <c r="K2" t="n">
         <v>500</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="O2" t="n">
         <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q2" t="n">
         <v>1.02</v>
@@ -908,7 +908,7 @@
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G3" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="H3" t="n">
         <v>8.6</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J3" t="n">
         <v>4.5</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.31</v>
@@ -1141,10 +1141,10 @@
         <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="R3" t="n">
         <v>1.49</v>
@@ -1153,16 +1153,16 @@
         <v>2.64</v>
       </c>
       <c r="T3" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="U3" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V3" t="n">
         <v>1.09</v>
       </c>
       <c r="W3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="X3" t="n">
         <v>25</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -1368,13 +1368,13 @@
         <v>2.02</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="H4" t="n">
         <v>3.45</v>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
         <v>3.05</v>
@@ -1398,13 +1398,13 @@
         <v>1.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="T4" t="n">
         <v>1.67</v>
@@ -1416,7 +1416,7 @@
         <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1428,7 +1428,7 @@
         <v>34</v>
       </c>
       <c r="AA4" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB4" t="n">
         <v>970</v>
@@ -1500,7 +1500,7 @@
         <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.05</v>
+        <v>8</v>
       </c>
       <c r="AZ4" t="n">
         <v>1.01</v>
@@ -1527,7 +1527,7 @@
         <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI4" t="n">
         <v>2.7</v>
@@ -1542,7 +1542,7 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BN4" t="n">
         <v>5.8</v>
@@ -1554,13 +1554,13 @@
         <v>970</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BR4" t="n">
         <v>36</v>
       </c>
       <c r="BS4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BT4" t="n">
         <v>8.4</v>
@@ -1572,23 +1572,23 @@
         <v>38</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BX4" t="n">
         <v>55</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>32</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>6.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M5" t="n">
         <v>1.04</v>
@@ -1724,10 +1724,10 @@
         <v>290</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AP5" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AQ5" t="n">
         <v>6.6</v>
@@ -1739,7 +1739,7 @@
         <v>8</v>
       </c>
       <c r="AT5" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
         <v>9.199999999999999</v>
@@ -1751,88 +1751,88 @@
         <v>11</v>
       </c>
       <c r="AX5" t="n">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
         <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>120</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>95</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>110</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>170</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
         <v>4.2</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -1912,13 +1912,13 @@
         <v>1.58</v>
       </c>
       <c r="S6" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="T6" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V6" t="n">
         <v>1.05</v>
@@ -1975,7 +1975,7 @@
         <v>290</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AO6" t="n">
         <v>630</v>
@@ -1984,109 +1984,109 @@
         <v>19</v>
       </c>
       <c r="AQ6" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>120</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
         <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AV6" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AY6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>160</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>170</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BL6" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS6" t="n">
         <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BU6" t="n">
         <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -2133,13 +2133,13 @@
         <v>2.3</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="I7" t="n">
         <v>4.9</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
         <v>4.5</v>
@@ -2166,7 +2166,7 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -2387,10 +2387,10 @@
         <v>1.69</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="I8" t="n">
-        <v>870</v>
+        <v>7.6</v>
       </c>
       <c r="J8" t="n">
         <v>3.65</v>
@@ -2399,212 +2399,212 @@
         <v>5.1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
         <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>990</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K9" t="n">
         <v>500</v>
@@ -2659,16 +2659,16 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O9" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I10" t="n">
         <v>3.2</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.5</v>
       </c>
       <c r="J10" t="n">
         <v>3.15</v>
@@ -2907,16 +2907,16 @@
         <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P10" t="n">
         <v>1.76</v>
@@ -2925,194 +2925,194 @@
         <v>2.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -3161,219 +3161,219 @@
         <v>3.7</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P11" t="n">
         <v>1.76</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Brondby</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mjallby</t>
+          <t>FC Copenhagen</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="H12" t="n">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="I12" t="n">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.16</v>
+        <v>1.84</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="BM12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BP12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BY12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Dutch Eredivisie</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,180 +3637,180 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Rigas Futbola Skola</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FK Jelgava</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
         <v>1.04</v>
       </c>
-      <c r="G13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N13" t="n">
-        <v>1.25</v>
+        <v>5.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.15</v>
+        <v>1.63</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.56</v>
       </c>
       <c r="S13" t="n">
-        <v>1.15</v>
+        <v>2.54</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,246 +3896,246 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="H14" t="n">
-        <v>3.65</v>
+        <v>2.62</v>
       </c>
       <c r="I14" t="n">
-        <v>4.5</v>
+        <v>2.64</v>
       </c>
       <c r="J14" t="n">
-        <v>2.76</v>
+        <v>3.35</v>
       </c>
       <c r="K14" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W14" t="n">
         <v>1.47</v>
       </c>
-      <c r="Q14" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Georgian Umaglesi Liga</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,246 +4150,246 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FC Rustavi</t>
+          <t>Rigas Futbola Skola</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Samgurali Tskaltubo</t>
+          <t>FK Jelgava</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.98</v>
+        <v>1.04</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7</v>
+        <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P15" t="n">
-        <v>1.79</v>
+        <v>1.28</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.84</v>
+        <v>1.12</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,36 +4399,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Al-Hazm (KSA)</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="G16" t="n">
-        <v>5.6</v>
+        <v>2.5</v>
       </c>
       <c r="H16" t="n">
-        <v>1.78</v>
+        <v>3.25</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="K16" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.34</v>
+        <v>1.47</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.6</v>
+        <v>2.78</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,14 +4636,14 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,234 +4653,234 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>FC Rustavi</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al-Akhdoud</t>
+          <t>Samgurali Tskaltubo</t>
         </is>
       </c>
       <c r="F17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L17" t="n">
         <v>1.35</v>
       </c>
-      <c r="G17" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="H17" t="n">
+      <c r="M17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X17" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU17" t="n">
         <v>6</v>
       </c>
-      <c r="I17" t="n">
+      <c r="AV17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>160</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>11</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>22</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW17" t="n">
         <v>24</v>
       </c>
-      <c r="J17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K17" t="n">
-        <v>11</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>0</v>
-      </c>
       <c r="BX17" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BY17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,229 +4912,229 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NEOM Sports Club</t>
+          <t>IA Akranes</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>IBV</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P18" t="n">
-        <v>2.78</v>
+        <v>1.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -5166,239 +5166,239 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Al-Feiha</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>13</v>
+        <v>3.25</v>
       </c>
       <c r="G19" t="n">
-        <v>17.5</v>
+        <v>5.6</v>
       </c>
       <c r="H19" t="n">
-        <v>1.23</v>
+        <v>1.78</v>
       </c>
       <c r="I19" t="n">
-        <v>1.27</v>
+        <v>1.97</v>
       </c>
       <c r="J19" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>8.6</v>
+        <v>5.3</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.94</v>
+        <v>2.34</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BH19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -5420,239 +5420,239 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al-Akhdoud</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="G20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>29</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>100</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O20" t="n">
         <v>1.17</v>
       </c>
-      <c r="H20" t="n">
-        <v>10</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="K20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
       <c r="P20" t="n">
-        <v>3.7</v>
+        <v>2.22</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -5674,239 +5674,239 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Al-Kholood Club</t>
+          <t>NEOM Sports Club</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al-Fateh (KSA)</t>
+          <t>Al-Ettifaq</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="G21" t="n">
-        <v>2.72</v>
+        <v>2.06</v>
       </c>
       <c r="H21" t="n">
-        <v>2.64</v>
+        <v>3.7</v>
       </c>
       <c r="I21" t="n">
-        <v>2.96</v>
+        <v>4.7</v>
       </c>
       <c r="J21" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K21" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.78</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
@@ -5928,31 +5928,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>Al-Feiha</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Al-Hilal</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.46</v>
+        <v>13</v>
       </c>
       <c r="G22" t="n">
-        <v>2.7</v>
+        <v>17.5</v>
       </c>
       <c r="H22" t="n">
-        <v>2.54</v>
+        <v>1.23</v>
       </c>
       <c r="I22" t="n">
-        <v>2.78</v>
+        <v>1.27</v>
       </c>
       <c r="J22" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="K22" t="n">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -5967,10 +5967,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.72</v>
+        <v>2.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,36 +6177,36 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Anderlecht</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sint Truiden</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.24</v>
+        <v>1.13</v>
       </c>
       <c r="G23" t="n">
-        <v>2.4</v>
+        <v>1.17</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>11.5</v>
       </c>
       <c r="I23" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>3.8</v>
+        <v>9.6</v>
       </c>
       <c r="K23" t="n">
-        <v>4.2</v>
+        <v>16.5</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -6221,10 +6221,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.36</v>
+        <v>3.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -6414,14 +6414,14 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,251 +6431,251 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Yellow-Red Mechelen</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Al-Fateh (KSA)</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>7.6</v>
+        <v>2.46</v>
       </c>
       <c r="G24" t="n">
-        <v>8.6</v>
+        <v>2.72</v>
       </c>
       <c r="H24" t="n">
-        <v>1.41</v>
+        <v>2.62</v>
       </c>
       <c r="I24" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T24" t="n">
         <v>1.45</v>
       </c>
-      <c r="J24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.66</v>
-      </c>
       <c r="U24" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X24" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="Y24" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD24" t="n">
         <v>16</v>
       </c>
-      <c r="Z24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AE24" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="AF24" t="n">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="AG24" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AH24" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AI24" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AJ24" t="n">
-        <v>200</v>
+        <v>46</v>
       </c>
       <c r="AK24" t="n">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="AL24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM24" t="n">
         <v>70</v>
       </c>
-      <c r="AM24" t="n">
-        <v>85</v>
-      </c>
       <c r="AN24" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>7.2</v>
+        <v>2.54</v>
       </c>
       <c r="AQ24" t="n">
-        <v>12</v>
+        <v>2.44</v>
       </c>
       <c r="AR24" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>12</v>
+        <v>2.62</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.2</v>
+        <v>2.42</v>
       </c>
       <c r="AU24" t="n">
-        <v>12.5</v>
+        <v>2.26</v>
       </c>
       <c r="AV24" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>12</v>
+        <v>2.58</v>
       </c>
       <c r="AX24" t="n">
-        <v>7.8</v>
+        <v>2.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>6.8</v>
+        <v>2.34</v>
       </c>
       <c r="AZ24" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BA24" t="n">
-        <v>18.5</v>
+        <v>2.6</v>
       </c>
       <c r="BB24" t="n">
-        <v>8.4</v>
+        <v>2.62</v>
       </c>
       <c r="BC24" t="n">
-        <v>8</v>
+        <v>2.56</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.8</v>
+        <v>2.58</v>
       </c>
       <c r="BE24" t="n">
-        <v>7.8</v>
+        <v>2.66</v>
       </c>
       <c r="BF24" t="n">
-        <v>7.8</v>
+        <v>2.78</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.95</v>
+        <v>2.78</v>
       </c>
       <c r="BH24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6685,42 +6685,42 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Gent</t>
+          <t>Al-Ittihad</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Union St Gilloise</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.6</v>
+        <v>2.46</v>
       </c>
       <c r="G25" t="n">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="H25" t="n">
-        <v>1.81</v>
+        <v>2.54</v>
       </c>
       <c r="I25" t="n">
-        <v>1.96</v>
+        <v>2.78</v>
       </c>
       <c r="J25" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="K25" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -6729,10 +6729,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.88</v>
+        <v>2.72</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.81</v>
+        <v>1.48</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -6741,10 +6741,10 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -6753,112 +6753,112 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BH25" t="n">
         <v>0</v>
@@ -6922,261 +6922,1277 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-19 13:16:11</t>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Belgian Pro League</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Yellow-Red Mechelen</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>200</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Belgian Pro League</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Gent</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Union St Gilloise</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Belgian Pro League</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Anderlecht</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sint Truiden</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Dutch Eredivisie</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>FC Utrecht</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Heerenveen</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Deportivo La Guaira</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Independiente Rivadavia</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="F30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>160</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ30" t="n">
         <v>4.7</v>
       </c>
-      <c r="G26" t="n">
+      <c r="BA30" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB30" t="n">
         <v>5.2</v>
       </c>
-      <c r="H26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>170</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>160</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE26" t="n">
+      <c r="BC30" t="n">
         <v>5.1</v>
       </c>
-      <c r="BF26" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG26" t="n">
+      <c r="BD30" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG30" t="n">
         <v>16</v>
       </c>
-      <c r="BH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB26" t="inlineStr">
-        <is>
-          <t>2026-05-19 13:16:11</t>
+      <c r="BH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:29:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB30"/>
+  <dimension ref="A1:CB33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
         <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
         <v>1.02</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
         <v>2.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="R3" t="n">
         <v>1.49</v>
@@ -1153,16 +1153,16 @@
         <v>2.64</v>
       </c>
       <c r="T3" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="U3" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="V3" t="n">
         <v>1.09</v>
       </c>
       <c r="W3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X3" t="n">
         <v>25</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -1365,58 +1365,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="H4" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6</v>
+        <v>2.82</v>
       </c>
       <c r="T4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>1.89</v>
+        <v>2.12</v>
       </c>
       <c r="V4" t="n">
         <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1425,10 +1425,10 @@
         <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AA4" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB4" t="n">
         <v>970</v>
@@ -1440,7 +1440,7 @@
         <v>970</v>
       </c>
       <c r="AE4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AF4" t="n">
         <v>970</v>
@@ -1452,16 +1452,16 @@
         <v>970</v>
       </c>
       <c r="AI4" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK4" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AL4" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1470,125 +1470,125 @@
         <v>970</v>
       </c>
       <c r="AO4" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.05</v>
+        <v>1.74</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.05</v>
+        <v>1.71</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="AT4" t="n">
-        <v>7</v>
+        <v>1.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="AY4" t="n">
-        <v>8</v>
+        <v>1.93</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BH4" t="n">
         <v>3.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="BJ4" t="n">
         <v>970</v>
       </c>
       <c r="BK4" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM4" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="BP4" t="n">
         <v>970</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BR4" t="n">
         <v>36</v>
       </c>
       <c r="BS4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BT4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="BV4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BX4" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BZ4" t="n">
         <v>32</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -1790,31 +1790,31 @@
         <v>14.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
         <v>190</v>
       </c>
       <c r="BM5" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
         <v>16.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
         <v>110</v>
       </c>
       <c r="BQ5" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
         <v>4.5</v>
@@ -1832,7 +1832,7 @@
         <v>29</v>
       </c>
       <c r="BY5" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="G6" t="n">
         <v>1.27</v>
@@ -1885,40 +1885,40 @@
         <v>21</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="K6" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="O6" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="S6" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="T6" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="U6" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="V6" t="n">
         <v>1.05</v>
@@ -1927,7 +1927,7 @@
         <v>4.7</v>
       </c>
       <c r="X6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Y6" t="n">
         <v>55</v>
@@ -1939,10 +1939,10 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AD6" t="n">
         <v>70</v>
@@ -1951,37 +1951,37 @@
         <v>420</v>
       </c>
       <c r="AF6" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AG6" t="n">
         <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AI6" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AJ6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AK6" t="n">
         <v>15.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM6" t="n">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AO6" t="n">
-        <v>630</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ6" t="n">
         <v>1.01</v>
@@ -1993,10 +1993,10 @@
         <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV6" t="n">
         <v>1.01</v>
@@ -2005,7 +2005,7 @@
         <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AY6" t="n">
         <v>8.800000000000001</v>
@@ -2020,7 +2020,7 @@
         <v>6.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BD6" t="n">
         <v>1.01</v>
@@ -2029,64 +2029,64 @@
         <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="BG6" t="n">
         <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BJ6" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="BM6" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="BP6" t="n">
         <v>7.8</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BR6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BS6" t="n">
         <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BU6" t="n">
         <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="BW6" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="BY6" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -2151,22 +2151,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.92</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
         <v>1.28</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.76</v>
+        <v>1.28</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.77</v>
+        <v>1.28</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -2405,40 +2405,40 @@
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
         <v>1.81</v>
       </c>
       <c r="U8" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V8" t="n">
         <v>1.15</v>
       </c>
       <c r="W8" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="X8" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
         <v>75</v>
@@ -2447,34 +2447,34 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD8" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AE8" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AG8" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AK8" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AL8" t="n">
         <v>40</v>
@@ -2483,64 +2483,64 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BB8" t="n">
         <v>11</v>
       </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR8" t="n">
+      <c r="BC8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BF8" t="n">
         <v>6.6</v>
       </c>
-      <c r="AS8" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BG8" t="n">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
@@ -2579,10 +2579,10 @@
         <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="BU8" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
@@ -2597,14 +2597,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
         <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -2674,7 +2674,7 @@
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
         <v>1.67</v>
       </c>
       <c r="U10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V10" t="n">
         <v>1.46</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G11" t="n">
         <v>2.48</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -3430,16 +3430,16 @@
         <v>2.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R12" t="n">
         <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="U12" t="n">
         <v>2.26</v>
@@ -3448,7 +3448,7 @@
         <v>1.71</v>
       </c>
       <c r="W12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X12" t="n">
         <v>19.5</v>
@@ -3463,7 +3463,7 @@
         <v>32</v>
       </c>
       <c r="AB12" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AC12" t="n">
         <v>8.4</v>
@@ -3478,10 +3478,10 @@
         <v>29</v>
       </c>
       <c r="AG12" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AI12" t="n">
         <v>36</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G13" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>3.95</v>
@@ -3690,7 +3690,7 @@
         <v>1.56</v>
       </c>
       <c r="S13" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T13" t="n">
         <v>1.61</v>
@@ -3738,7 +3738,7 @@
         <v>16.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ13" t="n">
         <v>22</v>
@@ -3762,7 +3762,7 @@
         <v>19.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AR13" t="n">
         <v>7.8</v>
@@ -3771,37 +3771,37 @@
         <v>9</v>
       </c>
       <c r="AT13" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AU13" t="n">
         <v>8.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="AX13" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AY13" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="BB13" t="n">
         <v>19</v>
       </c>
       <c r="BC13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="BE13" t="n">
         <v>8.800000000000001</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,175 +3896,175 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Rigas Futbola Skola</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mjallby</t>
+          <t>FK Jelgava</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>3.1</v>
+        <v>110</v>
       </c>
       <c r="H14" t="n">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>2.64</v>
+        <v>110</v>
       </c>
       <c r="J14" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4</v>
+        <v>110</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>1.32</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="P14" t="n">
-        <v>1.78</v>
+        <v>1.32</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.18</v>
+        <v>1.12</v>
       </c>
       <c r="R14" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>4.1</v>
+        <v>1.12</v>
       </c>
       <c r="T14" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,175 +4150,175 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Rigas Futbola Skola</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FK Jelgava</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="J15" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>1.28</v>
+        <v>3.45</v>
       </c>
       <c r="O15" t="n">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="P15" t="n">
-        <v>1.28</v>
+        <v>1.81</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.12</v>
+        <v>2.08</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>1.12</v>
+        <v>4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G16" t="n">
         <v>2.5</v>
       </c>
       <c r="H16" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="K16" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -4775,55 +4775,55 @@
         <v>70</v>
       </c>
       <c r="AP17" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
         <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
         <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
         <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
         <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
         <v>1.01</v>
@@ -4838,7 +4838,7 @@
         <v>12</v>
       </c>
       <c r="BK17" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL17" t="n">
         <v>160</v>
@@ -4850,31 +4850,31 @@
         <v>5.7</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BP17" t="n">
         <v>19</v>
       </c>
       <c r="BQ17" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BR17" t="n">
         <v>38</v>
       </c>
       <c r="BS17" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BT17" t="n">
         <v>8.6</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV17" t="n">
         <v>40</v>
       </c>
       <c r="BW17" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BX17" t="n">
         <v>55</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,229 +4912,229 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>IA Akranes</t>
+          <t>Al-Ittihad</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IBV</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.25</v>
+        <v>2.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.15</v>
+        <v>1.48</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -5166,239 +5166,239 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Al-Hazm (KSA)</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.25</v>
+        <v>1.12</v>
       </c>
       <c r="G19" t="n">
-        <v>5.6</v>
+        <v>1.13</v>
       </c>
       <c r="H19" t="n">
-        <v>1.78</v>
+        <v>18</v>
       </c>
       <c r="I19" t="n">
-        <v>1.97</v>
+        <v>870</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="K19" t="n">
-        <v>5.3</v>
+        <v>16.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.34</v>
+        <v>3.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="R19" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -5420,239 +5420,239 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>Al-Feiha</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al-Akhdoud</t>
+          <t>Al-Hilal</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.4</v>
+        <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>1.56</v>
+        <v>17.5</v>
       </c>
       <c r="H20" t="n">
-        <v>3.5</v>
+        <v>1.23</v>
       </c>
       <c r="I20" t="n">
-        <v>29</v>
+        <v>1.27</v>
       </c>
       <c r="J20" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="K20" t="n">
-        <v>100</v>
+        <v>8.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.22</v>
+        <v>2.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -5674,175 +5674,175 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NEOM Sports Club</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Al-Fateh (KSA)</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.87</v>
+        <v>2.46</v>
       </c>
       <c r="G21" t="n">
-        <v>2.06</v>
+        <v>2.72</v>
       </c>
       <c r="H21" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="I21" t="n">
-        <v>4.7</v>
+        <v>2.92</v>
       </c>
       <c r="J21" t="n">
         <v>3.7</v>
       </c>
       <c r="K21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N21" t="n">
         <v>5.1</v>
       </c>
-      <c r="L21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.78</v>
-      </c>
       <c r="O21" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="P21" t="n">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="R21" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="V21" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="W21" t="n">
-        <v>1.94</v>
+        <v>1.59</v>
       </c>
       <c r="X21" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="Y21" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="Z21" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB21" t="n">
         <v>18.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AD21" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AE21" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="AF21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AG21" t="n">
         <v>13</v>
       </c>
       <c r="AH21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR21" t="n">
         <v>18.5</v>
       </c>
-      <c r="AI21" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AS21" t="n">
-        <v>2.5</v>
+        <v>6.2</v>
       </c>
       <c r="AT21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY21" t="n">
         <v>10.5</v>
       </c>
-      <c r="AU21" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AZ21" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.38</v>
+        <v>6</v>
       </c>
       <c r="BB21" t="n">
-        <v>2.32</v>
+        <v>6</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.26</v>
+        <v>20</v>
       </c>
       <c r="BD21" t="n">
-        <v>18</v>
+        <v>5.9</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.42</v>
+        <v>6.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.5</v>
+        <v>12</v>
       </c>
       <c r="BH21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -5928,239 +5928,239 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Al-Feiha</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Al-Akhdoud</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>13</v>
+        <v>1.4</v>
       </c>
       <c r="G22" t="n">
-        <v>17.5</v>
+        <v>1.56</v>
       </c>
       <c r="H22" t="n">
-        <v>1.23</v>
+        <v>4.9</v>
       </c>
       <c r="I22" t="n">
-        <v>1.27</v>
+        <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="K22" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P22" t="n">
-        <v>2.94</v>
+        <v>2.22</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -6182,246 +6182,246 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.13</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>1.17</v>
+        <v>5.3</v>
       </c>
       <c r="H23" t="n">
-        <v>11.5</v>
+        <v>1.78</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>1.92</v>
       </c>
       <c r="J23" t="n">
-        <v>9.6</v>
+        <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>16.5</v>
+        <v>5.3</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P23" t="n">
-        <v>3.7</v>
+        <v>2.34</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BH23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6436,115 +6436,115 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Al-Kholood Club</t>
+          <t>IA Akranes</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al-Fateh (KSA)</t>
+          <t>IBV</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P24" t="n">
         <v>1.25</v>
       </c>
-      <c r="M24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.4</v>
-      </c>
       <c r="Q24" t="n">
-        <v>1.57</v>
+        <v>1.15</v>
       </c>
       <c r="R24" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>2.36</v>
+        <v>1.15</v>
       </c>
       <c r="T24" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
         <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
         <v>1000</v>
@@ -6553,58 +6553,58 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
@@ -6661,14 +6661,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -6690,239 +6690,239 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>NEOM Sports Club</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Al-Ettifaq</t>
         </is>
       </c>
       <c r="F25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U25" t="n">
         <v>2.46</v>
       </c>
-      <c r="G25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BH25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -6968,19 +6968,19 @@
         <v>5.5</v>
       </c>
       <c r="K26" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M26" t="n">
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="P26" t="n">
         <v>3</v>
@@ -6989,10 +6989,10 @@
         <v>1.41</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T26" t="n">
         <v>1.66</v>
@@ -7001,10 +7001,10 @@
         <v>2.3</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X26" t="n">
         <v>42</v>
@@ -7115,68 +7115,68 @@
         <v>3.95</v>
       </c>
       <c r="BH26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -7210,58 +7210,58 @@
         <v>4.6</v>
       </c>
       <c r="G27" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H27" t="n">
         <v>1.82</v>
       </c>
       <c r="I27" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="J27" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K27" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P27" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T27" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U27" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X27" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y27" t="n">
         <v>10.5</v>
@@ -7270,34 +7270,34 @@
         <v>13.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB27" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD27" t="n">
         <v>12.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF27" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AG27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI27" t="n">
         <v>46</v>
       </c>
       <c r="AJ27" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AK27" t="n">
         <v>80</v>
@@ -7306,7 +7306,7 @@
         <v>85</v>
       </c>
       <c r="AM27" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN27" t="n">
         <v>95</v>
@@ -7315,22 +7315,22 @@
         <v>15.5</v>
       </c>
       <c r="AP27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS27" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT27" t="n">
         <v>13.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV27" t="n">
         <v>8.800000000000001</v>
@@ -7339,98 +7339,98 @@
         <v>16.5</v>
       </c>
       <c r="AX27" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AY27" t="n">
         <v>16</v>
       </c>
       <c r="AZ27" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BC27" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BG27" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
         <v>2.4</v>
       </c>
       <c r="H28" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I28" t="n">
         <v>3.35</v>
@@ -7479,16 +7479,16 @@
         <v>4.2</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P28" t="n">
         <v>2.36</v>
@@ -7497,201 +7497,201 @@
         <v>1.63</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BH28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dutch Eredivisie</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7701,498 +7701,1260 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Zeljeznicar</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Siroki Brijeg</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.06</v>
+        <v>1.04</v>
       </c>
       <c r="G29" t="n">
-        <v>2.1</v>
+        <v>990</v>
       </c>
       <c r="H29" t="n">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="I29" t="n">
-        <v>3.8</v>
+        <v>990</v>
       </c>
       <c r="J29" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="K29" t="n">
-        <v>4.1</v>
+        <v>500</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P29" t="n">
-        <v>2.46</v>
+        <v>1.24</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-19 15:29:43</t>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Bosnian Premier League</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Fk Velez Mostar</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Sarajevo</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G30" t="n">
+        <v>990</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I30" t="n">
+        <v>990</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K30" t="n">
+        <v>500</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:42:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Dutch Eredivisie</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>FC Utrecht</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Heerenveen</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="X31" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>24</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB31" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:42:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Deportes Recoleta</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Cobreloa Calama</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G32" t="n">
+        <v>600</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I32" t="n">
+        <v>870</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K32" t="n">
+        <v>500</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB32" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:42:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Deportivo La Guaira</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Independiente Rivadavia</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="G30" t="n">
+      <c r="F33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G33" t="n">
         <v>5.4</v>
       </c>
-      <c r="H30" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="J30" t="n">
+      <c r="H33" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="J33" t="n">
         <v>3.4</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K33" t="n">
         <v>3.75</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
         <v>1.11</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
         <v>1.59</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="Q33" t="n">
         <v>2.46</v>
       </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
         <v>2.18</v>
       </c>
-      <c r="U30" t="n">
+      <c r="U33" t="n">
         <v>1.73</v>
       </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
         <v>10</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="Y33" t="n">
         <v>7.8</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="Z33" t="n">
         <v>12.5</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AA33" t="n">
         <v>27</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AB33" t="n">
         <v>15</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AC33" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AD33" t="n">
         <v>13</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AE33" t="n">
         <v>32</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AF33" t="n">
         <v>44</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AG33" t="n">
         <v>24</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AH33" t="n">
         <v>29</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AI33" t="n">
         <v>65</v>
       </c>
-      <c r="AJ30" t="n">
+      <c r="AJ33" t="n">
         <v>170</v>
       </c>
-      <c r="AK30" t="n">
+      <c r="AK33" t="n">
         <v>110</v>
       </c>
-      <c r="AL30" t="n">
+      <c r="AL33" t="n">
         <v>120</v>
       </c>
-      <c r="AM30" t="n">
+      <c r="AM33" t="n">
         <v>220</v>
       </c>
-      <c r="AN30" t="n">
+      <c r="AN33" t="n">
         <v>160</v>
       </c>
-      <c r="AO30" t="n">
+      <c r="AO33" t="n">
         <v>26</v>
       </c>
-      <c r="AP30" t="n">
+      <c r="AP33" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AQ30" t="n">
+      <c r="AQ33" t="n">
         <v>5.8</v>
       </c>
-      <c r="AR30" t="n">
+      <c r="AR33" t="n">
         <v>9</v>
       </c>
-      <c r="AS30" t="n">
+      <c r="AS33" t="n">
         <v>17</v>
       </c>
-      <c r="AT30" t="n">
+      <c r="AT33" t="n">
         <v>11</v>
       </c>
-      <c r="AU30" t="n">
+      <c r="AU33" t="n">
         <v>7.4</v>
       </c>
-      <c r="AV30" t="n">
+      <c r="AV33" t="n">
         <v>9.6</v>
       </c>
-      <c r="AW30" t="n">
+      <c r="AW33" t="n">
         <v>18.5</v>
       </c>
-      <c r="AX30" t="n">
+      <c r="AX33" t="n">
         <v>4.9</v>
       </c>
-      <c r="AY30" t="n">
+      <c r="AY33" t="n">
         <v>17.5</v>
       </c>
-      <c r="AZ30" t="n">
+      <c r="AZ33" t="n">
         <v>4.7</v>
       </c>
-      <c r="BA30" t="n">
+      <c r="BA33" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB30" t="n">
+      <c r="BB33" t="n">
         <v>5.2</v>
       </c>
-      <c r="BC30" t="n">
+      <c r="BC33" t="n">
         <v>5.1</v>
       </c>
-      <c r="BD30" t="n">
+      <c r="BD33" t="n">
         <v>5.2</v>
       </c>
-      <c r="BE30" t="n">
+      <c r="BE33" t="n">
         <v>5.3</v>
       </c>
-      <c r="BF30" t="n">
+      <c r="BF33" t="n">
         <v>5.2</v>
       </c>
-      <c r="BG30" t="n">
+      <c r="BG33" t="n">
         <v>16</v>
       </c>
-      <c r="BH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB30" t="inlineStr">
-        <is>
-          <t>2026-05-19 15:29:43</t>
+      <c r="BH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB33" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:42:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB33"/>
+  <dimension ref="A1:CB34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="O2" t="n">
         <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="Q2" t="n">
         <v>1.02</v>
@@ -896,7 +896,7 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -1114,19 +1114,19 @@
         <v>1.37</v>
       </c>
       <c r="G3" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H3" t="n">
         <v>8.6</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
         <v>4.5</v>
       </c>
       <c r="K3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
         <v>1.31</v>
@@ -1144,7 +1144,7 @@
         <v>2.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="R3" t="n">
         <v>1.49</v>
@@ -1153,16 +1153,16 @@
         <v>2.64</v>
       </c>
       <c r="T3" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="U3" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="V3" t="n">
         <v>1.09</v>
       </c>
       <c r="W3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="X3" t="n">
         <v>25</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -1395,10 +1395,10 @@
         <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="R4" t="n">
         <v>1.39</v>
@@ -1410,7 +1410,7 @@
         <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V4" t="n">
         <v>1.32</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
         <v>1.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q6" t="n">
         <v>1.6</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Georgian Umaglesi Liga</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,36 +2113,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FC Spaeri</t>
+          <t>FK Qabala</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Shamakhi FK</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2154,31 +2154,31 @@
         <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.28</v>
+        <v>1.02</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.28</v>
+        <v>1.51</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2343,21 +2343,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Greek Super League</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2372,67 +2372,67 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>FC Spaeri</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="G8" t="n">
-        <v>1.69</v>
+        <v>990</v>
       </c>
       <c r="H8" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>7.6</v>
+        <v>990</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="K8" t="n">
-        <v>5.1</v>
+        <v>500</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>1.27</v>
       </c>
       <c r="T8" t="n">
-        <v>1.81</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.83</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2441,7 +2441,7 @@
         <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
@@ -2450,97 +2450,97 @@
         <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
@@ -2579,7 +2579,7 @@
         <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
         <v>1.01</v>
@@ -2597,21 +2597,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,246 +2626,246 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.53</v>
       </c>
       <c r="G9" t="n">
-        <v>990</v>
+        <v>1.64</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="I9" t="n">
-        <v>990</v>
+        <v>7.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="K9" t="n">
-        <v>500</v>
+        <v>5.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.29</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="P9" t="n">
-        <v>1.28</v>
+        <v>2.16</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.23</v>
+        <v>1.67</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>1.64</v>
+        <v>2.78</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK9" t="n">
         <v>1.01</v>
       </c>
       <c r="BL9" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM9" t="n">
         <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ9" t="n">
         <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS9" t="n">
         <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BU9" t="n">
         <v>1.01</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW9" t="n">
         <v>1.01</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY9" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA9" t="n">
         <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Greek Super League</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,72 +2875,72 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.56</v>
+        <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>2.84</v>
+        <v>990</v>
       </c>
       <c r="H10" t="n">
-        <v>2.84</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>3.2</v>
+        <v>990</v>
       </c>
       <c r="J10" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>500</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>1.29</v>
       </c>
       <c r="O10" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>1.76</v>
+        <v>1.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>1.23</v>
       </c>
       <c r="R10" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>3.75</v>
+        <v>1.22</v>
       </c>
       <c r="T10" t="n">
-        <v>1.67</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2949,7 +2949,7 @@
         <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
@@ -2958,13 +2958,13 @@
         <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
         <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
         <v>1000</v>
@@ -2973,7 +2973,7 @@
         <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
@@ -2997,58 +2997,58 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -3134,31 +3134,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athlitiki Enosi Larissa</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="G11" t="n">
-        <v>2.48</v>
+        <v>2.84</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="I11" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3167,7 +3167,7 @@
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
         <v>1.39</v>
@@ -3176,133 +3176,133 @@
         <v>1.76</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
         <v>3.75</v>
       </c>
       <c r="T11" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="V11" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="W11" t="n">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="X11" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
         <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AF11" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>10.5</v>
+        <v>1.32</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10.5</v>
+        <v>1.32</v>
       </c>
       <c r="AR11" t="n">
-        <v>20</v>
+        <v>1.25</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.1</v>
+        <v>1.32</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.8</v>
+        <v>1.32</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.6</v>
+        <v>1.13</v>
       </c>
       <c r="AV11" t="n">
-        <v>12.5</v>
+        <v>1.32</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.9</v>
+        <v>1.28</v>
       </c>
       <c r="AX11" t="n">
-        <v>12.5</v>
+        <v>1.32</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.6</v>
+        <v>1.32</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16</v>
+        <v>1.24</v>
       </c>
       <c r="BA11" t="n">
-        <v>5</v>
+        <v>1.32</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.7</v>
+        <v>1.32</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.6</v>
+        <v>1.32</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.9</v>
+        <v>1.32</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.2</v>
+        <v>1.32</v>
       </c>
       <c r="BF11" t="n">
-        <v>17</v>
+        <v>1.32</v>
       </c>
       <c r="BG11" t="n">
-        <v>5</v>
+        <v>1.32</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Brondby</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Copenhagen</t>
+          <t>Athlitiki Enosi Larissa</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J12" t="n">
         <v>3.2</v>
       </c>
-      <c r="G12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.55</v>
-      </c>
       <c r="K12" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="P12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q12" t="n">
-        <v>1.86</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="T12" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="U12" t="n">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.71</v>
+        <v>1.35</v>
       </c>
       <c r="W12" t="n">
-        <v>1.41</v>
+        <v>1.69</v>
       </c>
       <c r="X12" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="AA12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK12" t="n">
         <v>32</v>
       </c>
-      <c r="AB12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>44</v>
-      </c>
       <c r="AL12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM12" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="AN12" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AO12" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="AP12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB12" t="n">
         <v>4.7</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS12" t="n">
+      <c r="BC12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE12" t="n">
         <v>5.2</v>
       </c>
-      <c r="AT12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BF12" t="n">
-        <v>5.2</v>
+        <v>17</v>
       </c>
       <c r="BG12" t="n">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
         <v>1.01</v>
       </c>
       <c r="BL12" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM12" t="n">
         <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BP12" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
         <v>1.01</v>
       </c>
       <c r="BR12" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
         <v>1.01</v>
       </c>
       <c r="BT12" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV12" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
         <v>1.01</v>
       </c>
       <c r="BX12" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
         <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dutch Eredivisie</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,251 +3637,251 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Brondby</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FC Groningen</t>
+          <t>FC Copenhagen</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.89</v>
+        <v>3.2</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="H13" t="n">
-        <v>3.95</v>
+        <v>2.34</v>
       </c>
       <c r="I13" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="J13" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="K13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BH13" t="n">
         <v>4.2</v>
       </c>
-      <c r="L13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2</v>
-      </c>
-      <c r="X13" t="n">
-        <v>26</v>
-      </c>
-      <c r="Y13" t="n">
+      <c r="BI13" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>130</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>30</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV13" t="n">
         <v>21</v>
       </c>
-      <c r="Z13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
       <c r="BW13" t="n">
         <v>1.01</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY13" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA13" t="n">
         <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Dutch Eredivisie</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,251 +3891,251 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Rigas Futbola Skola</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FK Jelgava</t>
+          <t>FC Groningen</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M14" t="n">
         <v>1.04</v>
       </c>
-      <c r="G14" t="n">
-        <v>110</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I14" t="n">
-        <v>110</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="K14" t="n">
-        <v>110</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N14" t="n">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="P14" t="n">
-        <v>1.32</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.12</v>
+        <v>1.63</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>1.56</v>
       </c>
       <c r="S14" t="n">
-        <v>1.12</v>
+        <v>2.52</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BL14" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,175 +4150,175 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Rigas Futbola Skola</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mjallby</t>
+          <t>FK Jelgava</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="G15" t="n">
-        <v>3.2</v>
+        <v>110</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>2.66</v>
+        <v>110</v>
       </c>
       <c r="J15" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="K15" t="n">
-        <v>3.45</v>
+        <v>110</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>3.45</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="P15" t="n">
-        <v>1.81</v>
+        <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.08</v>
+        <v>1.12</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>1.12</v>
       </c>
       <c r="T15" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,246 +4404,246 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.22</v>
+        <v>3.1</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="H16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S16" t="n">
         <v>4</v>
       </c>
-      <c r="I16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Georgian Umaglesi Liga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,229 +4658,229 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FC Rustavi</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Samgurali Tskaltubo</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.98</v>
+        <v>2.24</v>
       </c>
       <c r="G17" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="H17" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="K17" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="L17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.79</v>
+        <v>1.41</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.84</v>
+        <v>2.78</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN17" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR17" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT17" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV17" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ17" t="n">
         <v>0</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,234 +4907,234 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>FC Rustavi</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Samgurali Tskaltubo</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="H18" t="n">
-        <v>2.54</v>
+        <v>3.25</v>
       </c>
       <c r="I18" t="n">
-        <v>2.78</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>3.95</v>
+        <v>2.96</v>
       </c>
       <c r="K18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P18" t="n">
-        <v>2.72</v>
+        <v>1.79</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.48</v>
+        <v>1.84</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL18" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="BM18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP18" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR18" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV18" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -5166,31 +5166,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al-Ittihad</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.12</v>
+        <v>2.46</v>
       </c>
       <c r="G19" t="n">
-        <v>1.13</v>
+        <v>2.84</v>
       </c>
       <c r="H19" t="n">
-        <v>18</v>
+        <v>2.54</v>
       </c>
       <c r="I19" t="n">
-        <v>870</v>
+        <v>2.78</v>
       </c>
       <c r="J19" t="n">
-        <v>11.5</v>
+        <v>3.95</v>
       </c>
       <c r="K19" t="n">
-        <v>16.5</v>
+        <v>4.5</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.75</v>
+        <v>2.72</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -5420,31 +5420,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Al-Feiha</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H20" t="n">
+        <v>23</v>
+      </c>
+      <c r="I20" t="n">
+        <v>390</v>
+      </c>
+      <c r="J20" t="n">
         <v>13</v>
       </c>
-      <c r="G20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="J20" t="n">
-        <v>7</v>
-      </c>
       <c r="K20" t="n">
-        <v>8.6</v>
+        <v>16.5</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -5459,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.94</v>
+        <v>3.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -5674,239 +5674,239 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Al-Kholood Club</t>
+          <t>Al-Feiha</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al-Fateh (KSA)</t>
+          <t>Al-Hilal</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.46</v>
+        <v>13</v>
       </c>
       <c r="G21" t="n">
-        <v>2.72</v>
+        <v>17.5</v>
       </c>
       <c r="H21" t="n">
-        <v>2.62</v>
+        <v>1.22</v>
       </c>
       <c r="I21" t="n">
-        <v>2.92</v>
+        <v>1.29</v>
       </c>
       <c r="J21" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="K21" t="n">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="R21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -5928,175 +5928,175 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al-Akhdoud</t>
+          <t>Al-Fateh (KSA)</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.4</v>
+        <v>2.48</v>
       </c>
       <c r="G22" t="n">
-        <v>1.56</v>
+        <v>2.7</v>
       </c>
       <c r="H22" t="n">
-        <v>4.9</v>
+        <v>2.62</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="J22" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N22" t="n">
-        <v>2.22</v>
+        <v>5.1</v>
       </c>
       <c r="O22" t="n">
         <v>1.19</v>
       </c>
       <c r="P22" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="R22" t="n">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="S22" t="n">
-        <v>1.45</v>
+        <v>2.4</v>
       </c>
       <c r="T22" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="U22" t="n">
-        <v>1.92</v>
+        <v>2.54</v>
       </c>
       <c r="V22" t="n">
-        <v>1.07</v>
+        <v>1.54</v>
       </c>
       <c r="W22" t="n">
-        <v>2.78</v>
+        <v>1.59</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -6182,67 +6182,67 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Al-Hazm (KSA)</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>Al-Akhdoud</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>1.27</v>
       </c>
       <c r="G23" t="n">
-        <v>5.3</v>
+        <v>1.53</v>
       </c>
       <c r="H23" t="n">
-        <v>1.78</v>
+        <v>1.04</v>
       </c>
       <c r="I23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.92</v>
       </c>
-      <c r="J23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.01</v>
-      </c>
       <c r="V23" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.23</v>
+        <v>2.78</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -6278,7 +6278,7 @@
         <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
         <v>1000</v>
@@ -6299,58 +6299,58 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
         <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,14 +6414,14 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6436,31 +6436,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>IA Akranes</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IBV</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -6469,35 +6469,35 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="O24" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="P24" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="W24" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X24" t="n">
         <v>1000</v>
       </c>
@@ -6532,7 +6532,7 @@
         <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ24" t="n">
         <v>1000</v>
@@ -6553,58 +6553,58 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BA24" t="n">
         <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
@@ -6661,21 +6661,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6690,175 +6690,175 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NEOM Sports Club</t>
+          <t>IA Akranes</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>IBV</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="O25" t="n">
         <v>1.15</v>
       </c>
       <c r="P25" t="n">
-        <v>2.78</v>
+        <v>1.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="R25" t="n">
-        <v>1.72</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>2.16</v>
+        <v>1.15</v>
       </c>
       <c r="T25" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
@@ -6915,21 +6915,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6939,180 +6939,180 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Yellow-Red Mechelen</t>
+          <t>NEOM Sports Club</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Al-Ettifaq</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>7.6</v>
+        <v>1.84</v>
       </c>
       <c r="G26" t="n">
-        <v>8.6</v>
+        <v>2.02</v>
       </c>
       <c r="H26" t="n">
-        <v>1.41</v>
+        <v>3.7</v>
       </c>
       <c r="I26" t="n">
-        <v>1.45</v>
+        <v>4.4</v>
       </c>
       <c r="J26" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="K26" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="O26" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P26" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="R26" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="S26" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="T26" t="n">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="U26" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="V26" t="n">
-        <v>3.2</v>
+        <v>1.31</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>1.98</v>
       </c>
       <c r="X26" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="Y26" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Z26" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="AA26" t="n">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="AB26" t="n">
-        <v>44</v>
+        <v>970</v>
       </c>
       <c r="AC26" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AD26" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AE26" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="AF26" t="n">
-        <v>75</v>
+        <v>970</v>
       </c>
       <c r="AG26" t="n">
-        <v>30</v>
+        <v>970</v>
       </c>
       <c r="AH26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>23</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AK26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL26" t="n">
         <v>25</v>
       </c>
-      <c r="AJ26" t="n">
-        <v>200</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>100</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>70</v>
-      </c>
       <c r="AM26" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AN26" t="n">
-        <v>75</v>
+        <v>970</v>
       </c>
       <c r="AO26" t="n">
-        <v>4.4</v>
+        <v>25</v>
       </c>
       <c r="AP26" t="n">
-        <v>7.2</v>
+        <v>1.46</v>
       </c>
       <c r="AQ26" t="n">
-        <v>12</v>
+        <v>1.53</v>
       </c>
       <c r="AR26" t="n">
-        <v>10.5</v>
+        <v>1.39</v>
       </c>
       <c r="AS26" t="n">
-        <v>12</v>
+        <v>4.9</v>
       </c>
       <c r="AT26" t="n">
-        <v>7.2</v>
+        <v>1.95</v>
       </c>
       <c r="AU26" t="n">
-        <v>12.5</v>
+        <v>3.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>9.4</v>
+        <v>2.64</v>
       </c>
       <c r="AW26" t="n">
-        <v>12</v>
+        <v>1.4</v>
       </c>
       <c r="AX26" t="n">
-        <v>7.8</v>
+        <v>1.95</v>
       </c>
       <c r="AY26" t="n">
-        <v>25</v>
+        <v>3.65</v>
       </c>
       <c r="AZ26" t="n">
-        <v>16</v>
+        <v>1.95</v>
       </c>
       <c r="BA26" t="n">
-        <v>18.5</v>
+        <v>2.88</v>
       </c>
       <c r="BB26" t="n">
-        <v>8.4</v>
+        <v>1.53</v>
       </c>
       <c r="BC26" t="n">
-        <v>8</v>
+        <v>1.76</v>
       </c>
       <c r="BD26" t="n">
-        <v>7.8</v>
+        <v>1.44</v>
       </c>
       <c r="BE26" t="n">
-        <v>7.8</v>
+        <v>1.29</v>
       </c>
       <c r="BF26" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG26" t="n">
-        <v>3.95</v>
+        <v>18</v>
       </c>
       <c r="BH26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -7198,175 +7198,175 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Gent</t>
+          <t>Yellow-Red Mechelen</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Union St Gilloise</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="G27" t="n">
-        <v>5.3</v>
+        <v>8.6</v>
       </c>
       <c r="H27" t="n">
-        <v>1.82</v>
+        <v>1.41</v>
       </c>
       <c r="I27" t="n">
-        <v>1.92</v>
+        <v>1.45</v>
       </c>
       <c r="J27" t="n">
-        <v>3.85</v>
+        <v>5.5</v>
       </c>
       <c r="K27" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M27" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="N27" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="O27" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="P27" t="n">
-        <v>1.89</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.82</v>
+        <v>1.41</v>
       </c>
       <c r="R27" t="n">
-        <v>1.34</v>
+        <v>1.83</v>
       </c>
       <c r="S27" t="n">
-        <v>3.4</v>
+        <v>2.04</v>
       </c>
       <c r="T27" t="n">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="U27" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="V27" t="n">
-        <v>2.08</v>
+        <v>3.2</v>
       </c>
       <c r="W27" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="X27" t="n">
-        <v>18.5</v>
+        <v>42</v>
       </c>
       <c r="Y27" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="Z27" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AA27" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AB27" t="n">
-        <v>19.5</v>
+        <v>44</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.6</v>
+        <v>15.5</v>
       </c>
       <c r="AD27" t="n">
         <v>12.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AF27" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AG27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH27" t="n">
         <v>23</v>
       </c>
-      <c r="AH27" t="n">
-        <v>26</v>
-      </c>
       <c r="AI27" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="AJ27" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="AK27" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AL27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM27" t="n">
         <v>85</v>
       </c>
-      <c r="AM27" t="n">
-        <v>150</v>
-      </c>
       <c r="AN27" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AO27" t="n">
-        <v>15.5</v>
+        <v>4.4</v>
       </c>
       <c r="AP27" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="AQ27" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="AR27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV27" t="n">
         <v>9.4</v>
       </c>
-      <c r="AS27" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU27" t="n">
+      <c r="AW27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX27" t="n">
         <v>7.8</v>
       </c>
-      <c r="AV27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AY27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ27" t="n">
         <v>16</v>
       </c>
-      <c r="AZ27" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BA27" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="BC27" t="n">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG27" t="n">
-        <v>10.5</v>
+        <v>3.95</v>
       </c>
       <c r="BH27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -7452,176 +7452,176 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Anderlecht</t>
+          <t>Gent</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sint Truiden</t>
+          <t>Union St Gilloise</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.24</v>
+        <v>4.6</v>
       </c>
       <c r="G28" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>1.82</v>
       </c>
       <c r="I28" t="n">
-        <v>3.35</v>
+        <v>1.92</v>
       </c>
       <c r="J28" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA28" t="n">
         <v>4.2</v>
       </c>
-      <c r="L28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="X28" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AZ28" t="n">
+      <c r="BB28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG28" t="n">
         <v>10.5</v>
       </c>
-      <c r="BA28" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>3.2</v>
-      </c>
       <c r="BH28" t="n">
         <v>1000</v>
       </c>
@@ -7684,14 +7684,14 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Bosnian Premier League</t>
+          <t>Belgian Pro League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7706,115 +7706,115 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Zeljeznicar</t>
+          <t>Anderlecht</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Siroki Brijeg</t>
+          <t>Sint Truiden</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="G29" t="n">
-        <v>990</v>
+        <v>2.4</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="I29" t="n">
-        <v>990</v>
+        <v>3.35</v>
       </c>
       <c r="J29" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="K29" t="n">
-        <v>500</v>
+        <v>4.2</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N29" t="n">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="O29" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="P29" t="n">
-        <v>1.24</v>
+        <v>2.36</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="R29" t="n">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="S29" t="n">
-        <v>1.37</v>
+        <v>2.3</v>
       </c>
       <c r="T29" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.11</v>
+        <v>2.26</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN29" t="n">
         <v>1000</v>
@@ -7823,58 +7823,58 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BH29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
@@ -7960,12 +7960,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Fk Velez Mostar</t>
+          <t>Zeljeznicar</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Siroki Brijeg</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -7993,22 +7993,22 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P30" t="n">
         <v>1.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="R30" t="n">
         <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="T30" t="n">
         <v>1.11</v>
@@ -8192,14 +8192,14 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dutch Eredivisie</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8209,180 +8209,180 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Fk Velez Mostar</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="G31" t="n">
-        <v>2.08</v>
+        <v>990</v>
       </c>
       <c r="H31" t="n">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="I31" t="n">
-        <v>3.8</v>
+        <v>990</v>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="K31" t="n">
-        <v>4.2</v>
+        <v>500</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="O31" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="P31" t="n">
-        <v>2.46</v>
+        <v>1.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="R31" t="n">
-        <v>1.59</v>
+        <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>2.52</v>
+        <v>1.48</v>
       </c>
       <c r="T31" t="n">
-        <v>1.47</v>
+        <v>1.11</v>
       </c>
       <c r="U31" t="n">
-        <v>2.5</v>
+        <v>1.11</v>
       </c>
       <c r="V31" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC31" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD31" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH31" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AR31" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV31" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW31" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY31" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA31" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB31" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BC31" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="n">
         <v>1000</v>
@@ -8446,14 +8446,14 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Dutch Eredivisie</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8468,175 +8468,175 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Deportes Recoleta</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cobreloa Calama</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F32" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J32" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M32" t="n">
         <v>1.04</v>
       </c>
-      <c r="G32" t="n">
-        <v>600</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I32" t="n">
-        <v>870</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K32" t="n">
-        <v>500</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N32" t="n">
-        <v>1.25</v>
+        <v>5.3</v>
       </c>
       <c r="O32" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="P32" t="n">
-        <v>1.24</v>
+        <v>2.46</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="R32" t="n">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="S32" t="n">
-        <v>1.39</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U32" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W32" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="X32" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y32" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z32" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA32" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB32" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF32" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH32" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL32" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM32" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO32" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BH32" t="n">
         <v>1000</v>
@@ -8693,268 +8693,522 @@
         <v>1.01</v>
       </c>
       <c r="BZ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-19 17:42:27</t>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Deportes Recoleta</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Cobreloa Calama</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G33" t="n">
+        <v>600</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I33" t="n">
+        <v>870</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K33" t="n">
+        <v>500</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB33" t="inlineStr">
+        <is>
+          <t>2026-05-19 19:55:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Deportivo La Guaira</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Independiente Rivadavia</t>
         </is>
       </c>
-      <c r="F33" t="n">
+      <c r="F34" t="n">
         <v>4.7</v>
       </c>
-      <c r="G33" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="J33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
+      <c r="G34" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M34" t="n">
         <v>1.11</v>
       </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
+      <c r="N34" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P34" t="n">
         <v>1.59</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="Q34" t="n">
         <v>2.46</v>
       </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
+      <c r="R34" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="n">
         <v>2.18</v>
       </c>
-      <c r="U33" t="n">
+      <c r="U34" t="n">
         <v>1.73</v>
       </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y33" t="n">
+      <c r="V34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y34" t="n">
         <v>7.8</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="Z34" t="n">
         <v>12.5</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AA34" t="n">
         <v>27</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AB34" t="n">
         <v>15</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AC34" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AD34" t="n">
         <v>13</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AE34" t="n">
         <v>32</v>
       </c>
-      <c r="AF33" t="n">
+      <c r="AF34" t="n">
         <v>44</v>
       </c>
-      <c r="AG33" t="n">
+      <c r="AG34" t="n">
         <v>24</v>
       </c>
-      <c r="AH33" t="n">
+      <c r="AH34" t="n">
         <v>29</v>
       </c>
-      <c r="AI33" t="n">
+      <c r="AI34" t="n">
         <v>65</v>
       </c>
-      <c r="AJ33" t="n">
+      <c r="AJ34" t="n">
         <v>170</v>
       </c>
-      <c r="AK33" t="n">
+      <c r="AK34" t="n">
         <v>110</v>
       </c>
-      <c r="AL33" t="n">
+      <c r="AL34" t="n">
         <v>120</v>
       </c>
-      <c r="AM33" t="n">
+      <c r="AM34" t="n">
         <v>220</v>
       </c>
-      <c r="AN33" t="n">
+      <c r="AN34" t="n">
         <v>160</v>
       </c>
-      <c r="AO33" t="n">
+      <c r="AO34" t="n">
         <v>26</v>
       </c>
-      <c r="AP33" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ33" t="n">
+      <c r="AP34" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ34" t="n">
         <v>5.8</v>
       </c>
-      <c r="AR33" t="n">
+      <c r="AR34" t="n">
         <v>9</v>
       </c>
-      <c r="AS33" t="n">
+      <c r="AS34" t="n">
         <v>17</v>
       </c>
-      <c r="AT33" t="n">
+      <c r="AT34" t="n">
         <v>11</v>
       </c>
-      <c r="AU33" t="n">
+      <c r="AU34" t="n">
         <v>7.4</v>
       </c>
-      <c r="AV33" t="n">
+      <c r="AV34" t="n">
         <v>9.6</v>
       </c>
-      <c r="AW33" t="n">
+      <c r="AW34" t="n">
         <v>18.5</v>
       </c>
-      <c r="AX33" t="n">
+      <c r="AX34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB34" t="n">
         <v>4.9</v>
       </c>
-      <c r="AY33" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG33" t="n">
+      <c r="BC34" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG34" t="n">
         <v>16</v>
       </c>
-      <c r="BH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB33" t="inlineStr">
-        <is>
-          <t>2026-05-19 17:42:27</t>
+      <c r="BH34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB34" t="inlineStr">
+        <is>
+          <t>2026-05-19 19:55:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
         <v>990</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
         <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
         <v>1.02</v>
@@ -896,7 +896,7 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G3" t="n">
         <v>1.46</v>
       </c>
       <c r="H3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="L3" t="n">
         <v>1.31</v>
@@ -1141,10 +1141,10 @@
         <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R3" t="n">
         <v>1.49</v>
@@ -1153,16 +1153,16 @@
         <v>2.64</v>
       </c>
       <c r="T3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V3" t="n">
         <v>1.09</v>
       </c>
       <c r="W3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X3" t="n">
         <v>25</v>
@@ -1174,10 +1174,10 @@
         <v>100</v>
       </c>
       <c r="AA3" t="n">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
         <v>14</v>
@@ -1186,7 +1186,7 @@
         <v>40</v>
       </c>
       <c r="AE3" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF3" t="n">
         <v>10.5</v>
@@ -1198,7 +1198,7 @@
         <v>30</v>
       </c>
       <c r="AI3" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ3" t="n">
         <v>14</v>
@@ -1219,16 +1219,16 @@
         <v>210</v>
       </c>
       <c r="AP3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
         <v>7.2</v>
@@ -1240,19 +1240,19 @@
         <v>4.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY3" t="n">
         <v>8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB3" t="n">
         <v>9.199999999999999</v>
@@ -1261,16 +1261,16 @@
         <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BH3" t="n">
         <v>4.6</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1410,7 +1410,7 @@
         <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V4" t="n">
         <v>1.32</v>
@@ -1494,7 +1494,7 @@
         <v>1.93</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.87</v>
+        <v>5.6</v>
       </c>
       <c r="AX4" t="n">
         <v>1.94</v>
@@ -1527,7 +1527,7 @@
         <v>1.86</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI4" t="n">
         <v>2.94</v>
@@ -1536,7 +1536,7 @@
         <v>970</v>
       </c>
       <c r="BK4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BL4" t="n">
         <v>120</v>
@@ -1548,13 +1548,13 @@
         <v>5.9</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="BP4" t="n">
         <v>970</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR4" t="n">
         <v>36</v>
@@ -1578,17 +1578,17 @@
         <v>44</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BZ4" t="n">
         <v>32</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
         <v>130</v>
       </c>
       <c r="AG5" t="n">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="AH5" t="n">
         <v>30</v>
@@ -1739,7 +1739,7 @@
         <v>8</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU5" t="n">
         <v>9.199999999999999</v>
@@ -1751,31 +1751,31 @@
         <v>11</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AZ5" t="n">
         <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG5" t="n">
         <v>4.2</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
         <v>17</v>
       </c>
       <c r="AD6" t="n">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="AE6" t="n">
         <v>420</v>
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT6" t="n">
         <v>6.6</v>
@@ -1999,10 +1999,10 @@
         <v>11.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AX6" t="n">
         <v>5.7</v>
@@ -2011,10 +2011,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BB6" t="n">
         <v>6.6</v>
@@ -2023,16 +2023,16 @@
         <v>11</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BF6" t="n">
         <v>3.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH6" t="n">
         <v>5.1</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -2130,19 +2130,19 @@
         <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H7" t="n">
         <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2169,10 +2169,10 @@
         <v>1.51</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
         <v>970</v>
       </c>
       <c r="Y9" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="Z9" t="n">
         <v>75</v>
@@ -2707,7 +2707,7 @@
         <v>970</v>
       </c>
       <c r="AD9" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AE9" t="n">
         <v>100</v>
@@ -2719,7 +2719,7 @@
         <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AI9" t="n">
         <v>90</v>
@@ -2773,7 +2773,7 @@
         <v>4.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA9" t="n">
         <v>2.04</v>
@@ -2785,16 +2785,16 @@
         <v>5.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BF9" t="n">
         <v>3.95</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BH9" t="n">
         <v>4.2</v>
@@ -2803,7 +2803,7 @@
         <v>3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="BK9" t="n">
         <v>1.01</v>
@@ -2833,7 +2833,7 @@
         <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="BU9" t="n">
         <v>1.01</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -3185,10 +3185,10 @@
         <v>3.75</v>
       </c>
       <c r="T11" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="U11" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
         <v>1.46</v>
@@ -3209,10 +3209,10 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
         <v>1000</v>
@@ -3227,13 +3227,13 @@
         <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK11" t="n">
         <v>1000</v>
@@ -3245,64 +3245,64 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR11" t="n">
         <v>1.32</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AS11" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>2.2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H12" t="n">
         <v>3.3</v>
@@ -3427,13 +3427,13 @@
         <v>1.39</v>
       </c>
       <c r="P12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
         <v>2.04</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
         <v>3.75</v>
@@ -3448,7 +3448,7 @@
         <v>1.35</v>
       </c>
       <c r="W12" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="X12" t="n">
         <v>14.5</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -3657,46 +3657,46 @@
         <v>3.4</v>
       </c>
       <c r="H13" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I13" t="n">
         <v>2.4</v>
       </c>
       <c r="J13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R13" t="n">
         <v>1.38</v>
       </c>
-      <c r="M13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.4</v>
-      </c>
       <c r="S13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="U13" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V13" t="n">
         <v>1.71</v>
@@ -3705,7 +3705,7 @@
         <v>1.41</v>
       </c>
       <c r="X13" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y13" t="n">
         <v>13.5</v>
@@ -3717,7 +3717,7 @@
         <v>32</v>
       </c>
       <c r="AB13" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AC13" t="n">
         <v>8.4</v>
@@ -3729,7 +3729,7 @@
         <v>30</v>
       </c>
       <c r="AF13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG13" t="n">
         <v>970</v>
@@ -3738,7 +3738,7 @@
         <v>970</v>
       </c>
       <c r="AI13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ13" t="n">
         <v>70</v>
@@ -3750,7 +3750,7 @@
         <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AN13" t="n">
         <v>32</v>
@@ -3759,7 +3759,7 @@
         <v>22</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AQ13" t="n">
         <v>10</v>
@@ -3771,16 +3771,16 @@
         <v>5.2</v>
       </c>
       <c r="AT13" t="n">
-        <v>12</v>
+        <v>4.3</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV13" t="n">
         <v>10</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AX13" t="n">
         <v>5.1</v>
@@ -3804,7 +3804,7 @@
         <v>5.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF13" t="n">
         <v>5.2</v>
@@ -3813,13 +3813,13 @@
         <v>12.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="BJ13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK13" t="n">
         <v>1.01</v>
@@ -3837,13 +3837,13 @@
         <v>4.9</v>
       </c>
       <c r="BP13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BQ13" t="n">
         <v>1.01</v>
       </c>
       <c r="BR13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BS13" t="n">
         <v>1.01</v>
@@ -3867,14 +3867,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CA13" t="n">
         <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G14" t="n">
         <v>1.97</v>
@@ -3917,13 +3917,13 @@
         <v>4.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K14" t="n">
         <v>4.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="M14" t="n">
         <v>1.04</v>
@@ -3935,7 +3935,7 @@
         <v>1.21</v>
       </c>
       <c r="P14" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q14" t="n">
         <v>1.63</v>
@@ -3944,7 +3944,7 @@
         <v>1.56</v>
       </c>
       <c r="S14" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T14" t="n">
         <v>1.61</v>
@@ -4028,7 +4028,7 @@
         <v>9.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV14" t="n">
         <v>13</v>
@@ -4076,13 +4076,13 @@
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL14" t="n">
         <v>95</v>
       </c>
       <c r="BM14" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN14" t="n">
         <v>5.7</v>
@@ -4094,13 +4094,13 @@
         <v>14.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR14" t="n">
         <v>26</v>
       </c>
       <c r="BS14" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT14" t="n">
         <v>8.800000000000001</v>
@@ -4112,23 +4112,23 @@
         <v>34</v>
       </c>
       <c r="BW14" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BX14" t="n">
         <v>40</v>
       </c>
       <c r="BY14" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
         <v>18</v>
       </c>
       <c r="CA14" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -4162,19 +4162,19 @@
         <v>1.04</v>
       </c>
       <c r="G15" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H15" t="n">
         <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J15" t="n">
         <v>1.04</v>
       </c>
       <c r="K15" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -4201,10 +4201,10 @@
         <v>1.12</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
         <v>3.45</v>
       </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
@@ -4440,7 +4440,7 @@
         <v>3.45</v>
       </c>
       <c r="O16" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P16" t="n">
         <v>1.81</v>
@@ -4452,7 +4452,7 @@
         <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T16" t="n">
         <v>1.83</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q17" t="n">
         <v>2.78</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -5029,58 +5029,58 @@
         <v>70</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH18" t="n">
         <v>3.8</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -5432,16 +5432,16 @@
         <v>1.11</v>
       </c>
       <c r="G20" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="H20" t="n">
         <v>23</v>
       </c>
       <c r="I20" t="n">
-        <v>390</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="K20" t="n">
         <v>16.5</v>
@@ -5459,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G22" t="n">
         <v>2.7</v>
@@ -5946,13 +5946,13 @@
         <v>2.62</v>
       </c>
       <c r="I22" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="J22" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K22" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -5967,7 +5967,7 @@
         <v>1.19</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q22" t="n">
         <v>1.57</v>
@@ -5985,7 +5985,7 @@
         <v>2.54</v>
       </c>
       <c r="V22" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W22" t="n">
         <v>1.59</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -6200,7 +6200,7 @@
         <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="J23" t="n">
         <v>4.6</v>
@@ -6227,10 +6227,10 @@
         <v>1.45</v>
       </c>
       <c r="R23" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="S23" t="n">
-        <v>1.45</v>
+        <v>2.14</v>
       </c>
       <c r="T23" t="n">
         <v>1.73</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H24" t="n">
         <v>1.78</v>
       </c>
       <c r="I24" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K24" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -6469,7 +6469,7 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="O24" t="n">
         <v>1.2</v>
@@ -6487,13 +6487,13 @@
         <v>2.52</v>
       </c>
       <c r="T24" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V24" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="W24" t="n">
         <v>1.25</v>
@@ -6553,58 +6553,58 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BA24" t="n">
         <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6723,7 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O25" t="n">
         <v>1.15</v>
@@ -6741,10 +6741,10 @@
         <v>1.15</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V25" t="n">
         <v>1.01</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
         <v>1.51</v>
       </c>
       <c r="U26" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="V26" t="n">
         <v>1.31</v>
@@ -7007,10 +7007,10 @@
         <v>1.98</v>
       </c>
       <c r="X26" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="Y26" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="Z26" t="n">
         <v>36</v>
@@ -7085,10 +7085,10 @@
         <v>1.4</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AY26" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AZ26" t="n">
         <v>1.95</v>
@@ -7106,7 +7106,7 @@
         <v>1.44</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BF26" t="n">
         <v>5.9</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -7225,7 +7225,7 @@
         <v>6.2</v>
       </c>
       <c r="L27" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
         <v>1.02</v>
@@ -7240,7 +7240,7 @@
         <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R27" t="n">
         <v>1.83</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
         <v>4.3</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M28" t="n">
         <v>1.07</v>
@@ -7503,10 +7503,10 @@
         <v>3.4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U28" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V28" t="n">
         <v>2.08</v>
@@ -7623,68 +7623,68 @@
         <v>10.5</v>
       </c>
       <c r="BH28" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI28" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BJ28" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK28" t="n">
         <v>1.01</v>
       </c>
       <c r="BL28" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM28" t="n">
         <v>1.01</v>
       </c>
       <c r="BN28" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BO28" t="n">
         <v>1.01</v>
       </c>
       <c r="BP28" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BQ28" t="n">
         <v>1.01</v>
       </c>
       <c r="BR28" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS28" t="n">
         <v>1.01</v>
       </c>
       <c r="BT28" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU28" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BV28" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW28" t="n">
         <v>1.01</v>
       </c>
       <c r="BX28" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY28" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ28" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA28" t="n">
         <v>1.01</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
         <v>2.36</v>
       </c>
       <c r="O29" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P29" t="n">
         <v>2.36</v>
@@ -7751,16 +7751,16 @@
         <v>1.62</v>
       </c>
       <c r="R29" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="S29" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="T29" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="U29" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="V29" t="n">
         <v>1.43</v>
@@ -7769,112 +7769,112 @@
         <v>1.71</v>
       </c>
       <c r="X29" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="Y29" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="Z29" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AA29" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AB29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC29" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AE29" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI29" t="n">
         <v>36</v>
       </c>
-      <c r="AF29" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>42</v>
-      </c>
       <c r="AJ29" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK29" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL29" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM29" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP29" t="n">
-        <v>2.88</v>
+        <v>7.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>2.76</v>
+        <v>14.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.9</v>
+        <v>21</v>
       </c>
       <c r="AS29" t="n">
-        <v>3.05</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.68</v>
+        <v>12</v>
       </c>
       <c r="AU29" t="n">
-        <v>2.5</v>
+        <v>8.4</v>
       </c>
       <c r="AV29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY29" t="n">
         <v>10</v>
       </c>
-      <c r="AW29" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AZ29" t="n">
-        <v>2.74</v>
+        <v>6.4</v>
       </c>
       <c r="BA29" t="n">
-        <v>24</v>
+        <v>8.4</v>
       </c>
       <c r="BB29" t="n">
-        <v>2.94</v>
+        <v>8</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.86</v>
+        <v>7.4</v>
       </c>
       <c r="BD29" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="BE29" t="n">
-        <v>3.1</v>
+        <v>9.4</v>
       </c>
       <c r="BF29" t="n">
-        <v>3.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG29" t="n">
-        <v>3.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH29" t="n">
         <v>1000</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -8480,16 +8480,16 @@
         <v>2.04</v>
       </c>
       <c r="G32" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H32" t="n">
         <v>3.75</v>
       </c>
       <c r="I32" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J32" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K32" t="n">
         <v>4.2</v>
@@ -8513,7 +8513,7 @@
         <v>1.64</v>
       </c>
       <c r="R32" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S32" t="n">
         <v>2.5</v>
@@ -8525,10 +8525,10 @@
         <v>2.52</v>
       </c>
       <c r="V32" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W32" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="X32" t="n">
         <v>24</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -8734,13 +8734,13 @@
         <v>1.04</v>
       </c>
       <c r="G33" t="n">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H33" t="n">
         <v>1.04</v>
       </c>
       <c r="I33" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J33" t="n">
         <v>1.04</v>
@@ -8773,10 +8773,10 @@
         <v>1.39</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V33" t="n">
         <v>1.01</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
         <v>3.85</v>
       </c>
       <c r="L34" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="M34" t="n">
         <v>1.11</v>
@@ -9042,7 +9042,7 @@
         <v>11.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="Z34" t="n">
         <v>12.5</v>
@@ -9117,31 +9117,31 @@
         <v>18.5</v>
       </c>
       <c r="AX34" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AY34" t="n">
         <v>17.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BB34" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BC34" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BF34" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BG34" t="n">
         <v>16</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-19 19:55:31</t>
+          <t>2026-05-19 22:08:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB34"/>
+  <dimension ref="A1:CB36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G2" t="n">
-        <v>990</v>
+        <v>1.53</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I2" t="n">
         <v>990</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>2.96</v>
       </c>
       <c r="K2" t="n">
         <v>500</v>
@@ -908,7 +908,7 @@
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -1141,10 +1141,10 @@
         <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="R3" t="n">
         <v>1.49</v>
@@ -1153,10 +1153,10 @@
         <v>2.64</v>
       </c>
       <c r="T3" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="V3" t="n">
         <v>1.09</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>2.32</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I4" t="n">
         <v>4.2</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -1790,31 +1790,31 @@
         <v>14.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BL5" t="n">
         <v>190</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BN5" t="n">
         <v>16.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP5" t="n">
         <v>110</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BT5" t="n">
         <v>4.5</v>
@@ -1832,7 +1832,7 @@
         <v>29</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
         <v>6.4</v>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -2044,13 +2044,13 @@
         <v>17.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BL6" t="n">
         <v>260</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BN6" t="n">
         <v>4.2</v>
@@ -2068,25 +2068,25 @@
         <v>32</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BT6" t="n">
         <v>22</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BV6" t="n">
         <v>190</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BX6" t="n">
         <v>150</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -2292,65 +2292,65 @@
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -2546,55 +2546,55 @@
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2677,7 @@
         <v>2.78</v>
       </c>
       <c r="T9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U9" t="n">
         <v>2.06</v>
@@ -2743,76 +2743,76 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="AR9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BF9" t="n">
         <v>6.8</v>
       </c>
-      <c r="AS9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BG9" t="n">
-        <v>2.06</v>
+        <v>1.76</v>
       </c>
       <c r="BH9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI9" t="n">
         <v>3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
         <v>150</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
         <v>4.7</v>
@@ -2824,41 +2824,41 @@
         <v>12</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
         <v>29</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
         <v>11.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
         <v>65</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
         <v>70</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
         <v>21</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -2913,13 +2913,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
         <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
         <v>1.23</v>
@@ -3054,65 +3054,65 @@
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -3134,31 +3134,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Athlitiki Enosi Larissa</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.84</v>
+        <v>2.46</v>
       </c>
       <c r="H11" t="n">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="I11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J11" t="n">
         <v>3.2</v>
       </c>
-      <c r="J11" t="n">
-        <v>3.15</v>
-      </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3167,7 +3167,7 @@
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O11" t="n">
         <v>1.39</v>
@@ -3176,7 +3176,7 @@
         <v>1.76</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="R11" t="n">
         <v>1.29</v>
@@ -3185,188 +3185,188 @@
         <v>3.75</v>
       </c>
       <c r="T11" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="U11" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH11" t="n">
         <v>22</v>
       </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH11" t="n">
+      <c r="AI11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR11" t="n">
         <v>20</v>
       </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ11" t="n">
+      <c r="AS11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>24</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BR11" t="n">
         <v>44</v>
       </c>
-      <c r="AK11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -3388,49 +3388,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Athlitiki Enosi Larissa</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="G12" t="n">
-        <v>2.46</v>
+        <v>2.84</v>
       </c>
       <c r="H12" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N12" t="n">
         <v>3.3</v>
       </c>
-      <c r="I12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.2</v>
-      </c>
       <c r="O12" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="P12" t="n">
         <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R12" t="n">
         <v>1.29</v>
@@ -3439,188 +3439,188 @@
         <v>3.75</v>
       </c>
       <c r="T12" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BF12" t="n">
         <v>1.35</v>
       </c>
-      <c r="W12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="X12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>17</v>
-      </c>
       <c r="BG12" t="n">
-        <v>5</v>
+        <v>1.36</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>3.2</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H13" t="n">
         <v>2.36</v>
@@ -3669,7 +3669,7 @@
         <v>3.75</v>
       </c>
       <c r="L13" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
@@ -3681,7 +3681,7 @@
         <v>1.3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q13" t="n">
         <v>1.9</v>
@@ -3696,13 +3696,13 @@
         <v>1.6</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="V13" t="n">
         <v>1.71</v>
       </c>
       <c r="W13" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X13" t="n">
         <v>18.5</v>
@@ -3771,7 +3771,7 @@
         <v>5.2</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="AU13" t="n">
         <v>7</v>
@@ -3822,13 +3822,13 @@
         <v>11.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BL13" t="n">
         <v>130</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BN13" t="n">
         <v>7.8</v>
@@ -3840,13 +3840,13 @@
         <v>32</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BR13" t="n">
         <v>44</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BT13" t="n">
         <v>6.4</v>
@@ -3858,23 +3858,23 @@
         <v>21</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BX13" t="n">
         <v>36</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BZ13" t="n">
         <v>30</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
         <v>2.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R14" t="n">
         <v>1.56</v>
@@ -3989,7 +3989,7 @@
         <v>11</v>
       </c>
       <c r="AH14" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI14" t="n">
         <v>46</v>
@@ -4019,10 +4019,10 @@
         <v>18.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.8</v>
+        <v>25</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT14" t="n">
         <v>9.6</v>
@@ -4034,7 +4034,7 @@
         <v>13</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="AX14" t="n">
         <v>11</v>
@@ -4058,13 +4058,13 @@
         <v>21</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF14" t="n">
         <v>7.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.8</v>
+        <v>25</v>
       </c>
       <c r="BH14" t="n">
         <v>4.8</v>
@@ -4076,13 +4076,13 @@
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BL14" t="n">
         <v>95</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BN14" t="n">
         <v>5.7</v>
@@ -4094,13 +4094,13 @@
         <v>14.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BR14" t="n">
         <v>26</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BT14" t="n">
         <v>8.800000000000001</v>
@@ -4112,30 +4112,30 @@
         <v>34</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BX14" t="n">
         <v>40</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BZ14" t="n">
         <v>18</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,246 +4150,246 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Rigas Futbola Skola</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FK Jelgava</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="G15" t="n">
-        <v>990</v>
+        <v>2.6</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="I15" t="n">
-        <v>990</v>
+        <v>4.8</v>
       </c>
       <c r="J15" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="K15" t="n">
-        <v>500</v>
+        <v>3.25</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.12</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,246 +4404,246 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>FC Rustavi</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mjallby</t>
+          <t>Samgurali Tskaltubo</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.1</v>
+        <v>1.98</v>
       </c>
       <c r="G16" t="n">
-        <v>3.15</v>
+        <v>2.48</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="I16" t="n">
-        <v>2.62</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="K16" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="M16" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="P16" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="R16" t="n">
         <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="T16" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="U16" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="V16" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="W16" t="n">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="X16" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Y16" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="Z16" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AA16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>160</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BR16" t="n">
         <v>38</v>
       </c>
-      <c r="AB16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ16" t="n">
+      <c r="BS16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BX16" t="n">
         <v>55</v>
       </c>
-      <c r="AK16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>44</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>20</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>1000</v>
-      </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,246 +4658,246 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Rigas Futbola Skola</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>FK Jelgava</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="G17" t="n">
-        <v>2.54</v>
+        <v>990</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>990</v>
       </c>
       <c r="J17" t="n">
-        <v>2.82</v>
+        <v>1.04</v>
       </c>
       <c r="K17" t="n">
-        <v>3.3</v>
+        <v>500</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P17" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.78</v>
+        <v>1.12</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Georgian Umaglesi Liga</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,239 +4912,239 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FC Rustavi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Samgurali Tskaltubo</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.98</v>
+        <v>3.1</v>
       </c>
       <c r="G18" t="n">
-        <v>2.48</v>
+        <v>3.15</v>
       </c>
       <c r="H18" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="J18" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="L18" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="O18" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="P18" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="R18" t="n">
         <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="T18" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="U18" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="V18" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="W18" t="n">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="X18" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="Z18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO18" t="n">
         <v>36</v>
       </c>
-      <c r="AA18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="AP18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>44</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE18" t="n">
         <v>11</v>
       </c>
-      <c r="AC18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD18" t="n">
+      <c r="BF18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG18" t="n">
         <v>20</v>
       </c>
-      <c r="AE18" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL18" t="n">
+      <c r="BH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>38</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>60</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BZ18" t="n">
         <v>48</v>
       </c>
-      <c r="AM18" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>160</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>19</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>38</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>40</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>55</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>0</v>
-      </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -5166,31 +5166,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Al-Ittihad</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al-Quadisiya (KSA)</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.46</v>
+        <v>1.11</v>
       </c>
       <c r="G19" t="n">
-        <v>2.84</v>
+        <v>1.12</v>
       </c>
       <c r="H19" t="n">
-        <v>2.54</v>
+        <v>26</v>
       </c>
       <c r="I19" t="n">
-        <v>2.78</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>3.95</v>
+        <v>12</v>
       </c>
       <c r="K19" t="n">
-        <v>4.5</v>
+        <v>16.5</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.76</v>
+        <v>3.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -5420,31 +5420,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al-Ittihad</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al-Quadisiya (KSA)</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.11</v>
+        <v>2.52</v>
       </c>
       <c r="G20" t="n">
-        <v>1.13</v>
+        <v>2.94</v>
       </c>
       <c r="H20" t="n">
-        <v>23</v>
+        <v>2.46</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="J20" t="n">
-        <v>11.5</v>
+        <v>3.95</v>
       </c>
       <c r="K20" t="n">
-        <v>16.5</v>
+        <v>4.5</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -5459,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -5674,239 +5674,239 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Al-Feiha</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al-Hilal</t>
+          <t>Al-Fateh (KSA)</t>
         </is>
       </c>
       <c r="F21" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X21" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG21" t="n">
         <v>13</v>
       </c>
-      <c r="G21" t="n">
+      <c r="AH21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN21" t="n">
         <v>17.5</v>
       </c>
-      <c r="H21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="J21" t="n">
-        <v>7</v>
-      </c>
-      <c r="K21" t="n">
+      <c r="AO21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BN21" t="n">
         <v>8.6</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>0</v>
-      </c>
       <c r="BO21" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BP21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BQ21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BR21" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BS21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BT21" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU21" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BV21" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BW21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BX21" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BY21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="CA21" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -5928,246 +5928,246 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Al-Kholood Club</t>
+          <t>Al-Feiha</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al-Fateh (KSA)</t>
+          <t>Al-Hilal</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.46</v>
+        <v>13</v>
       </c>
       <c r="G22" t="n">
-        <v>2.7</v>
+        <v>17.5</v>
       </c>
       <c r="H22" t="n">
-        <v>2.62</v>
+        <v>1.22</v>
       </c>
       <c r="I22" t="n">
-        <v>2.98</v>
+        <v>1.28</v>
       </c>
       <c r="J22" t="n">
-        <v>3.7</v>
+        <v>7.2</v>
       </c>
       <c r="K22" t="n">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.42</v>
+        <v>2.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="R22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6182,31 +6182,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>IA Akranes</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al-Akhdoud</t>
+          <t>IBV</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -6215,34 +6215,34 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>2.22</v>
+        <v>1.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P23" t="n">
-        <v>2.22</v>
+        <v>1.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="R23" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>2.14</v>
+        <v>1.15</v>
       </c>
       <c r="T23" t="n">
-        <v>1.73</v>
+        <v>1.11</v>
       </c>
       <c r="U23" t="n">
-        <v>1.92</v>
+        <v>1.11</v>
       </c>
       <c r="V23" t="n">
         <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -6356,65 +6356,65 @@
         <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23" t="n">
         <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN23" t="n">
         <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT23" t="n">
         <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -6436,31 +6436,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Al-Hazm (KSA)</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al-Taawoun Buraidah</t>
+          <t>Al-Akhdoud</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4.1</v>
+        <v>1.28</v>
       </c>
       <c r="G24" t="n">
-        <v>4.9</v>
+        <v>1.51</v>
       </c>
       <c r="H24" t="n">
-        <v>1.78</v>
+        <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>1.95</v>
+        <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="K24" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -6469,22 +6469,22 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="O24" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="P24" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="R24" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="S24" t="n">
-        <v>2.52</v>
+        <v>2.08</v>
       </c>
       <c r="T24" t="n">
         <v>1.11</v>
@@ -6493,10 +6493,10 @@
         <v>1.11</v>
       </c>
       <c r="V24" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.25</v>
+        <v>2.96</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -6532,7 +6532,7 @@
         <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
         <v>1000</v>
@@ -6553,129 +6553,129 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
         <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BN24" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BP24" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BR24" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6690,239 +6690,239 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>IA Akranes</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IBV</t>
+          <t>Al-Taawoun Buraidah</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N25" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="O25" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="P25" t="n">
-        <v>1.25</v>
+        <v>2.34</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.15</v>
+        <v>1.62</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="S25" t="n">
-        <v>1.15</v>
+        <v>2.56</v>
       </c>
       <c r="T25" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="U25" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25" t="n">
         <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN25" t="n">
         <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT25" t="n">
         <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>3.75</v>
       </c>
       <c r="K26" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -7118,65 +7118,65 @@
         <v>1000</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BJ26" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BN26" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP26" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="BR26" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="BT26" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV26" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BX26" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BZ26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -7372,65 +7372,65 @@
         <v>1000</v>
       </c>
       <c r="BI27" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BJ27" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BN27" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BO27" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BP27" t="n">
         <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BT27" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BV27" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BX27" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BZ27" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -7503,10 +7503,10 @@
         <v>3.4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="U28" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="V28" t="n">
         <v>2.08</v>
@@ -7518,7 +7518,7 @@
         <v>18.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Z28" t="n">
         <v>13.5</v>
@@ -7593,7 +7593,7 @@
         <v>16.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AY28" t="n">
         <v>16</v>
@@ -7602,22 +7602,22 @@
         <v>17.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BC28" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BG28" t="n">
         <v>10.5</v>
@@ -7632,31 +7632,31 @@
         <v>12.5</v>
       </c>
       <c r="BK28" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BL28" t="n">
         <v>160</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BN28" t="n">
         <v>10</v>
       </c>
       <c r="BO28" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP28" t="n">
         <v>55</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BR28" t="n">
         <v>65</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BT28" t="n">
         <v>5.2</v>
@@ -7668,23 +7668,23 @@
         <v>15.5</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BX28" t="n">
         <v>34</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BZ28" t="n">
         <v>29</v>
       </c>
       <c r="CA28" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -7739,7 +7739,7 @@
         <v>1.03</v>
       </c>
       <c r="N29" t="n">
-        <v>2.36</v>
+        <v>1.1</v>
       </c>
       <c r="O29" t="n">
         <v>1.19</v>
@@ -7793,7 +7793,7 @@
         <v>32</v>
       </c>
       <c r="AF29" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AG29" t="n">
         <v>12</v>
@@ -7880,65 +7880,65 @@
         <v>1000</v>
       </c>
       <c r="BI29" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="BJ29" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK29" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BN29" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO29" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP29" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ29" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BR29" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS29" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BT29" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU29" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV29" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW29" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BX29" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY29" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="BZ29" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA29" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -8134,65 +8134,65 @@
         <v>1000</v>
       </c>
       <c r="BI30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ30" t="n">
         <v>1000</v>
       </c>
       <c r="BK30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN30" t="n">
         <v>1000</v>
       </c>
       <c r="BO30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP30" t="n">
         <v>1000</v>
       </c>
       <c r="BQ30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR30" t="n">
         <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT30" t="n">
         <v>1000</v>
       </c>
       <c r="BU30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ30" t="n">
         <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -8388,72 +8388,72 @@
         <v>1000</v>
       </c>
       <c r="BI31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ31" t="n">
         <v>1000</v>
       </c>
       <c r="BK31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN31" t="n">
         <v>1000</v>
       </c>
       <c r="BO31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP31" t="n">
         <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT31" t="n">
         <v>1000</v>
       </c>
       <c r="BU31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ31" t="n">
         <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dutch Eredivisie</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8468,246 +8468,246 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Deportes Recoleta</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Cobreloa Calama</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="G32" t="n">
-        <v>2.06</v>
+        <v>990</v>
       </c>
       <c r="H32" t="n">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="I32" t="n">
-        <v>3.8</v>
+        <v>990</v>
       </c>
       <c r="J32" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="K32" t="n">
-        <v>4.2</v>
+        <v>500</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>5.3</v>
+        <v>1.25</v>
       </c>
       <c r="O32" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="P32" t="n">
-        <v>2.46</v>
+        <v>1.24</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="R32" t="n">
-        <v>1.59</v>
+        <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>2.5</v>
+        <v>1.39</v>
       </c>
       <c r="T32" t="n">
-        <v>1.58</v>
+        <v>1.11</v>
       </c>
       <c r="U32" t="n">
-        <v>2.52</v>
+        <v>1.11</v>
       </c>
       <c r="V32" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AM32" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AR32" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AS32" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="AT32" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AU32" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV32" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW32" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AX32" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY32" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA32" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB32" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BC32" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BD32" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BE32" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF32" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BG32" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BH32" t="n">
         <v>1000</v>
       </c>
       <c r="BI32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ32" t="n">
         <v>1000</v>
       </c>
       <c r="BK32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN32" t="n">
         <v>1000</v>
       </c>
       <c r="BO32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP32" t="n">
         <v>1000</v>
       </c>
       <c r="BQ32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR32" t="n">
         <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT32" t="n">
         <v>1000</v>
       </c>
       <c r="BU32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV32" t="n">
         <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ32" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Dutch Eredivisie</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8722,239 +8722,239 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Deportes Recoleta</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cobreloa Calama</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="G33" t="n">
-        <v>990</v>
+        <v>2.06</v>
       </c>
       <c r="H33" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="I33" t="n">
-        <v>990</v>
+        <v>3.8</v>
       </c>
       <c r="J33" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="K33" t="n">
-        <v>500</v>
+        <v>4.2</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M33" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N33" t="n">
-        <v>1.25</v>
+        <v>5.3</v>
       </c>
       <c r="O33" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="P33" t="n">
-        <v>1.24</v>
+        <v>2.46</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="R33" t="n">
-        <v>1.18</v>
+        <v>1.59</v>
       </c>
       <c r="S33" t="n">
-        <v>1.39</v>
+        <v>2.5</v>
       </c>
       <c r="T33" t="n">
-        <v>1.11</v>
+        <v>1.58</v>
       </c>
       <c r="U33" t="n">
-        <v>1.11</v>
+        <v>2.52</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BH33" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI33" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BJ33" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK33" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BL33" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM33" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BN33" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO33" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP33" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ33" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BR33" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS33" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BT33" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU33" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BV33" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW33" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BX33" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY33" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BZ33" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="CA33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
         <v>11.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="Z34" t="n">
         <v>12.5</v>
@@ -9117,31 +9117,31 @@
         <v>18.5</v>
       </c>
       <c r="AX34" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AY34" t="n">
         <v>17.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BB34" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BC34" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BD34" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BE34" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF34" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BG34" t="n">
         <v>16</v>
@@ -9150,65 +9150,573 @@
         <v>1000</v>
       </c>
       <c r="BI34" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BJ34" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BK34" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BL34" t="n">
         <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BN34" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BO34" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="BP34" t="n">
         <v>1000</v>
       </c>
       <c r="BQ34" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BR34" t="n">
         <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BT34" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU34" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BV34" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW34" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BX34" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY34" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="BZ34" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA34" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-19 22:08:15</t>
+          <t>2026-05-20 00:21:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Univ Catolica (Chile)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Barcelona (ECU)</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H35" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I35" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>16</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BQ35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BR35" t="n">
+        <v>48</v>
+      </c>
+      <c r="BS35" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BT35" t="n">
+        <v>13</v>
+      </c>
+      <c r="BU35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BV35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BX35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BZ35" t="n">
+        <v>40</v>
+      </c>
+      <c r="CA35" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CB35" t="inlineStr">
+        <is>
+          <t>2026-05-20 00:21:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CONMEBOL Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Penarol</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X36" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>44</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>230</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>27</v>
+      </c>
+      <c r="BQ36" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR36" t="n">
+        <v>55</v>
+      </c>
+      <c r="BS36" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT36" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU36" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV36" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW36" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BX36" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY36" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BZ36" t="n">
+        <v>60</v>
+      </c>
+      <c r="CA36" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="CB36" t="inlineStr">
+        <is>
+          <t>2026-05-20 00:21:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
@@ -863,7 +863,7 @@
         <v>1.53</v>
       </c>
       <c r="H2" t="n">
-        <v>1.09</v>
+        <v>1.91</v>
       </c>
       <c r="I2" t="n">
         <v>990</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
         <v>4.4</v>
@@ -1129,7 +1129,7 @@
         <v>6.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
@@ -1144,16 +1144,16 @@
         <v>2.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S3" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="T3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U3" t="n">
         <v>1.78</v>
@@ -1162,10 +1162,10 @@
         <v>1.09</v>
       </c>
       <c r="W3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="X3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y3" t="n">
         <v>36</v>
@@ -1174,10 +1174,10 @@
         <v>100</v>
       </c>
       <c r="AA3" t="n">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="AB3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC3" t="n">
         <v>14</v>
@@ -1186,7 +1186,7 @@
         <v>40</v>
       </c>
       <c r="AE3" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AF3" t="n">
         <v>10.5</v>
@@ -1198,7 +1198,7 @@
         <v>30</v>
       </c>
       <c r="AI3" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AJ3" t="n">
         <v>14</v>
@@ -1216,43 +1216,43 @@
         <v>6.8</v>
       </c>
       <c r="AO3" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AP3" t="n">
         <v>16</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AY3" t="n">
         <v>8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB3" t="n">
         <v>9.199999999999999</v>
@@ -1261,43 +1261,43 @@
         <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF3" t="n">
         <v>4.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BJ3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK3" t="n">
         <v>4</v>
       </c>
       <c r="BL3" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="BM3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BN3" t="n">
         <v>4.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BP3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BQ3" t="n">
         <v>3.6</v>
@@ -1306,7 +1306,7 @@
         <v>27</v>
       </c>
       <c r="BS3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BT3" t="n">
         <v>14.5</v>
@@ -1315,26 +1315,26 @@
         <v>4.1</v>
       </c>
       <c r="BV3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BX3" t="n">
         <v>85</v>
       </c>
       <c r="BY3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BZ3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="CA3" t="n">
         <v>4.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -1368,28 +1368,28 @@
         <v>2.08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H4" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
         <v>4.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O4" t="n">
         <v>1.28</v>
@@ -1407,7 +1407,7 @@
         <v>2.82</v>
       </c>
       <c r="T4" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="U4" t="n">
         <v>2.12</v>
@@ -1416,7 +1416,7 @@
         <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -1619,25 +1619,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>13.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="I5" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="J5" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="K5" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M5" t="n">
         <v>1.04</v>
@@ -1646,28 +1646,28 @@
         <v>4.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R5" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
         <v>2.64</v>
       </c>
       <c r="T5" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V5" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="W5" t="n">
         <v>1.08</v>
@@ -1697,7 +1697,7 @@
         <v>15.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AG5" t="n">
         <v>950</v>
@@ -1709,25 +1709,25 @@
         <v>40</v>
       </c>
       <c r="AJ5" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AK5" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AL5" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AM5" t="n">
         <v>190</v>
       </c>
       <c r="AN5" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AO5" t="n">
         <v>6.6</v>
       </c>
       <c r="AP5" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>6.6</v>
@@ -1736,16 +1736,16 @@
         <v>6.2</v>
       </c>
       <c r="AS5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV5" t="n">
         <v>8</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>7.8</v>
       </c>
       <c r="AW5" t="n">
         <v>11</v>
@@ -1754,70 +1754,70 @@
         <v>7.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AZ5" t="n">
         <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC5" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>7.6</v>
       </c>
       <c r="BD5" t="n">
         <v>7.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF5" t="n">
         <v>7.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="BH5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>200</v>
+      </c>
+      <c r="BM5" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>190</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>4.6</v>
       </c>
       <c r="BN5" t="n">
         <v>16.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BP5" t="n">
+        <v>120</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BR5" t="n">
         <v>110</v>
       </c>
-      <c r="BQ5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>100</v>
-      </c>
       <c r="BS5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BU5" t="n">
         <v>3</v>
@@ -1826,13 +1826,13 @@
         <v>9.4</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="BX5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -1873,67 +1873,67 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="G6" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="H6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="I6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J6" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="R6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S6" t="n">
         <v>2.52</v>
       </c>
       <c r="T6" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="U6" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="X6" t="n">
         <v>30</v>
       </c>
       <c r="Y6" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="Z6" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
@@ -1942,34 +1942,34 @@
         <v>9.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="AE6" t="n">
-        <v>420</v>
+        <v>470</v>
       </c>
       <c r="AF6" t="n">
         <v>8</v>
       </c>
       <c r="AG6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AI6" t="n">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="AJ6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AK6" t="n">
         <v>15.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
         <v>310</v>
@@ -1981,64 +1981,64 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AQ6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS6" t="n">
         <v>7.8</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="AT6" t="n">
         <v>6.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AW6" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AZ6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA6" t="n">
         <v>7.6</v>
       </c>
-      <c r="BA6" t="n">
-        <v>9</v>
-      </c>
       <c r="BB6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC6" t="n">
         <v>11</v>
       </c>
       <c r="BD6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG6" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="BH6" t="n">
         <v>5.1</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ6" t="n">
         <v>17.5</v>
@@ -2062,7 +2062,7 @@
         <v>7.8</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BR6" t="n">
         <v>32</v>
@@ -2071,19 +2071,19 @@
         <v>4.1</v>
       </c>
       <c r="BT6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BV6" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BX6" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="BY6" t="n">
         <v>4.6</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -2384,109 +2384,109 @@
         <v>1.95</v>
       </c>
       <c r="G8" t="n">
-        <v>990</v>
+        <v>2.3</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="I8" t="n">
-        <v>990</v>
+        <v>4.9</v>
       </c>
       <c r="J8" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="K8" t="n">
-        <v>500</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
         <v>1.28</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.27</v>
+        <v>1.76</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>1.27</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>1.99</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP8" t="n">
         <v>1.01</v>
@@ -2543,55 +2543,55 @@
         <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK8" t="n">
         <v>1.04</v>
       </c>
       <c r="BL8" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM8" t="n">
         <v>1.04</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO8" t="n">
         <v>1.04</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ8" t="n">
         <v>1.04</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS8" t="n">
         <v>1.04</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU8" t="n">
         <v>1.04</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW8" t="n">
         <v>1.04</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY8" t="n">
         <v>1.04</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -2635,25 +2635,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G9" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="H9" t="n">
         <v>5.8</v>
       </c>
       <c r="I9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J9" t="n">
         <v>3.95</v>
       </c>
       <c r="K9" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
@@ -2665,10 +2665,10 @@
         <v>1.28</v>
       </c>
       <c r="P9" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R9" t="n">
         <v>1.45</v>
@@ -2686,7 +2686,7 @@
         <v>1.16</v>
       </c>
       <c r="W9" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="X9" t="n">
         <v>970</v>
@@ -2695,7 +2695,7 @@
         <v>950</v>
       </c>
       <c r="Z9" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
@@ -2722,7 +2722,7 @@
         <v>950</v>
       </c>
       <c r="AI9" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AJ9" t="n">
         <v>970</v>
@@ -2743,61 +2743,61 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA9" t="n">
         <v>3</v>
       </c>
-      <c r="AR9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>1.75</v>
-      </c>
       <c r="BB9" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="BH9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI9" t="n">
         <v>3</v>
@@ -2818,7 +2818,7 @@
         <v>4.7</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP9" t="n">
         <v>12</v>
@@ -2845,20 +2845,20 @@
         <v>1.04</v>
       </c>
       <c r="BX9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BY9" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="CA9" t="n">
         <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -3152,43 +3152,43 @@
         <v>3.3</v>
       </c>
       <c r="I11" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M11" t="n">
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="T11" t="n">
         <v>1.81</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
         <v>1.35</v>
@@ -3197,10 +3197,10 @@
         <v>1.71</v>
       </c>
       <c r="X11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z11" t="n">
         <v>29</v>
@@ -3209,7 +3209,7 @@
         <v>80</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC11" t="n">
         <v>8</v>
@@ -3221,34 +3221,34 @@
         <v>55</v>
       </c>
       <c r="AF11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG11" t="n">
         <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
         <v>65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK11" t="n">
         <v>32</v>
       </c>
       <c r="AL11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM11" t="n">
         <v>130</v>
       </c>
       <c r="AN11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP11" t="n">
         <v>10.5</v>
@@ -3260,7 +3260,7 @@
         <v>20</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AT11" t="n">
         <v>7.8</v>
@@ -3272,7 +3272,7 @@
         <v>12.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AX11" t="n">
         <v>12.5</v>
@@ -3284,89 +3284,89 @@
         <v>16</v>
       </c>
       <c r="BA11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>150</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU11" t="n">
         <v>5.2</v>
       </c>
-      <c r="BB11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC11" t="n">
+      <c r="BV11" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW11" t="n">
         <v>4.8</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BX11" t="n">
+        <v>48</v>
+      </c>
+      <c r="BY11" t="n">
         <v>5.1</v>
       </c>
-      <c r="BE11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>24</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>44</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>9</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>38</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>1.82</v>
-      </c>
       <c r="BZ11" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.74</v>
+        <v>4.8</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -3397,230 +3397,230 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="G12" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="H12" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="I12" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="J12" t="n">
         <v>3.15</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M12" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P12" t="n">
         <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
         <v>3.75</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="U12" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W12" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV12" t="n">
         <v>11</v>
       </c>
-      <c r="AC12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE12" t="n">
+      <c r="AW12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>170</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>27</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>46</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>29</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>46</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BZ12" t="n">
         <v>40</v>
       </c>
-      <c r="AF12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA12" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H13" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I13" t="n">
         <v>2.4</v>
@@ -3666,16 +3666,16 @@
         <v>3.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O13" t="n">
         <v>1.3</v>
@@ -3687,16 +3687,16 @@
         <v>1.9</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="U13" t="n">
-        <v>1.98</v>
+        <v>2.22</v>
       </c>
       <c r="V13" t="n">
         <v>1.71</v>
@@ -3750,7 +3750,7 @@
         <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN13" t="n">
         <v>32</v>
@@ -3759,7 +3759,7 @@
         <v>22</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ13" t="n">
         <v>10</v>
@@ -3780,7 +3780,7 @@
         <v>10</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX13" t="n">
         <v>5.1</v>
@@ -3792,7 +3792,7 @@
         <v>4.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB13" t="n">
         <v>5.7</v>
@@ -3816,7 +3816,7 @@
         <v>4.1</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BJ13" t="n">
         <v>11.5</v>
@@ -3852,7 +3852,7 @@
         <v>6.4</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BV13" t="n">
         <v>21</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -3908,13 +3908,13 @@
         <v>1.87</v>
       </c>
       <c r="G14" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J14" t="n">
         <v>3.8</v>
@@ -3932,37 +3932,37 @@
         <v>5.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
         <v>1.64</v>
       </c>
       <c r="R14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S14" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U14" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X14" t="n">
         <v>26</v>
       </c>
       <c r="Y14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z14" t="n">
         <v>36</v>
@@ -4019,10 +4019,10 @@
         <v>18.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>25</v>
+        <v>7.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT14" t="n">
         <v>9.6</v>
@@ -4034,7 +4034,7 @@
         <v>13</v>
       </c>
       <c r="AW14" t="n">
-        <v>32</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX14" t="n">
         <v>11</v>
@@ -4046,7 +4046,7 @@
         <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>32</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB14" t="n">
         <v>19</v>
@@ -4058,16 +4058,16 @@
         <v>21</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BF14" t="n">
         <v>7.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>25</v>
+        <v>7.8</v>
       </c>
       <c r="BH14" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BI14" t="n">
         <v>3.45</v>
@@ -4076,13 +4076,13 @@
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BL14" t="n">
         <v>95</v>
       </c>
       <c r="BM14" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BN14" t="n">
         <v>5.7</v>
@@ -4094,13 +4094,13 @@
         <v>14.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BR14" t="n">
         <v>26</v>
       </c>
       <c r="BS14" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BT14" t="n">
         <v>8.800000000000001</v>
@@ -4112,23 +4112,23 @@
         <v>34</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BX14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY14" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BZ14" t="n">
         <v>18</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I15" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="J15" t="n">
         <v>2.8</v>
       </c>
       <c r="K15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -4413,166 +4413,166 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.98</v>
+        <v>1.04</v>
       </c>
       <c r="G16" t="n">
-        <v>2.48</v>
+        <v>990</v>
       </c>
       <c r="H16" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>990</v>
       </c>
       <c r="J16" t="n">
-        <v>2.96</v>
+        <v>1.03</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4</v>
+        <v>500</v>
       </c>
       <c r="L16" t="n">
         <v>1.35</v>
       </c>
       <c r="M16" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="O16" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P16" t="n">
-        <v>1.79</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.96</v>
+        <v>1.32</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>3.15</v>
+        <v>1.32</v>
       </c>
       <c r="T16" t="n">
-        <v>1.77</v>
+        <v>1.11</v>
       </c>
       <c r="U16" t="n">
-        <v>1.98</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.76</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="n">
         <v>3.8</v>
@@ -4593,16 +4593,16 @@
         <v>4.7</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BO16" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BP16" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BR16" t="n">
         <v>38</v>
@@ -4611,13 +4611,13 @@
         <v>4.3</v>
       </c>
       <c r="BT16" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BV16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW16" t="n">
         <v>4.3</v>
@@ -4626,7 +4626,7 @@
         <v>55</v>
       </c>
       <c r="BY16" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -4939,34 +4939,34 @@
         <v>3.45</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P18" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R18" t="n">
         <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T18" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V18" t="n">
         <v>1.62</v>
@@ -4978,13 +4978,13 @@
         <v>14.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z18" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AA18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB18" t="n">
         <v>11.5</v>
@@ -4996,16 +4996,16 @@
         <v>12</v>
       </c>
       <c r="AE18" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AF18" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG18" t="n">
         <v>13.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AI18" t="n">
         <v>44</v>
@@ -5014,31 +5014,31 @@
         <v>55</v>
       </c>
       <c r="AK18" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AL18" t="n">
         <v>50</v>
       </c>
       <c r="AM18" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN18" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="AO18" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AP18" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR18" t="n">
         <v>14</v>
       </c>
       <c r="AS18" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AT18" t="n">
         <v>10</v>
@@ -5050,101 +5050,101 @@
         <v>10.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>8.6</v>
+        <v>19</v>
       </c>
       <c r="AX18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY18" t="n">
         <v>12</v>
       </c>
       <c r="AZ18" t="n">
-        <v>7.4</v>
+        <v>16.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.6</v>
+        <v>27</v>
       </c>
       <c r="BB18" t="n">
         <v>44</v>
       </c>
       <c r="BC18" t="n">
-        <v>9.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="BD18" t="n">
-        <v>9.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BE18" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="BF18" t="n">
-        <v>9.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BG18" t="n">
         <v>20</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.76</v>
+        <v>2.54</v>
       </c>
       <c r="BJ18" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.57</v>
+        <v>3.5</v>
       </c>
       <c r="BL18" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.76</v>
+        <v>4.8</v>
       </c>
       <c r="BN18" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="BO18" t="n">
         <v>4.6</v>
       </c>
       <c r="BP18" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.69</v>
+        <v>4.2</v>
       </c>
       <c r="BR18" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.71</v>
+        <v>4.4</v>
       </c>
       <c r="BT18" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU18" t="n">
         <v>4.1</v>
       </c>
       <c r="BV18" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.67</v>
+        <v>4.1</v>
       </c>
       <c r="BX18" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="BZ18" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
         <v>1.12</v>
       </c>
       <c r="H19" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
         <v>4.8</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M21" t="n">
         <v>1.04</v>
@@ -5713,7 +5713,7 @@
         <v>1.19</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q21" t="n">
         <v>1.57</v>
@@ -5785,10 +5785,10 @@
         <v>60</v>
       </c>
       <c r="AN21" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO21" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AP21" t="n">
         <v>20</v>
@@ -5812,7 +5812,7 @@
         <v>11</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX21" t="n">
         <v>17</v>
@@ -5824,19 +5824,19 @@
         <v>12.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC21" t="n">
         <v>20</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE21" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF21" t="n">
         <v>10.5</v>
@@ -5845,68 +5845,68 @@
         <v>12</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.92</v>
+        <v>3.35</v>
       </c>
       <c r="BJ21" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="BL21" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.93</v>
+        <v>4.4</v>
       </c>
       <c r="BN21" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="BO21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>23</v>
+      </c>
+      <c r="BW21" t="n">
         <v>3.85</v>
       </c>
-      <c r="BP21" t="n">
-        <v>25</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>28</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BX21" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.83</v>
+        <v>4</v>
       </c>
       <c r="BZ21" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.78</v>
+        <v>3.75</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="G24" t="n">
         <v>1.51</v>
@@ -6454,19 +6454,19 @@
         <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="J24" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="K24" t="n">
         <v>1000</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N24" t="n">
         <v>2.22</v>
@@ -6478,13 +6478,13 @@
         <v>2.22</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="R24" t="n">
         <v>1.43</v>
       </c>
       <c r="S24" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="T24" t="n">
         <v>1.11</v>
@@ -6493,7 +6493,7 @@
         <v>1.11</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W24" t="n">
         <v>2.96</v>
@@ -6607,68 +6607,68 @@
         <v>1.01</v>
       </c>
       <c r="BH24" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.97</v>
+        <v>3.5</v>
       </c>
       <c r="BJ24" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.74</v>
+        <v>3.9</v>
       </c>
       <c r="BL24" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.97</v>
+        <v>5.5</v>
       </c>
       <c r="BN24" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BO24" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="BP24" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.68</v>
+        <v>3.6</v>
       </c>
       <c r="BR24" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.85</v>
+        <v>4.6</v>
       </c>
       <c r="BT24" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.76</v>
+        <v>4</v>
       </c>
       <c r="BV24" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.97</v>
+        <v>5.3</v>
       </c>
       <c r="BX24" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.97</v>
+        <v>5.3</v>
       </c>
       <c r="BZ24" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.77</v>
+        <v>4</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -6705,7 +6705,7 @@
         <v>4.9</v>
       </c>
       <c r="H25" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="I25" t="n">
         <v>1.92</v>
@@ -6717,25 +6717,25 @@
         <v>4.6</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M25" t="n">
         <v>1.04</v>
       </c>
       <c r="N25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S25" t="n">
         <v>2.56</v>
@@ -6744,7 +6744,7 @@
         <v>1.64</v>
       </c>
       <c r="U25" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V25" t="n">
         <v>2.06</v>
@@ -6756,7 +6756,7 @@
         <v>950</v>
       </c>
       <c r="Y25" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z25" t="n">
         <v>16</v>
@@ -6774,7 +6774,7 @@
         <v>13</v>
       </c>
       <c r="AE25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF25" t="n">
         <v>44</v>
@@ -6798,131 +6798,131 @@
         <v>60</v>
       </c>
       <c r="AM25" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN25" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP25" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AQ25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU25" t="n">
         <v>3.3</v>
       </c>
-      <c r="AR25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.15</v>
-      </c>
       <c r="AV25" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AW25" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AX25" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AY25" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AZ25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>110</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>42</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>46</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BU25" t="n">
         <v>3.55</v>
       </c>
-      <c r="BA25" t="n">
+      <c r="BV25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>26</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="CA25" t="n">
         <v>3.75</v>
       </c>
-      <c r="BB25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA25" t="n">
-        <v>1.04</v>
-      </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -6971,13 +6971,13 @@
         <v>5.3</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M26" t="n">
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O26" t="n">
         <v>1.15</v>
@@ -6998,7 +6998,7 @@
         <v>1.51</v>
       </c>
       <c r="U26" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="V26" t="n">
         <v>1.31</v>
@@ -7070,16 +7070,16 @@
         <v>1.39</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.64</v>
+        <v>3.9</v>
       </c>
       <c r="AW26" t="n">
         <v>1.4</v>
@@ -7088,13 +7088,13 @@
         <v>1.96</v>
       </c>
       <c r="AY26" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.88</v>
+        <v>4.4</v>
       </c>
       <c r="BB26" t="n">
         <v>1.53</v>
@@ -7115,68 +7115,68 @@
         <v>18</v>
       </c>
       <c r="BH26" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BI26" t="n">
-        <v>2.12</v>
+        <v>3.9</v>
       </c>
       <c r="BJ26" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.79</v>
+        <v>3.55</v>
       </c>
       <c r="BL26" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BM26" t="n">
-        <v>2.12</v>
+        <v>5.2</v>
       </c>
       <c r="BN26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BP26" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.89</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR26" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.97</v>
+        <v>4.4</v>
       </c>
       <c r="BT26" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BU26" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BV26" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BW26" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="BX26" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BY26" t="n">
-        <v>2.02</v>
+        <v>4.7</v>
       </c>
       <c r="BZ26" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.89</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
         <v>7.6</v>
       </c>
       <c r="G27" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="H27" t="n">
         <v>1.41</v>
@@ -7225,7 +7225,7 @@
         <v>6.2</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M27" t="n">
         <v>1.02</v>
@@ -7252,7 +7252,7 @@
         <v>1.66</v>
       </c>
       <c r="U27" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V27" t="n">
         <v>3.2</v>
@@ -7261,7 +7261,7 @@
         <v>1.13</v>
       </c>
       <c r="X27" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Y27" t="n">
         <v>16</v>
@@ -7309,7 +7309,7 @@
         <v>85</v>
       </c>
       <c r="AN27" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO27" t="n">
         <v>4.4</v>
@@ -7327,7 +7327,7 @@
         <v>12</v>
       </c>
       <c r="AT27" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU27" t="n">
         <v>10.5</v>
@@ -7339,28 +7339,28 @@
         <v>12</v>
       </c>
       <c r="AX27" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY27" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="AZ27" t="n">
         <v>16</v>
       </c>
       <c r="BA27" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BB27" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC27" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD27" t="n">
         <v>7.8</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF27" t="n">
         <v>7.8</v>
@@ -7369,68 +7369,68 @@
         <v>3.95</v>
       </c>
       <c r="BH27" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.04</v>
+        <v>4.1</v>
       </c>
       <c r="BJ27" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.78</v>
+        <v>7.6</v>
       </c>
       <c r="BL27" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM27" t="n">
-        <v>2.04</v>
+        <v>5.6</v>
       </c>
       <c r="BN27" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="BO27" t="n">
-        <v>1.81</v>
+        <v>8.6</v>
       </c>
       <c r="BP27" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BQ27" t="n">
-        <v>2.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR27" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS27" t="n">
-        <v>2.04</v>
+        <v>5.4</v>
       </c>
       <c r="BT27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BU27" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="BV27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>21</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BZ27" t="n">
         <v>11</v>
       </c>
-      <c r="BW27" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BX27" t="n">
-        <v>25</v>
-      </c>
-      <c r="BY27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BZ27" t="n">
-        <v>13</v>
-      </c>
       <c r="CA27" t="n">
-        <v>1.77</v>
+        <v>7.4</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -7479,10 +7479,10 @@
         <v>4.3</v>
       </c>
       <c r="L28" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="M28" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N28" t="n">
         <v>3.7</v>
@@ -7491,22 +7491,22 @@
         <v>1.32</v>
       </c>
       <c r="P28" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="Q28" t="n">
         <v>1.82</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
         <v>3.4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="U28" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="V28" t="n">
         <v>2.08</v>
@@ -7518,7 +7518,7 @@
         <v>18.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="Z28" t="n">
         <v>13.5</v>
@@ -7527,10 +7527,10 @@
         <v>24</v>
       </c>
       <c r="AB28" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AD28" t="n">
         <v>12.5</v>
@@ -7545,10 +7545,10 @@
         <v>23</v>
       </c>
       <c r="AH28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI28" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ28" t="n">
         <v>140</v>
@@ -7557,19 +7557,19 @@
         <v>80</v>
       </c>
       <c r="AL28" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM28" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN28" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AO28" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ28" t="n">
         <v>7.4</v>
@@ -7593,7 +7593,7 @@
         <v>16.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AY28" t="n">
         <v>16</v>
@@ -7602,22 +7602,22 @@
         <v>17.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BC28" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BG28" t="n">
         <v>10.5</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G29" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H29" t="n">
         <v>3.05</v>
@@ -7733,16 +7733,16 @@
         <v>4.2</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N29" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P29" t="n">
         <v>2.36</v>
@@ -7766,7 +7766,7 @@
         <v>1.43</v>
       </c>
       <c r="W29" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X29" t="n">
         <v>950</v>
@@ -7778,10 +7778,10 @@
         <v>25</v>
       </c>
       <c r="AA29" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB29" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC29" t="n">
         <v>9.6</v>
@@ -7820,7 +7820,7 @@
         <v>13</v>
       </c>
       <c r="AO29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP29" t="n">
         <v>7.4</v>
@@ -7832,7 +7832,7 @@
         <v>21</v>
       </c>
       <c r="AS29" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT29" t="n">
         <v>12</v>
@@ -7862,13 +7862,13 @@
         <v>8</v>
       </c>
       <c r="BC29" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD29" t="n">
         <v>8</v>
       </c>
       <c r="BE29" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF29" t="n">
         <v>9.199999999999999</v>
@@ -7877,68 +7877,68 @@
         <v>7.4</v>
       </c>
       <c r="BH29" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI29" t="n">
-        <v>1.92</v>
+        <v>3.25</v>
       </c>
       <c r="BJ29" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK29" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="BL29" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM29" t="n">
-        <v>1.93</v>
+        <v>4.4</v>
       </c>
       <c r="BN29" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO29" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BP29" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="BQ29" t="n">
-        <v>1.77</v>
+        <v>3.7</v>
       </c>
       <c r="BR29" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BS29" t="n">
-        <v>1.82</v>
+        <v>4</v>
       </c>
       <c r="BT29" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BU29" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BV29" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BW29" t="n">
-        <v>1.82</v>
+        <v>4</v>
       </c>
       <c r="BX29" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BY29" t="n">
-        <v>1.85</v>
+        <v>4.1</v>
       </c>
       <c r="BZ29" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="CA29" t="n">
-        <v>1.79</v>
+        <v>3.8</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -8734,43 +8734,43 @@
         <v>2.04</v>
       </c>
       <c r="G33" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H33" t="n">
         <v>3.75</v>
       </c>
       <c r="I33" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J33" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="K33" t="n">
         <v>4.2</v>
       </c>
       <c r="L33" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="M33" t="n">
         <v>1.04</v>
       </c>
       <c r="N33" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O33" t="n">
         <v>1.2</v>
       </c>
       <c r="P33" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q33" t="n">
         <v>1.64</v>
       </c>
       <c r="R33" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S33" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T33" t="n">
         <v>1.58</v>
@@ -8779,10 +8779,10 @@
         <v>2.52</v>
       </c>
       <c r="V33" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W33" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="X33" t="n">
         <v>24</v>
@@ -8809,7 +8809,7 @@
         <v>38</v>
       </c>
       <c r="AF33" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG33" t="n">
         <v>11</v>
@@ -8833,13 +8833,13 @@
         <v>65</v>
       </c>
       <c r="AN33" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AO33" t="n">
         <v>28</v>
       </c>
       <c r="AP33" t="n">
-        <v>20</v>
+        <v>9.6</v>
       </c>
       <c r="AQ33" t="n">
         <v>18</v>
@@ -8893,68 +8893,68 @@
         <v>24</v>
       </c>
       <c r="BH33" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BI33" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BJ33" t="n">
         <v>10.5</v>
       </c>
       <c r="BK33" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="BL33" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BM33" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BN33" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BO33" t="n">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="BP33" t="n">
         <v>16</v>
       </c>
       <c r="BQ33" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BR33" t="n">
         <v>27</v>
       </c>
       <c r="BS33" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="BT33" t="n">
         <v>9</v>
       </c>
       <c r="BU33" t="n">
-        <v>3.35</v>
+        <v>5.6</v>
       </c>
       <c r="BV33" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW33" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BX33" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY33" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BZ33" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="CA33" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -8985,40 +8985,40 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G34" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="H34" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="I34" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="J34" t="n">
         <v>3.45</v>
       </c>
       <c r="K34" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N34" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O34" t="n">
         <v>1.5</v>
       </c>
       <c r="P34" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="R34" t="n">
         <v>1.21</v>
@@ -9027,13 +9027,13 @@
         <v>5</v>
       </c>
       <c r="T34" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U34" t="n">
         <v>1.73</v>
       </c>
       <c r="V34" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="W34" t="n">
         <v>1.23</v>
@@ -9045,7 +9045,7 @@
         <v>7.8</v>
       </c>
       <c r="Z34" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA34" t="n">
         <v>27</v>
@@ -9060,7 +9060,7 @@
         <v>13</v>
       </c>
       <c r="AE34" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF34" t="n">
         <v>44</v>
@@ -9090,7 +9090,7 @@
         <v>160</v>
       </c>
       <c r="AO34" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP34" t="n">
         <v>9</v>
@@ -9117,34 +9117,34 @@
         <v>18.5</v>
       </c>
       <c r="AX34" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AY34" t="n">
         <v>17.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB34" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BC34" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF34" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG34" t="n">
-        <v>16</v>
+        <v>4.3</v>
       </c>
       <c r="BH34" t="n">
         <v>1000</v>
@@ -9165,7 +9165,7 @@
         <v>1.64</v>
       </c>
       <c r="BN34" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BO34" t="n">
         <v>1.45</v>
@@ -9183,7 +9183,7 @@
         <v>1.64</v>
       </c>
       <c r="BT34" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU34" t="n">
         <v>3.35</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -9257,34 +9257,34 @@
         <v>4</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M35" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N35" t="n">
-        <v>1.74</v>
+        <v>3.05</v>
       </c>
       <c r="O35" t="n">
         <v>1.39</v>
       </c>
       <c r="P35" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="Q35" t="n">
         <v>2.14</v>
       </c>
       <c r="R35" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S35" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T35" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="U35" t="n">
-        <v>1.11</v>
+        <v>1.82</v>
       </c>
       <c r="V35" t="n">
         <v>1.19</v>
@@ -9293,176 +9293,176 @@
         <v>2.16</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z35" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA35" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB35" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC35" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD35" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE35" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF35" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG35" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI35" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK35" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL35" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM35" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN35" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO35" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH35" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI35" t="n">
-        <v>1.69</v>
+        <v>2.52</v>
       </c>
       <c r="BJ35" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BK35" t="n">
-        <v>1.53</v>
+        <v>4</v>
       </c>
       <c r="BL35" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="BM35" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="BN35" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="BO35" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="BP35" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BQ35" t="n">
-        <v>1.55</v>
+        <v>4.1</v>
       </c>
       <c r="BR35" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="BS35" t="n">
-        <v>1.64</v>
+        <v>5</v>
       </c>
       <c r="BT35" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BU35" t="n">
-        <v>1.5</v>
+        <v>3.75</v>
       </c>
       <c r="BV35" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW35" t="n">
-        <v>1.7</v>
+        <v>5.2</v>
       </c>
       <c r="BX35" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY35" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="BZ35" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="CA35" t="n">
-        <v>1.63</v>
+        <v>4.9</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>
@@ -9493,19 +9493,19 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G36" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J36" t="n">
         <v>2.96</v>
-      </c>
-      <c r="H36" t="n">
-        <v>3</v>
-      </c>
-      <c r="I36" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2.9</v>
       </c>
       <c r="K36" t="n">
         <v>3.25</v>
@@ -9526,7 +9526,7 @@
         <v>1.52</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="R36" t="n">
         <v>1.18</v>
@@ -9541,10 +9541,10 @@
         <v>1.76</v>
       </c>
       <c r="V36" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W36" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X36" t="n">
         <v>9</v>
@@ -9553,7 +9553,7 @@
         <v>9.4</v>
       </c>
       <c r="Z36" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA36" t="n">
         <v>65</v>
@@ -9580,7 +9580,7 @@
         <v>24</v>
       </c>
       <c r="AI36" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ36" t="n">
         <v>55</v>
@@ -9601,7 +9601,7 @@
         <v>65</v>
       </c>
       <c r="AP36" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ36" t="n">
         <v>7.6</v>
@@ -9610,7 +9610,7 @@
         <v>16.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT36" t="n">
         <v>7</v>
@@ -9622,7 +9622,7 @@
         <v>12</v>
       </c>
       <c r="AW36" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX36" t="n">
         <v>14</v>
@@ -9634,22 +9634,22 @@
         <v>19</v>
       </c>
       <c r="BA36" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB36" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC36" t="n">
         <v>7.8</v>
       </c>
-      <c r="BC36" t="n">
-        <v>34</v>
-      </c>
       <c r="BD36" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE36" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF36" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG36" t="n">
         <v>44</v>
@@ -9664,59 +9664,59 @@
         <v>11.5</v>
       </c>
       <c r="BK36" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BL36" t="n">
         <v>230</v>
       </c>
       <c r="BM36" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BN36" t="n">
         <v>5.8</v>
       </c>
       <c r="BO36" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BP36" t="n">
         <v>27</v>
       </c>
       <c r="BQ36" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BR36" t="n">
         <v>55</v>
       </c>
       <c r="BS36" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BT36" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BU36" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BV36" t="n">
         <v>34</v>
       </c>
       <c r="BW36" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BX36" t="n">
         <v>60</v>
       </c>
       <c r="BY36" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ36" t="n">
         <v>60</v>
       </c>
       <c r="CA36" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-20 00:21:22</t>
+          <t>2026-05-20 02:34:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M2" t="n">
         <v>1.05</v>
       </c>
-      <c r="G2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="I2" t="n">
-        <v>990</v>
-      </c>
-      <c r="J2" t="n">
+      <c r="N2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="X2" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>180</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>400</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>300</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>340</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI2" t="n">
         <v>2.96</v>
       </c>
-      <c r="K2" t="n">
-        <v>500</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
         <v>6.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
@@ -1153,10 +1153,10 @@
         <v>2.68</v>
       </c>
       <c r="T3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.85</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.78</v>
       </c>
       <c r="V3" t="n">
         <v>1.09</v>
@@ -1222,10 +1222,10 @@
         <v>16</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AS3" t="n">
         <v>5.1</v>
@@ -1240,7 +1240,7 @@
         <v>4.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AX3" t="n">
         <v>6.8</v>
@@ -1264,7 +1264,7 @@
         <v>4.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF3" t="n">
         <v>4.7</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -1368,16 +1368,16 @@
         <v>2.08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I4" t="n">
         <v>4.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
         <v>4.9</v>
@@ -1389,10 +1389,10 @@
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="P4" t="n">
         <v>2.04</v>
@@ -1401,7 +1401,7 @@
         <v>1.87</v>
       </c>
       <c r="R4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
         <v>2.82</v>
@@ -1416,7 +1416,7 @@
         <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1494,7 +1494,7 @@
         <v>1.93</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.6</v>
+        <v>1.87</v>
       </c>
       <c r="AX4" t="n">
         <v>1.94</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="H5" t="n">
         <v>1.34</v>
@@ -1631,7 +1631,7 @@
         <v>1.39</v>
       </c>
       <c r="J5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K5" t="n">
         <v>6</v>
@@ -1670,7 +1670,7 @@
         <v>3.55</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
         <v>22</v>
@@ -1739,7 +1739,7 @@
         <v>4.7</v>
       </c>
       <c r="AT5" t="n">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="AU5" t="n">
         <v>9.4</v>
@@ -1757,7 +1757,7 @@
         <v>6.8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>20</v>
+        <v>6.4</v>
       </c>
       <c r="BA5" t="n">
         <v>6.8</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="G6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="H6" t="n">
         <v>17</v>
@@ -1885,10 +1885,10 @@
         <v>24</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.24</v>
@@ -1909,7 +1909,7 @@
         <v>1.58</v>
       </c>
       <c r="R6" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="S6" t="n">
         <v>2.52</v>
@@ -1924,7 +1924,7 @@
         <v>1.04</v>
       </c>
       <c r="W6" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="X6" t="n">
         <v>30</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
         <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
@@ -2423,10 +2423,10 @@
         <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="U8" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="V8" t="n">
         <v>1.25</v>
@@ -2489,58 +2489,58 @@
         <v>60</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH8" t="n">
         <v>3.95</v>
@@ -2552,49 +2552,49 @@
         <v>11</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BL8" t="n">
         <v>130</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BN8" t="n">
         <v>5.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="BP8" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BR8" t="n">
         <v>32</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BT8" t="n">
         <v>8.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BV8" t="n">
         <v>38</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BX8" t="n">
         <v>48</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -2635,25 +2635,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="G9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H9" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J9" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
@@ -2683,7 +2683,7 @@
         <v>2.06</v>
       </c>
       <c r="V9" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W9" t="n">
         <v>2.52</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -2913,13 +2913,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O10" t="n">
         <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Q10" t="n">
         <v>1.23</v>
@@ -2928,7 +2928,7 @@
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G11" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H11" t="n">
         <v>3.3</v>
@@ -3194,7 +3194,7 @@
         <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X11" t="n">
         <v>14</v>
@@ -3257,7 +3257,7 @@
         <v>10.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AS11" t="n">
         <v>5.8</v>
@@ -3281,7 +3281,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA11" t="n">
         <v>5.7</v>
@@ -3290,7 +3290,7 @@
         <v>5.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.3</v>
+        <v>20</v>
       </c>
       <c r="BD11" t="n">
         <v>5.6</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
         <v>2.94</v>
       </c>
       <c r="H12" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I12" t="n">
         <v>3.05</v>
@@ -3412,7 +3412,7 @@
         <v>3.15</v>
       </c>
       <c r="K12" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="L12" t="n">
         <v>1.38</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G13" t="n">
         <v>3.4</v>
@@ -3666,10 +3666,10 @@
         <v>3.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
@@ -3702,7 +3702,7 @@
         <v>1.71</v>
       </c>
       <c r="W13" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="X13" t="n">
         <v>18.5</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -4007,7 +4007,7 @@
         <v>65</v>
       </c>
       <c r="AN14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO14" t="n">
         <v>40</v>
@@ -4019,10 +4019,10 @@
         <v>18.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AT14" t="n">
         <v>9.6</v>
@@ -4034,7 +4034,7 @@
         <v>13</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AX14" t="n">
         <v>11</v>
@@ -4046,7 +4046,7 @@
         <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BB14" t="n">
         <v>19</v>
@@ -4058,13 +4058,13 @@
         <v>21</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF14" t="n">
         <v>7.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH14" t="n">
         <v>4.4</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -4162,19 +4162,19 @@
         <v>2.32</v>
       </c>
       <c r="G15" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H15" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="I15" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -4413,166 +4413,166 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="G16" t="n">
-        <v>990</v>
+        <v>2.5</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="I16" t="n">
-        <v>990</v>
+        <v>4.7</v>
       </c>
       <c r="J16" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="K16" t="n">
-        <v>500</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
         <v>1.35</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>1.79</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.32</v>
+        <v>1.84</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>1.32</v>
+        <v>3.15</v>
       </c>
       <c r="T16" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="U16" t="n">
-        <v>1.11</v>
+        <v>1.99</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.67</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH16" t="n">
         <v>3.8</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>1.04</v>
       </c>
       <c r="G17" t="n">
-        <v>990</v>
+        <v>1.63</v>
       </c>
       <c r="H17" t="n">
         <v>1.04</v>
@@ -4679,7 +4679,7 @@
         <v>990</v>
       </c>
       <c r="J17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K17" t="n">
         <v>500</v>
@@ -4715,10 +4715,10 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4927,7 @@
         <v>3.15</v>
       </c>
       <c r="H18" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="I18" t="n">
         <v>2.62</v>
@@ -4945,34 +4945,34 @@
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S18" t="n">
         <v>3.95</v>
       </c>
       <c r="T18" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V18" t="n">
         <v>1.62</v>
       </c>
       <c r="W18" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X18" t="n">
         <v>14.5</v>
@@ -4981,7 +4981,7 @@
         <v>10</v>
       </c>
       <c r="Z18" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA18" t="n">
         <v>40</v>
@@ -4990,22 +4990,22 @@
         <v>11.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE18" t="n">
         <v>48</v>
       </c>
       <c r="AF18" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG18" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH18" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI18" t="n">
         <v>44</v>
@@ -5029,10 +5029,10 @@
         <v>30</v>
       </c>
       <c r="AP18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR18" t="n">
         <v>14</v>
@@ -5047,7 +5047,7 @@
         <v>6.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW18" t="n">
         <v>19</v>
@@ -5080,7 +5080,7 @@
         <v>30</v>
       </c>
       <c r="BG18" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BH18" t="n">
         <v>3.65</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -5181,10 +5181,10 @@
         <v>1.12</v>
       </c>
       <c r="H19" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="J19" t="n">
         <v>12</v>
@@ -5193,212 +5193,212 @@
         <v>16.5</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P19" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="Q19" t="n">
         <v>1.27</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BH19" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BI19" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL19" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="BM19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BO19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BP19" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BR19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BS19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT19" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BU19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV19" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX19" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="BY19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CA19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -5432,13 +5432,13 @@
         <v>2.52</v>
       </c>
       <c r="G20" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="H20" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I20" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J20" t="n">
         <v>3.95</v>
@@ -5447,16 +5447,16 @@
         <v>4.5</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P20" t="n">
         <v>2.8</v>
@@ -5465,194 +5465,194 @@
         <v>1.41</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL20" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BM20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BO20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BP20" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BS20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT20" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BU20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BV20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX20" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BY20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="CA20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -5698,10 +5698,10 @@
         <v>3.7</v>
       </c>
       <c r="K21" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M21" t="n">
         <v>1.04</v>
@@ -5710,25 +5710,25 @@
         <v>5.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R21" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S21" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="T21" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U21" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V21" t="n">
         <v>1.53</v>
@@ -5740,7 +5740,7 @@
         <v>25</v>
       </c>
       <c r="Y21" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z21" t="n">
         <v>23</v>
@@ -5749,7 +5749,7 @@
         <v>42</v>
       </c>
       <c r="AB21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AC21" t="n">
         <v>10</v>
@@ -5791,7 +5791,7 @@
         <v>19.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ21" t="n">
         <v>14</v>
@@ -5800,7 +5800,7 @@
         <v>18.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT21" t="n">
         <v>13</v>
@@ -5812,7 +5812,7 @@
         <v>11</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX21" t="n">
         <v>17</v>
@@ -5824,19 +5824,19 @@
         <v>12.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB21" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC21" t="n">
         <v>20</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE21" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF21" t="n">
         <v>10.5</v>
@@ -5845,10 +5845,10 @@
         <v>12</v>
       </c>
       <c r="BH21" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BJ21" t="n">
         <v>10.5</v>
@@ -5857,25 +5857,25 @@
         <v>3.2</v>
       </c>
       <c r="BL21" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BM21" t="n">
         <v>4.4</v>
       </c>
       <c r="BN21" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO21" t="n">
         <v>4.5</v>
       </c>
       <c r="BP21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ21" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BR21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS21" t="n">
         <v>4</v>
@@ -5899,14 +5899,14 @@
         <v>4</v>
       </c>
       <c r="BZ21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5943,7 @@
         <v>17.5</v>
       </c>
       <c r="H22" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="I22" t="n">
         <v>1.28</v>
@@ -5955,212 +5955,212 @@
         <v>8.6</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="P22" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="Q22" t="n">
         <v>1.44</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BI22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL22" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="BM22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN22" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BO22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP22" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="BQ22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR22" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BS22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BU22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BV22" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BW22" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BX22" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BY22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -6445,166 +6445,166 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="G24" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="I24" t="n">
-        <v>18.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J24" t="n">
         <v>5.1</v>
       </c>
       <c r="K24" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="L24" t="n">
         <v>1.25</v>
       </c>
       <c r="M24" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>2.22</v>
+        <v>5.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="R24" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="S24" t="n">
-        <v>1.99</v>
+        <v>2.46</v>
       </c>
       <c r="T24" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="U24" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V24" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="W24" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH24" t="n">
         <v>4.9</v>
@@ -6613,7 +6613,7 @@
         <v>3.5</v>
       </c>
       <c r="BJ24" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK24" t="n">
         <v>3.9</v>
@@ -6625,13 +6625,13 @@
         <v>5.5</v>
       </c>
       <c r="BN24" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP24" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ24" t="n">
         <v>3.6</v>
@@ -6640,22 +6640,22 @@
         <v>25</v>
       </c>
       <c r="BS24" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BT24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BU24" t="n">
         <v>4</v>
       </c>
       <c r="BV24" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BW24" t="n">
         <v>5.3</v>
       </c>
       <c r="BX24" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BY24" t="n">
         <v>5.3</v>
@@ -6664,11 +6664,11 @@
         <v>14</v>
       </c>
       <c r="CA24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -6699,19 +6699,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G25" t="n">
         <v>4.9</v>
       </c>
       <c r="H25" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="I25" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K25" t="n">
         <v>4.6</v>
@@ -6726,7 +6726,7 @@
         <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P25" t="n">
         <v>2.38</v>
@@ -6747,7 +6747,7 @@
         <v>2.12</v>
       </c>
       <c r="V25" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W25" t="n">
         <v>1.26</v>
@@ -6870,7 +6870,7 @@
         <v>11.5</v>
       </c>
       <c r="BK25" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BL25" t="n">
         <v>110</v>
@@ -6891,7 +6891,7 @@
         <v>4.2</v>
       </c>
       <c r="BR25" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BS25" t="n">
         <v>4.2</v>
@@ -6906,13 +6906,13 @@
         <v>13.5</v>
       </c>
       <c r="BW25" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BX25" t="n">
         <v>26</v>
       </c>
       <c r="BY25" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BZ25" t="n">
         <v>18.5</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G26" t="n">
         <v>2.02</v>
@@ -6980,7 +6980,7 @@
         <v>5.5</v>
       </c>
       <c r="O26" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P26" t="n">
         <v>2.78</v>
@@ -7070,7 +7070,7 @@
         <v>1.39</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="AT26" t="n">
         <v>3.9</v>
@@ -7112,7 +7112,7 @@
         <v>5.9</v>
       </c>
       <c r="BG26" t="n">
-        <v>18</v>
+        <v>7.2</v>
       </c>
       <c r="BH26" t="n">
         <v>5.5</v>
@@ -7142,7 +7142,7 @@
         <v>14</v>
       </c>
       <c r="BQ26" t="n">
-        <v>9.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="BR26" t="n">
         <v>23</v>
@@ -7154,7 +7154,7 @@
         <v>9</v>
       </c>
       <c r="BU26" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV26" t="n">
         <v>30</v>
@@ -7172,11 +7172,11 @@
         <v>14.5</v>
       </c>
       <c r="CA26" t="n">
-        <v>9.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
         <v>7.6</v>
       </c>
       <c r="G27" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="H27" t="n">
         <v>1.41</v>
@@ -7252,7 +7252,7 @@
         <v>1.66</v>
       </c>
       <c r="U27" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V27" t="n">
         <v>3.2</v>
@@ -7306,7 +7306,7 @@
         <v>70</v>
       </c>
       <c r="AM27" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AN27" t="n">
         <v>70</v>
@@ -7357,13 +7357,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BD27" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE27" t="n">
         <v>8</v>
       </c>
       <c r="BF27" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG27" t="n">
         <v>3.95</v>
@@ -7375,62 +7375,62 @@
         <v>4.1</v>
       </c>
       <c r="BJ27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>7.6</v>
+        <v>3.7</v>
       </c>
       <c r="BL27" t="n">
         <v>95</v>
       </c>
       <c r="BM27" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BN27" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BO27" t="n">
-        <v>8.6</v>
+        <v>3.85</v>
       </c>
       <c r="BP27" t="n">
         <v>60</v>
       </c>
       <c r="BQ27" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BR27" t="n">
         <v>55</v>
       </c>
       <c r="BS27" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BT27" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BU27" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BV27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BW27" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="BX27" t="n">
         <v>21</v>
       </c>
       <c r="BY27" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BZ27" t="n">
         <v>11</v>
       </c>
       <c r="CA27" t="n">
-        <v>7.4</v>
+        <v>3.65</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -7479,10 +7479,10 @@
         <v>4.3</v>
       </c>
       <c r="L28" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="M28" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
         <v>3.7</v>
@@ -7491,10 +7491,10 @@
         <v>1.32</v>
       </c>
       <c r="P28" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="R28" t="n">
         <v>1.35</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -7733,7 +7733,7 @@
         <v>4.2</v>
       </c>
       <c r="L29" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M29" t="n">
         <v>1.04</v>
@@ -7745,13 +7745,13 @@
         <v>1.21</v>
       </c>
       <c r="P29" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q29" t="n">
         <v>1.62</v>
       </c>
       <c r="R29" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S29" t="n">
         <v>2.56</v>
@@ -7760,7 +7760,7 @@
         <v>1.58</v>
       </c>
       <c r="U29" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V29" t="n">
         <v>1.43</v>
@@ -7871,16 +7871,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BF29" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG29" t="n">
-        <v>7.4</v>
+        <v>15.5</v>
       </c>
       <c r="BH29" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI29" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ29" t="n">
         <v>10.5</v>
@@ -7892,7 +7892,7 @@
         <v>95</v>
       </c>
       <c r="BM29" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BN29" t="n">
         <v>6.6</v>
@@ -7904,41 +7904,41 @@
         <v>18.5</v>
       </c>
       <c r="BQ29" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BR29" t="n">
         <v>29</v>
       </c>
       <c r="BS29" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BT29" t="n">
         <v>8</v>
       </c>
       <c r="BU29" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV29" t="n">
         <v>27</v>
       </c>
       <c r="BW29" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BX29" t="n">
         <v>36</v>
       </c>
       <c r="BY29" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BZ29" t="n">
         <v>21</v>
       </c>
       <c r="CA29" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -7993,22 +7993,22 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O30" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="P30" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="R30" t="n">
         <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T30" t="n">
         <v>1.11</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -8734,22 +8734,22 @@
         <v>2.04</v>
       </c>
       <c r="G33" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H33" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I33" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J33" t="n">
         <v>3.95</v>
       </c>
       <c r="K33" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L33" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="M33" t="n">
         <v>1.04</v>
@@ -8761,7 +8761,7 @@
         <v>1.2</v>
       </c>
       <c r="P33" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q33" t="n">
         <v>1.64</v>
@@ -8776,13 +8776,13 @@
         <v>1.58</v>
       </c>
       <c r="U33" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V33" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W33" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X33" t="n">
         <v>24</v>
@@ -8794,7 +8794,7 @@
         <v>32</v>
       </c>
       <c r="AA33" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB33" t="n">
         <v>13.5</v>
@@ -8806,7 +8806,7 @@
         <v>15.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF33" t="n">
         <v>15</v>
@@ -8827,7 +8827,7 @@
         <v>19</v>
       </c>
       <c r="AL33" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM33" t="n">
         <v>65</v>
@@ -8896,7 +8896,7 @@
         <v>5</v>
       </c>
       <c r="BI33" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ33" t="n">
         <v>10.5</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -8994,16 +8994,16 @@
         <v>1.82</v>
       </c>
       <c r="I34" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="J34" t="n">
         <v>3.45</v>
       </c>
       <c r="K34" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M34" t="n">
         <v>1.1</v>
@@ -9033,7 +9033,7 @@
         <v>1.73</v>
       </c>
       <c r="V34" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W34" t="n">
         <v>1.23</v>
@@ -9147,68 +9147,68 @@
         <v>4.3</v>
       </c>
       <c r="BH34" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI34" t="n">
-        <v>1.64</v>
+        <v>2.3</v>
       </c>
       <c r="BJ34" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BK34" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="BL34" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="BM34" t="n">
-        <v>1.64</v>
+        <v>4.9</v>
       </c>
       <c r="BN34" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BO34" t="n">
-        <v>1.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP34" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BQ34" t="n">
-        <v>1.64</v>
+        <v>4.7</v>
       </c>
       <c r="BR34" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BS34" t="n">
-        <v>1.64</v>
+        <v>4.7</v>
       </c>
       <c r="BT34" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="BU34" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BV34" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BW34" t="n">
-        <v>1.52</v>
+        <v>3.95</v>
       </c>
       <c r="BX34" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BY34" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="BZ34" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="CA34" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -9239,10 +9239,10 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G35" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H35" t="n">
         <v>5.4</v>
@@ -9290,7 +9290,7 @@
         <v>1.19</v>
       </c>
       <c r="W35" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X35" t="n">
         <v>14.5</v>
@@ -9410,59 +9410,59 @@
         <v>13.5</v>
       </c>
       <c r="BK35" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BL35" t="n">
         <v>220</v>
       </c>
       <c r="BM35" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BN35" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BO35" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="BP35" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ35" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="BR35" t="n">
         <v>40</v>
       </c>
       <c r="BS35" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BT35" t="n">
         <v>11</v>
       </c>
       <c r="BU35" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="BV35" t="n">
         <v>70</v>
       </c>
       <c r="BW35" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BX35" t="n">
         <v>80</v>
       </c>
       <c r="BY35" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BZ35" t="n">
         <v>34</v>
       </c>
       <c r="CA35" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="G36" t="n">
         <v>2.98</v>
@@ -9502,7 +9502,7 @@
         <v>2.94</v>
       </c>
       <c r="I36" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J36" t="n">
         <v>2.96</v>
@@ -9523,10 +9523,10 @@
         <v>1.52</v>
       </c>
       <c r="P36" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R36" t="n">
         <v>1.18</v>
@@ -9541,10 +9541,10 @@
         <v>1.76</v>
       </c>
       <c r="V36" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W36" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X36" t="n">
         <v>9</v>
@@ -9661,62 +9661,62 @@
         <v>2.28</v>
       </c>
       <c r="BJ36" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BK36" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BL36" t="n">
         <v>230</v>
       </c>
       <c r="BM36" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="BN36" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BO36" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP36" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BQ36" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BR36" t="n">
         <v>55</v>
       </c>
       <c r="BS36" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="BT36" t="n">
         <v>6.8</v>
       </c>
       <c r="BU36" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV36" t="n">
         <v>34</v>
       </c>
       <c r="BW36" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BX36" t="n">
         <v>60</v>
       </c>
       <c r="BY36" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="BZ36" t="n">
         <v>60</v>
       </c>
       <c r="CA36" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-20 02:34:45</t>
+          <t>2026-05-20 04:48:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
@@ -857,118 +857,118 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>990</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L2" t="n">
         <v>1.29</v>
       </c>
-      <c r="G2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="H2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.36</v>
-      </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>2.96</v>
       </c>
       <c r="O2" t="n">
-        <v>1.28</v>
+        <v>1.04</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>2.44</v>
       </c>
       <c r="T2" t="n">
-        <v>2.34</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.59</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>3.75</v>
+        <v>2.96</v>
       </c>
       <c r="X2" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
         <v>1.01</v>
@@ -977,10 +977,10 @@
         <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
         <v>1.01</v>
@@ -989,22 +989,22 @@
         <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
         <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
         <v>1.01</v>
@@ -1013,74 +1013,74 @@
         <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
         <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.96</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL2" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP2" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BR2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT2" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV2" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="G3" t="n">
         <v>1.47</v>
       </c>
       <c r="H3" t="n">
-        <v>8.6</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>990</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>6.4</v>
+        <v>500</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.22</v>
+        <v>1.03</v>
       </c>
       <c r="P3" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="R3" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>2.68</v>
+        <v>2.36</v>
       </c>
       <c r="T3" t="n">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.85</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
         <v>3.1</v>
       </c>
       <c r="X3" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="G4" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="H4" t="n">
-        <v>1.09</v>
+        <v>2.92</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9</v>
+        <v>500</v>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="P4" t="n">
         <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>2.82</v>
+        <v>2.32</v>
       </c>
       <c r="T4" t="n">
-        <v>1.77</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.94</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.88</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -1619,220 +1619,220 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="G5" t="n">
-        <v>14</v>
+        <v>990</v>
       </c>
       <c r="H5" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="I5" t="n">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="J5" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L5" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.26</v>
+        <v>1.86</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>2.64</v>
+        <v>2.14</v>
       </c>
       <c r="T5" t="n">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.81</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL5" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BN5" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP5" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR5" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BV5" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX5" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -1873,220 +1873,220 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="G6" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="H6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>24</v>
+        <v>990</v>
       </c>
       <c r="J6" t="n">
         <v>6.2</v>
       </c>
       <c r="K6" t="n">
-        <v>7.8</v>
+        <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
         <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="P6" t="n">
-        <v>2.42</v>
+        <v>1.97</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="R6" t="n">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="T6" t="n">
-        <v>2.38</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="X6" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>470</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>2.84</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -2160,13 +2160,13 @@
         <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.51</v>
+        <v>1.05</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -2384,217 +2384,217 @@
         <v>1.95</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3</v>
+        <v>990</v>
       </c>
       <c r="H8" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>990</v>
       </c>
       <c r="J8" t="n">
-        <v>2.78</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>500</v>
       </c>
       <c r="L8" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>1.24</v>
       </c>
       <c r="O8" t="n">
-        <v>1.28</v>
+        <v>1.02</v>
       </c>
       <c r="P8" t="n">
-        <v>1.92</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.76</v>
+        <v>1.02</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>2.7</v>
+        <v>1.02</v>
       </c>
       <c r="T8" t="n">
-        <v>1.71</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>2.06</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.9</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.82</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="G9" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="H9" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K9" t="n">
-        <v>5.2</v>
+        <v>500</v>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="M9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>2.22</v>
       </c>
       <c r="O9" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="P9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W9" t="n">
         <v>2.24</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.52</v>
-      </c>
       <c r="X9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
         <v>1.04</v>
       </c>
       <c r="BL9" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
         <v>1.04</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
         <v>1.04</v>
       </c>
       <c r="BR9" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
         <v>1.04</v>
       </c>
       <c r="BT9" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
         <v>1.04</v>
       </c>
       <c r="BV9" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
         <v>1.04</v>
       </c>
       <c r="BX9" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
         <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -2913,22 +2913,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="O10" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="P10" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.05</v>
+        <v>1.6</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -3143,230 +3143,230 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I11" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J11" t="n">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="K11" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="P11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>1.79</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.81</v>
-      </c>
       <c r="U11" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W11" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="X11" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.7</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -3397,230 +3397,230 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="G12" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="H12" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="I12" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.15</v>
+        <v>1.09</v>
       </c>
       <c r="K12" t="n">
         <v>3.45</v>
       </c>
       <c r="L12" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>3.75</v>
+        <v>2.38</v>
       </c>
       <c r="T12" t="n">
-        <v>1.82</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W12" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X12" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.54</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL12" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN12" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP12" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BR12" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BT12" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV12" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BX12" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>3.2</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="H13" t="n">
         <v>2.34</v>
@@ -3663,218 +3663,218 @@
         <v>2.4</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="K13" t="n">
         <v>3.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="O13" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P13" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q13" t="n">
         <v>1.9</v>
       </c>
       <c r="R13" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>3.25</v>
+        <v>1.05</v>
       </c>
       <c r="T13" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="U13" t="n">
-        <v>2.22</v>
+        <v>1.11</v>
       </c>
       <c r="V13" t="n">
         <v>1.71</v>
       </c>
       <c r="W13" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="X13" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="Y13" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AA13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.7</v>
+        <v>1.06</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10</v>
+        <v>1.12</v>
       </c>
       <c r="AR13" t="n">
-        <v>11.5</v>
+        <v>1.06</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.2</v>
+        <v>1.12</v>
       </c>
       <c r="AT13" t="n">
-        <v>11.5</v>
+        <v>1.12</v>
       </c>
       <c r="AU13" t="n">
-        <v>7</v>
+        <v>1.12</v>
       </c>
       <c r="AV13" t="n">
-        <v>10</v>
+        <v>1.12</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.2</v>
+        <v>1.12</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.1</v>
+        <v>1.12</v>
       </c>
       <c r="AY13" t="n">
-        <v>12</v>
+        <v>1.12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.5</v>
+        <v>1.12</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.4</v>
+        <v>1.12</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.7</v>
+        <v>1.12</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.5</v>
+        <v>1.12</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.6</v>
+        <v>1.12</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.9</v>
+        <v>1.12</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.2</v>
+        <v>1.12</v>
       </c>
       <c r="BG13" t="n">
-        <v>12.5</v>
+        <v>1.12</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.82</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL13" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN13" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BP13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BR13" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT13" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BV13" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX13" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -3905,230 +3905,230 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G14" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="I14" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="K14" t="n">
         <v>4.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="P14" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
         <v>1.64</v>
       </c>
       <c r="R14" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="S14" t="n">
-        <v>2.52</v>
+        <v>2.04</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
         <v>2.46</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="X14" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP14" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV14" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="G15" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="H15" t="n">
         <v>3.85</v>
       </c>
       <c r="I15" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="J15" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="K15" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -4413,220 +4413,220 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5</v>
+        <v>990</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>4.7</v>
+        <v>990</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3</v>
+        <v>500</v>
       </c>
       <c r="L16" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>1.24</v>
       </c>
       <c r="O16" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="P16" t="n">
-        <v>1.79</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.84</v>
+        <v>1.04</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>3.15</v>
+        <v>1.05</v>
       </c>
       <c r="T16" t="n">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="U16" t="n">
-        <v>1.99</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BL16" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="BP16" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BR16" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BT16" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BV16" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BX16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>1.04</v>
       </c>
       <c r="G17" t="n">
-        <v>1.63</v>
+        <v>990</v>
       </c>
       <c r="H17" t="n">
         <v>1.04</v>
@@ -4679,7 +4679,7 @@
         <v>990</v>
       </c>
       <c r="J17" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="K17" t="n">
         <v>500</v>
@@ -4688,25 +4688,25 @@
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O17" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="P17" t="n">
         <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
         <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -4715,10 +4715,10 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -4921,25 +4921,25 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G18" t="n">
         <v>3.15</v>
       </c>
       <c r="H18" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I18" t="n">
         <v>2.62</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K18" t="n">
         <v>3.45</v>
       </c>
       <c r="L18" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
@@ -4948,22 +4948,22 @@
         <v>3.45</v>
       </c>
       <c r="O18" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P18" t="n">
         <v>1.81</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R18" t="n">
         <v>1.31</v>
       </c>
       <c r="S18" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="U18" t="n">
         <v>2.08</v>
@@ -4972,19 +4972,19 @@
         <v>1.62</v>
       </c>
       <c r="W18" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X18" t="n">
         <v>14.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AB18" t="n">
         <v>11.5</v>
@@ -4993,40 +4993,40 @@
         <v>7.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE18" t="n">
         <v>48</v>
       </c>
       <c r="AF18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH18" t="n">
         <v>20</v>
       </c>
-      <c r="AG18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>21</v>
-      </c>
       <c r="AI18" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
         <v>75</v>
       </c>
       <c r="AL18" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
         <v>80</v>
       </c>
       <c r="AO18" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AP18" t="n">
         <v>11</v>
@@ -5035,116 +5035,116 @@
         <v>9.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS18" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AT18" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW18" t="n">
         <v>19</v>
       </c>
       <c r="AX18" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY18" t="n">
         <v>12</v>
       </c>
       <c r="AZ18" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BA18" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB18" t="n">
         <v>27</v>
       </c>
-      <c r="BB18" t="n">
-        <v>44</v>
-      </c>
       <c r="BC18" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BD18" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BE18" t="n">
         <v>40</v>
       </c>
       <c r="BF18" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BG18" t="n">
         <v>17</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.54</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BL18" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="BM18" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BN18" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP18" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR18" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT18" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV18" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BX18" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -5175,64 +5175,64 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="G19" t="n">
         <v>1.12</v>
       </c>
       <c r="H19" t="n">
-        <v>25</v>
+        <v>9.4</v>
       </c>
       <c r="I19" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="K19" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="L19" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>7.4</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="T19" t="n">
         <v>1.11</v>
       </c>
-      <c r="P19" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.22</v>
-      </c>
       <c r="U19" t="n">
-        <v>1.59</v>
+        <v>1.11</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
         <v>1000</v>
@@ -5241,164 +5241,164 @@
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AG19" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.95</v>
+        <v>1.11</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4</v>
+        <v>1.05</v>
       </c>
       <c r="AR19" t="n">
-        <v>3.2</v>
+        <v>1.05</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.2</v>
+        <v>1.05</v>
       </c>
       <c r="AT19" t="n">
-        <v>4.3</v>
+        <v>1.05</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.9</v>
+        <v>1.05</v>
       </c>
       <c r="AV19" t="n">
-        <v>4</v>
+        <v>1.05</v>
       </c>
       <c r="AW19" t="n">
-        <v>3.2</v>
+        <v>1.05</v>
       </c>
       <c r="AX19" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>4.2</v>
+        <v>1.05</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5.4</v>
+        <v>1.05</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.1</v>
+        <v>1.05</v>
       </c>
       <c r="BB19" t="n">
-        <v>3.75</v>
+        <v>1.05</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.2</v>
+        <v>1.05</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.3</v>
+        <v>1.05</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.9</v>
+        <v>1.05</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.16</v>
+        <v>1.05</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.94</v>
+        <v>1.05</v>
       </c>
       <c r="BH19" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL19" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN19" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP19" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR19" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT19" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV19" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX19" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -5429,230 +5429,230 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="G20" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="H20" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="I20" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="K20" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="L20" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
         <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>6.2</v>
+        <v>2.62</v>
       </c>
       <c r="O20" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="P20" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="R20" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="S20" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="T20" t="n">
         <v>1.39</v>
       </c>
       <c r="U20" t="n">
-        <v>2.5</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X20" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL20" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN20" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP20" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR20" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT20" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV20" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX20" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -5686,49 +5686,49 @@
         <v>2.46</v>
       </c>
       <c r="G21" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H21" t="n">
         <v>2.62</v>
       </c>
       <c r="I21" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="J21" t="n">
         <v>3.7</v>
       </c>
       <c r="K21" t="n">
-        <v>4.5</v>
+        <v>500</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="R21" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="S21" t="n">
-        <v>2.46</v>
+        <v>1.78</v>
       </c>
       <c r="T21" t="n">
-        <v>1.54</v>
+        <v>1.11</v>
       </c>
       <c r="U21" t="n">
-        <v>2.52</v>
+        <v>1.11</v>
       </c>
       <c r="V21" t="n">
         <v>1.53</v>
@@ -5737,176 +5737,176 @@
         <v>1.59</v>
       </c>
       <c r="X21" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL21" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN21" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP21" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BR21" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BT21" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV21" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BX21" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -5937,230 +5937,230 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="G22" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="I22" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="J22" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="K22" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
         <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="O22" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="P22" t="n">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="R22" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="S22" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="T22" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="U22" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V22" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
         <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL22" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN22" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP22" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR22" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT22" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV22" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX22" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -6212,25 +6212,25 @@
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="O23" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="P23" t="n">
         <v>1.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="R23" t="n">
         <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="T23" t="n">
         <v>1.11</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -6445,230 +6445,230 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="G24" t="n">
         <v>1.48</v>
       </c>
       <c r="H24" t="n">
-        <v>7.6</v>
+        <v>3.55</v>
       </c>
       <c r="I24" t="n">
-        <v>9.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="J24" t="n">
         <v>5.1</v>
       </c>
       <c r="K24" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="L24" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="P24" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="R24" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="S24" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="T24" t="n">
-        <v>1.81</v>
+        <v>1.11</v>
       </c>
       <c r="U24" t="n">
-        <v>2.06</v>
+        <v>1.11</v>
       </c>
       <c r="V24" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="W24" t="n">
         <v>3.05</v>
       </c>
       <c r="X24" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL24" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN24" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BP24" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR24" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BT24" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BV24" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BX24" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -6699,230 +6699,230 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="H25" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="I25" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="J25" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="K25" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="L25" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="O25" t="n">
-        <v>1.21</v>
+        <v>1.03</v>
       </c>
       <c r="P25" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
         <v>1.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="S25" t="n">
         <v>2.56</v>
       </c>
       <c r="T25" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="U25" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="V25" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="W25" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="X25" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL25" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN25" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="BP25" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR25" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT25" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BV25" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BX25" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -6953,230 +6953,230 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="G26" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="H26" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="I26" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="J26" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K26" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="L26" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="O26" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P26" t="n">
-        <v>2.78</v>
+        <v>2.32</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="R26" t="n">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="S26" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="T26" t="n">
-        <v>1.51</v>
+        <v>1.11</v>
       </c>
       <c r="U26" t="n">
-        <v>2.46</v>
+        <v>1.11</v>
       </c>
       <c r="V26" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="W26" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="X26" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BL26" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BN26" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP26" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BR26" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT26" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV26" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BX26" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -7207,230 +7207,230 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="G27" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="H27" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="I27" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="J27" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="K27" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="L27" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
         <v>1.02</v>
       </c>
       <c r="N27" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="O27" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="R27" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="S27" t="n">
-        <v>2.04</v>
+        <v>1.74</v>
       </c>
       <c r="T27" t="n">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="U27" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V27" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="W27" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AA27" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AD27" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE27" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ27" t="n">
-        <v>12</v>
+        <v>1.17</v>
       </c>
       <c r="AR27" t="n">
-        <v>10.5</v>
+        <v>1.08</v>
       </c>
       <c r="AS27" t="n">
-        <v>12</v>
+        <v>1.17</v>
       </c>
       <c r="AT27" t="n">
-        <v>7.4</v>
+        <v>1.17</v>
       </c>
       <c r="AU27" t="n">
-        <v>10.5</v>
+        <v>1.08</v>
       </c>
       <c r="AV27" t="n">
-        <v>9.4</v>
+        <v>1.17</v>
       </c>
       <c r="AW27" t="n">
-        <v>12</v>
+        <v>1.17</v>
       </c>
       <c r="AX27" t="n">
-        <v>8</v>
+        <v>1.17</v>
       </c>
       <c r="AY27" t="n">
-        <v>22</v>
+        <v>1.17</v>
       </c>
       <c r="AZ27" t="n">
-        <v>16</v>
+        <v>1.17</v>
       </c>
       <c r="BA27" t="n">
-        <v>21</v>
+        <v>1.17</v>
       </c>
       <c r="BB27" t="n">
-        <v>8.6</v>
+        <v>1.17</v>
       </c>
       <c r="BC27" t="n">
-        <v>8.199999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="BD27" t="n">
-        <v>8</v>
+        <v>1.17</v>
       </c>
       <c r="BE27" t="n">
-        <v>8</v>
+        <v>1.17</v>
       </c>
       <c r="BF27" t="n">
-        <v>8</v>
+        <v>1.17</v>
       </c>
       <c r="BG27" t="n">
-        <v>3.95</v>
+        <v>1.17</v>
       </c>
       <c r="BH27" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BI27" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BJ27" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK27" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL27" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BN27" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BO27" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BP27" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BR27" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BT27" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BU27" t="n">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BV27" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BX27" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BZ27" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -7461,230 +7461,230 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="G28" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="H28" t="n">
         <v>1.82</v>
       </c>
       <c r="I28" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="J28" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="K28" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L28" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="M28" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="O28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R28" t="n">
         <v>1.32</v>
       </c>
-      <c r="P28" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.35</v>
-      </c>
       <c r="S28" t="n">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="T28" t="n">
-        <v>1.88</v>
+        <v>1.11</v>
       </c>
       <c r="U28" t="n">
-        <v>1.96</v>
+        <v>1.11</v>
       </c>
       <c r="V28" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="W28" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="X28" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR28" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV28" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AY28" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC28" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BI28" t="n">
-        <v>2.74</v>
+        <v>1.04</v>
       </c>
       <c r="BJ28" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK28" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BL28" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BN28" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BO28" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="BP28" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR28" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT28" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BU28" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BV28" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BX28" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ28" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -7715,230 +7715,230 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="G29" t="n">
         <v>2.38</v>
       </c>
       <c r="H29" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="I29" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="J29" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N29" t="n">
         <v>4.2</v>
       </c>
-      <c r="L29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N29" t="n">
-        <v>5</v>
-      </c>
       <c r="O29" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="P29" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="R29" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="S29" t="n">
-        <v>2.56</v>
+        <v>1.05</v>
       </c>
       <c r="T29" t="n">
-        <v>1.58</v>
+        <v>1.11</v>
       </c>
       <c r="U29" t="n">
-        <v>2.52</v>
+        <v>1.11</v>
       </c>
       <c r="V29" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="W29" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="X29" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR29" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AS29" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AT29" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AU29" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV29" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AW29" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AX29" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AY29" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA29" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB29" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BC29" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD29" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BE29" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF29" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI29" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ29" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL29" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BN29" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO29" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP29" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BR29" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BT29" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV29" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BX29" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ29" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -7993,22 +7993,22 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O30" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="P30" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="R30" t="n">
         <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T30" t="n">
         <v>1.11</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -8223,10 +8223,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="G31" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H31" t="n">
         <v>1.04</v>
@@ -8247,7 +8247,7 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="O31" t="n">
         <v>1.01</v>
@@ -8262,7 +8262,7 @@
         <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>1.48</v>
+        <v>1.05</v>
       </c>
       <c r="T31" t="n">
         <v>1.11</v>
@@ -8271,7 +8271,7 @@
         <v>1.11</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W31" t="n">
         <v>1.01</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -8504,19 +8504,19 @@
         <v>1.25</v>
       </c>
       <c r="O32" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P32" t="n">
         <v>1.24</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="R32" t="n">
         <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>1.39</v>
+        <v>1.05</v>
       </c>
       <c r="T32" t="n">
         <v>1.11</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -8731,10 +8731,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="G33" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H33" t="n">
         <v>3.8</v>
@@ -8743,52 +8743,52 @@
         <v>3.9</v>
       </c>
       <c r="J33" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K33" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L33" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
         <v>1.04</v>
       </c>
       <c r="N33" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="O33" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="P33" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="Q33" t="n">
         <v>1.64</v>
       </c>
       <c r="R33" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="S33" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="T33" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="U33" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V33" t="n">
         <v>1.34</v>
       </c>
       <c r="W33" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="X33" t="n">
         <v>24</v>
       </c>
       <c r="Y33" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Z33" t="n">
         <v>32</v>
@@ -8797,49 +8797,49 @@
         <v>75</v>
       </c>
       <c r="AB33" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AC33" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AD33" t="n">
         <v>15.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AF33" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AG33" t="n">
         <v>11</v>
       </c>
       <c r="AH33" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AI33" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ33" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK33" t="n">
         <v>19</v>
       </c>
       <c r="AL33" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM33" t="n">
         <v>65</v>
       </c>
       <c r="AN33" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AO33" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AP33" t="n">
-        <v>9.6</v>
+        <v>16</v>
       </c>
       <c r="AQ33" t="n">
         <v>18</v>
@@ -8848,25 +8848,25 @@
         <v>27</v>
       </c>
       <c r="AS33" t="n">
-        <v>55</v>
+        <v>5.2</v>
       </c>
       <c r="AT33" t="n">
         <v>12</v>
       </c>
       <c r="AU33" t="n">
-        <v>8.800000000000001</v>
+        <v>3.45</v>
       </c>
       <c r="AV33" t="n">
         <v>14</v>
       </c>
       <c r="AW33" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="AX33" t="n">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="AY33" t="n">
-        <v>9.800000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="AZ33" t="n">
         <v>14</v>
@@ -8878,83 +8878,83 @@
         <v>22</v>
       </c>
       <c r="BC33" t="n">
-        <v>17</v>
+        <v>4.2</v>
       </c>
       <c r="BD33" t="n">
-        <v>24</v>
+        <v>4.5</v>
       </c>
       <c r="BE33" t="n">
-        <v>50</v>
+        <v>5.1</v>
       </c>
       <c r="BF33" t="n">
         <v>9</v>
       </c>
       <c r="BG33" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="BH33" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI33" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BJ33" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK33" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL33" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN33" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO33" t="n">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BP33" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BQ33" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BR33" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BT33" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU33" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV33" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BX33" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BZ33" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="CA33" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -8988,227 +8988,227 @@
         <v>4.8</v>
       </c>
       <c r="G34" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="H34" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="I34" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="J34" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K34" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="L34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O34" t="n">
         <v>1.44</v>
       </c>
-      <c r="M34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.5</v>
-      </c>
       <c r="P34" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="Q34" t="n">
         <v>2.42</v>
       </c>
       <c r="R34" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="T34" t="n">
-        <v>2.2</v>
+        <v>1.11</v>
       </c>
       <c r="U34" t="n">
-        <v>1.73</v>
+        <v>1.11</v>
       </c>
       <c r="V34" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="W34" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="X34" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Y34" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="Z34" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AA34" t="n">
         <v>27</v>
       </c>
       <c r="AB34" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AC34" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD34" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE34" t="n">
         <v>30</v>
       </c>
       <c r="AF34" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AG34" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AH34" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="AI34" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AK34" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AL34" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM34" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AO34" t="n">
         <v>25</v>
       </c>
       <c r="AP34" t="n">
-        <v>9</v>
+        <v>1.21</v>
       </c>
       <c r="AQ34" t="n">
-        <v>5.8</v>
+        <v>1.21</v>
       </c>
       <c r="AR34" t="n">
-        <v>9</v>
+        <v>1.21</v>
       </c>
       <c r="AS34" t="n">
-        <v>17</v>
+        <v>1.16</v>
       </c>
       <c r="AT34" t="n">
-        <v>11</v>
+        <v>1.21</v>
       </c>
       <c r="AU34" t="n">
-        <v>7.4</v>
+        <v>1.21</v>
       </c>
       <c r="AV34" t="n">
-        <v>9.6</v>
+        <v>1.21</v>
       </c>
       <c r="AW34" t="n">
-        <v>18.5</v>
+        <v>1.16</v>
       </c>
       <c r="AX34" t="n">
-        <v>4.7</v>
+        <v>1.18</v>
       </c>
       <c r="AY34" t="n">
-        <v>17.5</v>
+        <v>1.21</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4.6</v>
+        <v>1.16</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.9</v>
+        <v>1.21</v>
       </c>
       <c r="BB34" t="n">
-        <v>5.1</v>
+        <v>1.21</v>
       </c>
       <c r="BC34" t="n">
-        <v>5</v>
+        <v>1.21</v>
       </c>
       <c r="BD34" t="n">
-        <v>5</v>
+        <v>1.21</v>
       </c>
       <c r="BE34" t="n">
-        <v>5.1</v>
+        <v>1.21</v>
       </c>
       <c r="BF34" t="n">
-        <v>5</v>
+        <v>1.21</v>
       </c>
       <c r="BG34" t="n">
-        <v>4.3</v>
+        <v>1.15</v>
       </c>
       <c r="BH34" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI34" t="n">
-        <v>2.3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ34" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK34" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL34" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BN34" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BO34" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP34" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BQ34" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR34" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BT34" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BU34" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV34" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BW34" t="n">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BX34" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ34" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA34" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -9239,16 +9239,16 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G35" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="H35" t="n">
         <v>5.4</v>
       </c>
       <c r="I35" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="J35" t="n">
         <v>3.5</v>
@@ -9269,16 +9269,16 @@
         <v>1.39</v>
       </c>
       <c r="P35" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q35" t="n">
         <v>2.14</v>
       </c>
       <c r="R35" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T35" t="n">
         <v>2.02</v>
@@ -9287,7 +9287,7 @@
         <v>1.82</v>
       </c>
       <c r="V35" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W35" t="n">
         <v>2.18</v>
@@ -9308,7 +9308,7 @@
         <v>8.6</v>
       </c>
       <c r="AC35" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD35" t="n">
         <v>28</v>
@@ -9329,7 +9329,7 @@
         <v>120</v>
       </c>
       <c r="AJ35" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AK35" t="n">
         <v>26</v>
@@ -9341,82 +9341,82 @@
         <v>200</v>
       </c>
       <c r="AN35" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO35" t="n">
         <v>170</v>
       </c>
       <c r="AP35" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AQ35" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR35" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AS35" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AT35" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AU35" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV35" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE35" t="n">
         <v>4.2</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>4.8</v>
       </c>
       <c r="BF35" t="n">
         <v>10.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BH35" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI35" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ35" t="n">
         <v>13.5</v>
       </c>
       <c r="BK35" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BL35" t="n">
         <v>220</v>
       </c>
       <c r="BM35" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BN35" t="n">
         <v>4.9</v>
@@ -9428,41 +9428,41 @@
         <v>15.5</v>
       </c>
       <c r="BQ35" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BR35" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BS35" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BT35" t="n">
         <v>11</v>
       </c>
       <c r="BU35" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BV35" t="n">
         <v>70</v>
       </c>
       <c r="BW35" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BX35" t="n">
         <v>80</v>
       </c>
       <c r="BY35" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BZ35" t="n">
         <v>34</v>
       </c>
       <c r="CA35" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>
@@ -9493,40 +9493,40 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="G36" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H36" t="n">
         <v>2.98</v>
       </c>
-      <c r="H36" t="n">
-        <v>2.94</v>
-      </c>
       <c r="I36" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="J36" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K36" t="n">
         <v>3.25</v>
       </c>
       <c r="L36" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="M36" t="n">
         <v>1.12</v>
       </c>
       <c r="N36" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="O36" t="n">
         <v>1.52</v>
       </c>
       <c r="P36" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.78</v>
+        <v>2.64</v>
       </c>
       <c r="R36" t="n">
         <v>1.18</v>
@@ -9535,34 +9535,34 @@
         <v>5.4</v>
       </c>
       <c r="T36" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U36" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V36" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="W36" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="X36" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y36" t="n">
         <v>9.4</v>
       </c>
       <c r="Z36" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA36" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB36" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC36" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD36" t="n">
         <v>15.5</v>
@@ -9571,7 +9571,7 @@
         <v>50</v>
       </c>
       <c r="AF36" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG36" t="n">
         <v>14</v>
@@ -9580,13 +9580,13 @@
         <v>24</v>
       </c>
       <c r="AI36" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ36" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK36" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL36" t="n">
         <v>70</v>
@@ -9595,73 +9595,73 @@
         <v>210</v>
       </c>
       <c r="AN36" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AO36" t="n">
         <v>65</v>
       </c>
       <c r="AP36" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ36" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR36" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS36" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT36" t="n">
         <v>7</v>
       </c>
       <c r="AU36" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV36" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="AX36" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY36" t="n">
         <v>11</v>
       </c>
       <c r="AZ36" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB36" t="n">
         <v>8</v>
       </c>
       <c r="BC36" t="n">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="BD36" t="n">
         <v>8.4</v>
       </c>
       <c r="BE36" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF36" t="n">
         <v>8</v>
       </c>
       <c r="BG36" t="n">
-        <v>44</v>
+        <v>8.4</v>
       </c>
       <c r="BH36" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BI36" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BJ36" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK36" t="n">
         <v>4.1</v>
@@ -9670,53 +9670,53 @@
         <v>230</v>
       </c>
       <c r="BM36" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BN36" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO36" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP36" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BQ36" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BR36" t="n">
         <v>55</v>
       </c>
       <c r="BS36" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BT36" t="n">
         <v>6.8</v>
       </c>
       <c r="BU36" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV36" t="n">
         <v>34</v>
       </c>
       <c r="BW36" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BX36" t="n">
         <v>60</v>
       </c>
       <c r="BY36" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BZ36" t="n">
         <v>60</v>
       </c>
       <c r="CA36" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-20 04:48:00</t>
+          <t>2026-05-20 07:02:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="G2" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="H2" t="n">
         <v>14</v>
@@ -875,13 +875,13 @@
         <v>6.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
         <v>1.31</v>
@@ -902,16 +902,16 @@
         <v>2.44</v>
       </c>
       <c r="U2" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="V2" t="n">
         <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="X2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y2" t="n">
         <v>44</v>
@@ -923,10 +923,10 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD2" t="n">
         <v>70</v>
@@ -935,7 +935,7 @@
         <v>450</v>
       </c>
       <c r="AF2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AG2" t="n">
         <v>13.5</v>
@@ -947,7 +947,7 @@
         <v>340</v>
       </c>
       <c r="AJ2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK2" t="n">
         <v>21</v>
@@ -968,13 +968,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AT2" t="n">
         <v>5.1</v>
@@ -983,22 +983,22 @@
         <v>9.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AY2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BB2" t="n">
         <v>7.2</v>
@@ -1007,22 +1007,22 @@
         <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH2" t="n">
         <v>4.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="BJ2" t="n">
         <v>17.5</v>
@@ -1031,7 +1031,7 @@
         <v>3.85</v>
       </c>
       <c r="BL2" t="n">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="BM2" t="n">
         <v>4.9</v>
@@ -1046,7 +1046,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR2" t="n">
         <v>38</v>
@@ -1055,10 +1055,10 @@
         <v>4.4</v>
       </c>
       <c r="BT2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BV2" t="n">
         <v>190</v>
@@ -1073,14 +1073,14 @@
         <v>4.8</v>
       </c>
       <c r="BZ2" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="CA2" t="n">
         <v>3.9</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.38</v>
       </c>
       <c r="G3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H3" t="n">
         <v>8.4</v>
@@ -1141,10 +1141,10 @@
         <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="R3" t="n">
         <v>1.49</v>
@@ -1153,10 +1153,10 @@
         <v>2.68</v>
       </c>
       <c r="T3" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="V3" t="n">
         <v>1.09</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G4" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H4" t="n">
         <v>3.4</v>
@@ -1377,10 +1377,10 @@
         <v>4.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.42</v>
@@ -1407,7 +1407,7 @@
         <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U4" t="n">
         <v>1.93</v>
@@ -1416,7 +1416,7 @@
         <v>1.34</v>
       </c>
       <c r="W4" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1503,10 +1503,10 @@
         <v>3.9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.35</v>
+        <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BB4" t="n">
         <v>2.34</v>
@@ -1515,25 +1515,25 @@
         <v>4.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.38</v>
+        <v>4.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BF4" t="n">
         <v>11</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BH4" t="n">
         <v>3.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BJ4" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="BK4" t="n">
         <v>3.45</v>
@@ -1542,7 +1542,7 @@
         <v>150</v>
       </c>
       <c r="BM4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BN4" t="n">
         <v>5.9</v>
@@ -1554,10 +1554,10 @@
         <v>970</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BR4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS4" t="n">
         <v>4.3</v>
@@ -1572,23 +1572,23 @@
         <v>36</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BX4" t="n">
         <v>50</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>32</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -1625,13 +1625,13 @@
         <v>12.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="I5" t="n">
         <v>1.41</v>
       </c>
       <c r="J5" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="K5" t="n">
         <v>6</v>
@@ -1646,7 +1646,7 @@
         <v>4.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P5" t="n">
         <v>2.22</v>
@@ -1661,13 +1661,13 @@
         <v>2.62</v>
       </c>
       <c r="T5" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="V5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="W5" t="n">
         <v>1.08</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -1879,16 +1879,16 @@
         <v>1.25</v>
       </c>
       <c r="H6" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="I6" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.23</v>
@@ -1903,28 +1903,28 @@
         <v>1.19</v>
       </c>
       <c r="P6" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="R6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S6" t="n">
         <v>2.42</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U6" t="n">
         <v>1.58</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="X6" t="n">
         <v>32</v>
@@ -1933,7 +1933,7 @@
         <v>70</v>
       </c>
       <c r="Z6" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
@@ -1942,13 +1942,13 @@
         <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD6" t="n">
         <v>90</v>
       </c>
       <c r="AE6" t="n">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="AF6" t="n">
         <v>8.800000000000001</v>
@@ -1975,7 +1975,7 @@
         <v>350</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1999,10 +1999,10 @@
         <v>12.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX6" t="n">
         <v>5.6</v>
@@ -2011,7 +2011,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA6" t="n">
         <v>4.4</v>
@@ -2029,7 +2029,7 @@
         <v>4.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BG6" t="n">
         <v>4.5</v>
@@ -2074,10 +2074,10 @@
         <v>24</v>
       </c>
       <c r="BU6" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BV6" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="BW6" t="n">
         <v>4.6</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>990</v>
       </c>
       <c r="J7" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>500</v>
@@ -2148,19 +2148,19 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
         <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="P7" t="n">
         <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -2638,13 +2638,13 @@
         <v>1.55</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H9" t="n">
         <v>5.8</v>
       </c>
       <c r="I9" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J9" t="n">
         <v>3.75</v>
@@ -2674,7 +2674,7 @@
         <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T9" t="n">
         <v>1.78</v>
@@ -2686,7 +2686,7 @@
         <v>1.16</v>
       </c>
       <c r="W9" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="X9" t="n">
         <v>970</v>
@@ -2701,10 +2701,10 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC9" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AD9" t="n">
         <v>950</v>
@@ -2743,58 +2743,58 @@
         <v>120</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AW9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BA9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH9" t="n">
         <v>4.2</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
         <v>990</v>
       </c>
       <c r="J10" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="K10" t="n">
         <v>500</v>
@@ -2910,7 +2910,7 @@
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
         <v>1.33</v>
@@ -2922,13 +2922,13 @@
         <v>1.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.6</v>
+        <v>1.05</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -3158,13 +3158,13 @@
         <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
         <v>1.38</v>
       </c>
       <c r="M11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
         <v>3.3</v>
@@ -3173,10 +3173,10 @@
         <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R11" t="n">
         <v>1.3</v>
@@ -3185,10 +3185,10 @@
         <v>3.6</v>
       </c>
       <c r="T11" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="U11" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
         <v>1.35</v>
@@ -3209,10 +3209,10 @@
         <v>80</v>
       </c>
       <c r="AB11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11" t="n">
         <v>17.5</v>
@@ -3230,7 +3230,7 @@
         <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ11" t="n">
         <v>36</v>
@@ -3248,19 +3248,19 @@
         <v>25</v>
       </c>
       <c r="AO11" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR11" t="n">
         <v>18.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AT11" t="n">
         <v>7.2</v>
@@ -3272,7 +3272,7 @@
         <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AX11" t="n">
         <v>11</v>
@@ -3284,25 +3284,25 @@
         <v>14</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BC11" t="n">
         <v>19.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BF11" t="n">
         <v>16</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BH11" t="n">
         <v>3.65</v>
@@ -3314,13 +3314,13 @@
         <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>3.8</v>
+        <v>7.4</v>
       </c>
       <c r="BL11" t="n">
         <v>150</v>
       </c>
       <c r="BM11" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BN11" t="n">
         <v>5.8</v>
@@ -3332,13 +3332,13 @@
         <v>21</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR11" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BS11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BT11" t="n">
         <v>7.6</v>
@@ -3350,23 +3350,23 @@
         <v>34</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BX11" t="n">
         <v>48</v>
       </c>
       <c r="BY11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BZ11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G12" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="H12" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="I12" t="n">
         <v>3.05</v>
@@ -3430,25 +3430,25 @@
         <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="R12" t="n">
         <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V12" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W12" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="X12" t="n">
         <v>14.5</v>
@@ -3535,7 +3535,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BA12" t="n">
         <v>4</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -3654,19 +3654,19 @@
         <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H13" t="n">
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -3675,7 +3675,7 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O13" t="n">
         <v>1.04</v>
@@ -3690,13 +3690,13 @@
         <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V13" t="n">
         <v>1.01</v>
@@ -3816,65 +3816,65 @@
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN13" t="n">
         <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G14" t="n">
         <v>3.4</v>
@@ -3917,10 +3917,10 @@
         <v>2.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L14" t="n">
         <v>1.32</v>
@@ -3941,7 +3941,7 @@
         <v>1.91</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
         <v>3.25</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
         <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
         <v>1.27</v>
@@ -4183,7 +4183,7 @@
         <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O15" t="n">
         <v>1.2</v>
@@ -4204,7 +4204,7 @@
         <v>1.6</v>
       </c>
       <c r="U15" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V15" t="n">
         <v>1.3</v>
@@ -4213,7 +4213,7 @@
         <v>2.04</v>
       </c>
       <c r="X15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y15" t="n">
         <v>25</v>
@@ -4225,7 +4225,7 @@
         <v>90</v>
       </c>
       <c r="AB15" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC15" t="n">
         <v>10.5</v>
@@ -4243,7 +4243,7 @@
         <v>12.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI15" t="n">
         <v>55</v>
@@ -4273,10 +4273,10 @@
         <v>18.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT15" t="n">
         <v>9.800000000000001</v>
@@ -4288,7 +4288,7 @@
         <v>13.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX15" t="n">
         <v>11</v>
@@ -4300,7 +4300,7 @@
         <v>12</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB15" t="n">
         <v>19</v>
@@ -4312,13 +4312,13 @@
         <v>21</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF15" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG15" t="n">
-        <v>25</v>
+        <v>5.1</v>
       </c>
       <c r="BH15" t="n">
         <v>4.8</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -4416,10 +4416,10 @@
         <v>2.32</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H16" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I16" t="n">
         <v>4.3</v>
@@ -4431,16 +4431,16 @@
         <v>3.05</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P16" t="n">
         <v>1.42</v>
@@ -4449,194 +4449,194 @@
         <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BH16" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BL16" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="BM16" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BP16" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BT16" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BV16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BX16" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BY16" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -4670,16 +4670,16 @@
         <v>2.04</v>
       </c>
       <c r="G17" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="H17" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I17" t="n">
         <v>4.7</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="K17" t="n">
         <v>4.3</v>
@@ -4700,7 +4700,7 @@
         <v>1.79</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="R17" t="n">
         <v>1.3</v>
@@ -4727,7 +4727,7 @@
         <v>16.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AA17" t="n">
         <v>95</v>
@@ -4736,7 +4736,7 @@
         <v>11.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD17" t="n">
         <v>19</v>
@@ -4772,61 +4772,61 @@
         <v>23</v>
       </c>
       <c r="AO17" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AR17" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AU17" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="AV17" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AW17" t="n">
         <v>4.1</v>
       </c>
       <c r="AX17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AY17" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BA17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD17" t="n">
         <v>4.1</v>
       </c>
-      <c r="BB17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4</v>
-      </c>
       <c r="BE17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG17" t="n">
         <v>4.2</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>4.1</v>
       </c>
       <c r="BH17" t="n">
         <v>3.8</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
         <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="H18" t="n">
         <v>1.04</v>
@@ -4972,7 +4972,7 @@
         <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>2.52</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G19" t="n">
         <v>3.15</v>
@@ -5199,16 +5199,16 @@
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R19" t="n">
         <v>1.31</v>
@@ -5268,7 +5268,7 @@
         <v>55</v>
       </c>
       <c r="AK19" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL19" t="n">
         <v>55</v>
@@ -5280,13 +5280,13 @@
         <v>38</v>
       </c>
       <c r="AO19" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AP19" t="n">
         <v>11</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR19" t="n">
         <v>14.5</v>
@@ -5322,7 +5322,7 @@
         <v>46</v>
       </c>
       <c r="BC19" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="BD19" t="n">
         <v>44</v>
@@ -5334,7 +5334,7 @@
         <v>32</v>
       </c>
       <c r="BG19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BH19" t="n">
         <v>3.65</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -5432,13 +5432,13 @@
         <v>2.46</v>
       </c>
       <c r="G20" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="H20" t="n">
         <v>2.52</v>
       </c>
       <c r="I20" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J20" t="n">
         <v>4</v>
@@ -5453,10 +5453,10 @@
         <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="O20" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P20" t="n">
         <v>2.86</v>
@@ -5471,16 +5471,16 @@
         <v>2.12</v>
       </c>
       <c r="T20" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="U20" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="V20" t="n">
         <v>1.55</v>
       </c>
       <c r="W20" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="X20" t="n">
         <v>950</v>
@@ -5504,7 +5504,7 @@
         <v>16.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF20" t="n">
         <v>28</v>
@@ -5525,10 +5525,10 @@
         <v>28</v>
       </c>
       <c r="AL20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM20" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN20" t="n">
         <v>14.5</v>
@@ -5537,7 +5537,7 @@
         <v>15</v>
       </c>
       <c r="AP20" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AQ20" t="n">
         <v>14</v>
@@ -5546,19 +5546,19 @@
         <v>17</v>
       </c>
       <c r="AS20" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AT20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>8.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="AV20" t="n">
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX20" t="n">
         <v>16.5</v>
@@ -5570,10 +5570,10 @@
         <v>10</v>
       </c>
       <c r="BA20" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BC20" t="n">
         <v>16.5</v>
@@ -5582,13 +5582,13 @@
         <v>19</v>
       </c>
       <c r="BE20" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BF20" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG20" t="n">
-        <v>9</v>
+        <v>3.25</v>
       </c>
       <c r="BH20" t="n">
         <v>5.5</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="G21" t="n">
         <v>2.72</v>
@@ -5722,16 +5722,16 @@
         <v>1.55</v>
       </c>
       <c r="S21" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T21" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U21" t="n">
         <v>2.52</v>
       </c>
       <c r="V21" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W21" t="n">
         <v>1.59</v>
@@ -5740,31 +5740,31 @@
         <v>28</v>
       </c>
       <c r="Y21" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Z21" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AA21" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AB21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD21" t="n">
         <v>16</v>
       </c>
-      <c r="AC21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AE21" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AF21" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AG21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH21" t="n">
         <v>18</v>
@@ -5773,10 +5773,10 @@
         <v>34</v>
       </c>
       <c r="AJ21" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AK21" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AL21" t="n">
         <v>32</v>
@@ -5785,58 +5785,58 @@
         <v>70</v>
       </c>
       <c r="AN21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO21" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AP21" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR21" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AS21" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="AT21" t="n">
         <v>13</v>
       </c>
       <c r="AU21" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AV21" t="n">
         <v>11</v>
       </c>
       <c r="AW21" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="AX21" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AZ21" t="n">
         <v>10.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>6.4</v>
+        <v>24</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="BC21" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BE21" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="BF21" t="n">
         <v>10.5</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5943,7 @@
         <v>1.12</v>
       </c>
       <c r="H22" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="I22" t="n">
         <v>46</v>
@@ -5952,10 +5952,10 @@
         <v>12</v>
       </c>
       <c r="K22" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="L22" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="M22" t="n">
         <v>1.01</v>
@@ -6060,7 +6060,7 @@
         <v>10</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AV22" t="n">
         <v>4.8</v>
@@ -6084,7 +6084,7 @@
         <v>6.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BD22" t="n">
         <v>4.5</v>
@@ -6099,10 +6099,10 @@
         <v>5</v>
       </c>
       <c r="BH22" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BI22" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BJ22" t="n">
         <v>17.5</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
         <v>13.5</v>
       </c>
       <c r="G23" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="H23" t="n">
         <v>1.22</v>
@@ -6206,7 +6206,7 @@
         <v>7.2</v>
       </c>
       <c r="K23" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="L23" t="n">
         <v>1.21</v>
@@ -6233,16 +6233,16 @@
         <v>2.08</v>
       </c>
       <c r="T23" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="U23" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V23" t="n">
         <v>4.6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
         <v>42</v>
@@ -6254,7 +6254,7 @@
         <v>10.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AB23" t="n">
         <v>60</v>
@@ -6284,7 +6284,7 @@
         <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AL23" t="n">
         <v>180</v>
@@ -6293,16 +6293,16 @@
         <v>190</v>
       </c>
       <c r="AN23" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AO23" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AQ23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR23" t="n">
         <v>8</v>
@@ -6311,7 +6311,7 @@
         <v>7.6</v>
       </c>
       <c r="AT23" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AU23" t="n">
         <v>13.5</v>
@@ -6323,34 +6323,34 @@
         <v>10.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AY23" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BB23" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BC23" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BF23" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="BH23" t="n">
         <v>5.8</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -6717,7 +6717,7 @@
         <v>6.2</v>
       </c>
       <c r="L25" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="M25" t="n">
         <v>1.04</v>
@@ -6741,10 +6741,10 @@
         <v>2.46</v>
       </c>
       <c r="T25" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="U25" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="V25" t="n">
         <v>1.13</v>
@@ -6768,7 +6768,7 @@
         <v>12.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD25" t="n">
         <v>34</v>
@@ -6786,7 +6786,7 @@
         <v>26</v>
       </c>
       <c r="AI25" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ25" t="n">
         <v>15.5</v>
@@ -6795,13 +6795,13 @@
         <v>17</v>
       </c>
       <c r="AL25" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM25" t="n">
         <v>120</v>
       </c>
       <c r="AN25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AO25" t="n">
         <v>130</v>
@@ -6813,25 +6813,25 @@
         <v>4.6</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT25" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU25" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AV25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX25" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY25" t="n">
         <v>8</v>
@@ -6852,13 +6852,13 @@
         <v>4.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH25" t="n">
         <v>4.9</v>
@@ -6876,7 +6876,7 @@
         <v>130</v>
       </c>
       <c r="BM25" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BN25" t="n">
         <v>4.7</v>
@@ -6888,10 +6888,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BQ25" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BR25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BS25" t="n">
         <v>4.7</v>
@@ -6906,7 +6906,7 @@
         <v>70</v>
       </c>
       <c r="BW25" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BX25" t="n">
         <v>65</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
         <v>4.2</v>
       </c>
       <c r="G26" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H26" t="n">
         <v>1.78</v>
@@ -6977,7 +6977,7 @@
         <v>1.04</v>
       </c>
       <c r="N26" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O26" t="n">
         <v>1.21</v>
@@ -6998,13 +6998,13 @@
         <v>1.58</v>
       </c>
       <c r="U26" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V26" t="n">
         <v>2.1</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X26" t="n">
         <v>950</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G27" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="H27" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I27" t="n">
         <v>4.6</v>
@@ -7225,31 +7225,31 @@
         <v>5.1</v>
       </c>
       <c r="L27" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M27" t="n">
         <v>1.02</v>
       </c>
       <c r="N27" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O27" t="n">
         <v>1.16</v>
       </c>
       <c r="P27" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R27" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="S27" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="T27" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="U27" t="n">
         <v>2.44</v>
@@ -7258,7 +7258,7 @@
         <v>1.31</v>
       </c>
       <c r="W27" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="X27" t="n">
         <v>950</v>
@@ -7297,7 +7297,7 @@
         <v>44</v>
       </c>
       <c r="AJ27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK27" t="n">
         <v>970</v>
@@ -7306,37 +7306,37 @@
         <v>29</v>
       </c>
       <c r="AM27" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN27" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AO27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP27" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AR27" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AS27" t="n">
         <v>4.8</v>
       </c>
       <c r="AT27" t="n">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AX27" t="n">
         <v>12</v>
@@ -7348,31 +7348,31 @@
         <v>11.5</v>
       </c>
       <c r="BA27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE27" t="n">
         <v>4.7</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>4.9</v>
       </c>
       <c r="BF27" t="n">
         <v>5.9</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH27" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BI27" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BJ27" t="n">
         <v>9.800000000000001</v>
@@ -7396,13 +7396,13 @@
         <v>14</v>
       </c>
       <c r="BQ27" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BR27" t="n">
         <v>23</v>
       </c>
       <c r="BS27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BT27" t="n">
         <v>9</v>
@@ -7420,17 +7420,17 @@
         <v>34</v>
       </c>
       <c r="BY27" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BZ27" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="CA27" t="n">
         <v>4</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -7461,25 +7461,25 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="G28" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="I28" t="n">
         <v>1.46</v>
       </c>
       <c r="J28" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K28" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L28" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="M28" t="n">
         <v>1.02</v>
@@ -7500,16 +7500,16 @@
         <v>1.83</v>
       </c>
       <c r="S28" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T28" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="U28" t="n">
         <v>2.32</v>
       </c>
       <c r="V28" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="W28" t="n">
         <v>1.13</v>
@@ -7530,7 +7530,7 @@
         <v>46</v>
       </c>
       <c r="AC28" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AD28" t="n">
         <v>12.5</v>
@@ -7548,7 +7548,7 @@
         <v>24</v>
       </c>
       <c r="AI28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ28" t="n">
         <v>230</v>
@@ -7557,7 +7557,7 @@
         <v>100</v>
       </c>
       <c r="AL28" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM28" t="n">
         <v>90</v>
@@ -7569,7 +7569,7 @@
         <v>4.4</v>
       </c>
       <c r="AP28" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AQ28" t="n">
         <v>10.5</v>
@@ -7581,43 +7581,43 @@
         <v>10.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AU28" t="n">
         <v>10.5</v>
       </c>
       <c r="AV28" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW28" t="n">
         <v>10.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AY28" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AZ28" t="n">
         <v>18</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BB28" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC28" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BD28" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BE28" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BF28" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BG28" t="n">
         <v>3.9</v>
@@ -7638,7 +7638,7 @@
         <v>95</v>
       </c>
       <c r="BM28" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BN28" t="n">
         <v>13</v>
@@ -7656,16 +7656,16 @@
         <v>55</v>
       </c>
       <c r="BS28" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BT28" t="n">
         <v>5.1</v>
       </c>
       <c r="BU28" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BV28" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BW28" t="n">
         <v>3.45</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -7718,19 +7718,19 @@
         <v>4.6</v>
       </c>
       <c r="G29" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="H29" t="n">
         <v>1.82</v>
       </c>
       <c r="I29" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>3.85</v>
       </c>
       <c r="K29" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L29" t="n">
         <v>1.33</v>
@@ -7742,13 +7742,13 @@
         <v>3.7</v>
       </c>
       <c r="O29" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P29" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="R29" t="n">
         <v>1.34</v>
@@ -7757,22 +7757,22 @@
         <v>3.45</v>
       </c>
       <c r="T29" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U29" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V29" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="W29" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
         <v>18.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Z29" t="n">
         <v>13.5</v>
@@ -7781,10 +7781,10 @@
         <v>24</v>
       </c>
       <c r="AB29" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD29" t="n">
         <v>12.5</v>
@@ -7793,7 +7793,7 @@
         <v>24</v>
       </c>
       <c r="AF29" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG29" t="n">
         <v>23</v>
@@ -7805,7 +7805,7 @@
         <v>46</v>
       </c>
       <c r="AJ29" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AK29" t="n">
         <v>80</v>
@@ -7817,10 +7817,10 @@
         <v>150</v>
       </c>
       <c r="AN29" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AO29" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AP29" t="n">
         <v>11</v>
@@ -7829,49 +7829,49 @@
         <v>7.4</v>
       </c>
       <c r="AR29" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS29" t="n">
         <v>16.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AU29" t="n">
         <v>7.8</v>
       </c>
       <c r="AV29" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW29" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AX29" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AY29" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AZ29" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>26</v>
+        <v>4.5</v>
       </c>
       <c r="BB29" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BC29" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BG29" t="n">
         <v>9.199999999999999</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -7972,22 +7972,22 @@
         <v>2.26</v>
       </c>
       <c r="G30" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I30" t="n">
         <v>3.3</v>
       </c>
       <c r="J30" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K30" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L30" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="M30" t="n">
         <v>1.04</v>
@@ -8011,16 +8011,16 @@
         <v>2.56</v>
       </c>
       <c r="T30" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="U30" t="n">
         <v>2.52</v>
       </c>
       <c r="V30" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W30" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="X30" t="n">
         <v>27</v>
@@ -8053,7 +8053,7 @@
         <v>14.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI30" t="n">
         <v>44</v>
@@ -8065,7 +8065,7 @@
         <v>27</v>
       </c>
       <c r="AL30" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM30" t="n">
         <v>75</v>
@@ -8086,7 +8086,7 @@
         <v>21</v>
       </c>
       <c r="AS30" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AT30" t="n">
         <v>12.5</v>
@@ -8101,7 +8101,7 @@
         <v>3.8</v>
       </c>
       <c r="AX30" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AY30" t="n">
         <v>10.5</v>
@@ -8110,7 +8110,7 @@
         <v>13</v>
       </c>
       <c r="BA30" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BB30" t="n">
         <v>3.8</v>
@@ -8131,7 +8131,7 @@
         <v>15.5</v>
       </c>
       <c r="BH30" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BI30" t="n">
         <v>3.3</v>
@@ -8140,13 +8140,13 @@
         <v>10.5</v>
       </c>
       <c r="BK30" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="BL30" t="n">
         <v>95</v>
       </c>
       <c r="BM30" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BN30" t="n">
         <v>6.6</v>
@@ -8158,13 +8158,13 @@
         <v>18.5</v>
       </c>
       <c r="BQ30" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="BR30" t="n">
         <v>29</v>
       </c>
       <c r="BS30" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="BT30" t="n">
         <v>8</v>
@@ -8176,23 +8176,23 @@
         <v>27</v>
       </c>
       <c r="BW30" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BX30" t="n">
         <v>36</v>
       </c>
       <c r="BY30" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BZ30" t="n">
         <v>21</v>
       </c>
       <c r="CA30" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -8247,13 +8247,13 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="O31" t="n">
         <v>1.35</v>
       </c>
       <c r="P31" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Q31" t="n">
         <v>1.35</v>
@@ -8262,7 +8262,7 @@
         <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>1.35</v>
+        <v>1.05</v>
       </c>
       <c r="T31" t="n">
         <v>1.11</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -8477,19 +8477,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.63</v>
+        <v>1.05</v>
       </c>
       <c r="G32" t="n">
         <v>990</v>
       </c>
       <c r="H32" t="n">
-        <v>1.68</v>
+        <v>1.05</v>
       </c>
       <c r="I32" t="n">
         <v>990</v>
       </c>
       <c r="J32" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K32" t="n">
         <v>500</v>
@@ -8507,7 +8507,7 @@
         <v>1.49</v>
       </c>
       <c r="P32" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q32" t="n">
         <v>1.49</v>
@@ -8525,10 +8525,10 @@
         <v>1.11</v>
       </c>
       <c r="V32" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -8731,145 +8731,145 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="G33" t="n">
-        <v>990</v>
+        <v>3.8</v>
       </c>
       <c r="H33" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="I33" t="n">
-        <v>990</v>
+        <v>2.84</v>
       </c>
       <c r="J33" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="K33" t="n">
-        <v>500</v>
+        <v>4.2</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N33" t="n">
-        <v>1.25</v>
+        <v>2.6</v>
       </c>
       <c r="O33" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P33" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.39</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S33" t="n">
-        <v>1.38</v>
+        <v>3.6</v>
       </c>
       <c r="T33" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="U33" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AS33" t="n">
         <v>1.01</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW33" t="n">
         <v>1.01</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BA33" t="n">
         <v>1.01</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
         <v>3.8</v>
       </c>
       <c r="I34" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J34" t="n">
         <v>4.1</v>
@@ -9003,37 +9003,37 @@
         <v>4.2</v>
       </c>
       <c r="L34" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="M34" t="n">
         <v>1.04</v>
       </c>
       <c r="N34" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O34" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P34" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R34" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S34" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="T34" t="n">
         <v>1.6</v>
       </c>
       <c r="U34" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V34" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W34" t="n">
         <v>1.98</v>
@@ -9042,16 +9042,16 @@
         <v>22</v>
       </c>
       <c r="Y34" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="Z34" t="n">
         <v>32</v>
       </c>
       <c r="AA34" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB34" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC34" t="n">
         <v>9.6</v>
@@ -9084,28 +9084,28 @@
         <v>28</v>
       </c>
       <c r="AM34" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AN34" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AO34" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP34" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AQ34" t="n">
         <v>18</v>
       </c>
       <c r="AR34" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="AS34" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AT34" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU34" t="n">
         <v>8.6</v>
@@ -9141,31 +9141,31 @@
         <v>50</v>
       </c>
       <c r="BF34" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG34" t="n">
         <v>25</v>
       </c>
       <c r="BH34" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BI34" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BJ34" t="n">
         <v>10.5</v>
       </c>
       <c r="BK34" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="BL34" t="n">
         <v>100</v>
       </c>
       <c r="BM34" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BN34" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO34" t="n">
         <v>3.95</v>
@@ -9174,13 +9174,13 @@
         <v>16</v>
       </c>
       <c r="BQ34" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="BR34" t="n">
         <v>27</v>
       </c>
       <c r="BS34" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BT34" t="n">
         <v>9</v>
@@ -9192,23 +9192,23 @@
         <v>34</v>
       </c>
       <c r="BW34" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BX34" t="n">
         <v>40</v>
       </c>
       <c r="BY34" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BZ34" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="CA34" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -9242,19 +9242,19 @@
         <v>4.8</v>
       </c>
       <c r="G35" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H35" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="I35" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="J35" t="n">
         <v>3.45</v>
       </c>
       <c r="K35" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L35" t="n">
         <v>1.54</v>
@@ -9266,13 +9266,13 @@
         <v>2.76</v>
       </c>
       <c r="O35" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P35" t="n">
         <v>1.61</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R35" t="n">
         <v>1.21</v>
@@ -9287,13 +9287,13 @@
         <v>1.72</v>
       </c>
       <c r="V35" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="W35" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X35" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y35" t="n">
         <v>6.6</v>
@@ -9332,7 +9332,7 @@
         <v>190</v>
       </c>
       <c r="AK35" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AL35" t="n">
         <v>130</v>
@@ -9350,55 +9350,55 @@
         <v>7.8</v>
       </c>
       <c r="AQ35" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AR35" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS35" t="n">
-        <v>15.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT35" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AU35" t="n">
         <v>7.6</v>
       </c>
       <c r="AV35" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AW35" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX35" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AY35" t="n">
-        <v>15</v>
+        <v>5.3</v>
       </c>
       <c r="AZ35" t="n">
         <v>20</v>
       </c>
       <c r="BA35" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB35" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC35" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE35" t="n">
         <v>5.3</v>
       </c>
-      <c r="BD35" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE35" t="n">
+      <c r="BF35" t="n">
         <v>5.2</v>
       </c>
-      <c r="BF35" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BG35" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BH35" t="n">
         <v>3.25</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -9493,13 +9493,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G36" t="n">
         <v>2.86</v>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I36" t="n">
         <v>3.3</v>
@@ -9508,7 +9508,7 @@
         <v>3.1</v>
       </c>
       <c r="K36" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L36" t="n">
         <v>1.56</v>
@@ -9517,16 +9517,16 @@
         <v>1.12</v>
       </c>
       <c r="N36" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="O36" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P36" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R36" t="n">
         <v>1.19</v>
@@ -9544,19 +9544,19 @@
         <v>1.44</v>
       </c>
       <c r="W36" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X36" t="n">
         <v>10.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="Z36" t="n">
         <v>23</v>
       </c>
       <c r="AA36" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB36" t="n">
         <v>8.6</v>
@@ -9580,7 +9580,7 @@
         <v>26</v>
       </c>
       <c r="AI36" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ36" t="n">
         <v>50</v>
@@ -9604,55 +9604,55 @@
         <v>7</v>
       </c>
       <c r="AQ36" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR36" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT36" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AU36" t="n">
         <v>5.7</v>
       </c>
       <c r="AV36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY36" t="n">
         <v>11</v>
       </c>
-      <c r="AW36" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>10</v>
-      </c>
       <c r="AZ36" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB36" t="n">
         <v>38</v>
       </c>
       <c r="BC36" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BD36" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE36" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF36" t="n">
         <v>6.2</v>
       </c>
-      <c r="BF36" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BG36" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH36" t="n">
         <v>3</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
         <v>1.72</v>
       </c>
       <c r="G37" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="H37" t="n">
         <v>5.4</v>
@@ -9762,28 +9762,28 @@
         <v>3.6</v>
       </c>
       <c r="K37" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L37" t="n">
         <v>1.46</v>
       </c>
       <c r="M37" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N37" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O37" t="n">
         <v>1.39</v>
       </c>
       <c r="P37" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q37" t="n">
         <v>2.14</v>
       </c>
       <c r="R37" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -9792,13 +9792,13 @@
         <v>2.02</v>
       </c>
       <c r="U37" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="V37" t="n">
         <v>1.19</v>
       </c>
       <c r="W37" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X37" t="n">
         <v>14.5</v>
@@ -9855,7 +9855,7 @@
         <v>170</v>
       </c>
       <c r="AP37" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ37" t="n">
         <v>12</v>
@@ -9870,7 +9870,7 @@
         <v>5.4</v>
       </c>
       <c r="AU37" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV37" t="n">
         <v>16.5</v>
@@ -9936,10 +9936,10 @@
         <v>15.5</v>
       </c>
       <c r="BQ37" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BR37" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS37" t="n">
         <v>4.3</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>
@@ -10004,19 +10004,19 @@
         <v>1.04</v>
       </c>
       <c r="G38" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H38" t="n">
         <v>1.04</v>
       </c>
       <c r="I38" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J38" t="n">
         <v>1.04</v>
       </c>
       <c r="K38" t="n">
-        <v>440</v>
+        <v>500</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
@@ -10025,13 +10025,13 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O38" t="n">
         <v>1.27</v>
       </c>
       <c r="P38" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q38" t="n">
         <v>1.27</v>
@@ -10043,10 +10043,10 @@
         <v>1.27</v>
       </c>
       <c r="T38" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U38" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V38" t="n">
         <v>1.01</v>
@@ -10166,65 +10166,65 @@
         <v>1000</v>
       </c>
       <c r="BI38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ38" t="n">
         <v>1000</v>
       </c>
       <c r="BK38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN38" t="n">
         <v>1000</v>
       </c>
       <c r="BO38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP38" t="n">
         <v>1000</v>
       </c>
       <c r="BQ38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR38" t="n">
         <v>1000</v>
       </c>
       <c r="BS38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT38" t="n">
         <v>1000</v>
       </c>
       <c r="BU38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV38" t="n">
         <v>1000</v>
       </c>
       <c r="BW38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX38" t="n">
         <v>1000</v>
       </c>
       <c r="BY38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ38" t="n">
         <v>1000</v>
       </c>
       <c r="CA38" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:05</t>
+          <t>2026-05-20 11:32:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="G2" t="n">
         <v>1.34</v>
@@ -881,19 +881,19 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
         <v>3.1</v>
@@ -902,13 +902,13 @@
         <v>2.36</v>
       </c>
       <c r="U2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V2" t="n">
         <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="X2" t="n">
         <v>21</v>
@@ -947,7 +947,7 @@
         <v>310</v>
       </c>
       <c r="AJ2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AK2" t="n">
         <v>20</v>
@@ -959,7 +959,7 @@
         <v>360</v>
       </c>
       <c r="AN2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
@@ -968,13 +968,13 @@
         <v>14.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT2" t="n">
         <v>6.4</v>
@@ -986,7 +986,7 @@
         <v>25</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX2" t="n">
         <v>6.2</v>
@@ -998,7 +998,7 @@
         <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2" t="n">
         <v>7.2</v>
@@ -1007,16 +1007,16 @@
         <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF2" t="n">
         <v>5.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH2" t="n">
         <v>3.75</v>
@@ -1076,11 +1076,11 @@
         <v>15.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -1114,19 +1114,19 @@
         <v>1.38</v>
       </c>
       <c r="G3" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="H3" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.27</v>
@@ -1153,16 +1153,16 @@
         <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="U3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="V3" t="n">
         <v>1.1</v>
       </c>
       <c r="W3" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="X3" t="n">
         <v>22</v>
@@ -1171,37 +1171,37 @@
         <v>65</v>
       </c>
       <c r="Z3" t="n">
-        <v>540</v>
+        <v>95</v>
       </c>
       <c r="AA3" t="n">
-        <v>330</v>
+        <v>410</v>
       </c>
       <c r="AB3" t="n">
         <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD3" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AE3" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>470</v>
+        <v>260</v>
       </c>
       <c r="AJ3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK3" t="n">
         <v>15.5</v>
@@ -1210,25 +1210,25 @@
         <v>38</v>
       </c>
       <c r="AM3" t="n">
-        <v>390</v>
+        <v>150</v>
       </c>
       <c r="AN3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AO3" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="AP3" t="n">
         <v>17.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT3" t="n">
         <v>8</v>
@@ -1237,10 +1237,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW3" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX3" t="n">
         <v>7</v>
@@ -1252,10 +1252,10 @@
         <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BB3" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BC3" t="n">
         <v>12.5</v>
@@ -1264,13 +1264,13 @@
         <v>16</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF3" t="n">
         <v>5</v>
       </c>
       <c r="BG3" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BH3" t="n">
         <v>4.3</v>
@@ -1282,59 +1282,59 @@
         <v>12</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BP3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR3" t="n">
         <v>24</v>
       </c>
       <c r="BS3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BT3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BZ3" t="n">
         <v>13</v>
       </c>
-      <c r="BU3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>9</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>13.5</v>
-      </c>
       <c r="CA3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
         <v>3.5</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J4" t="n">
         <v>3.25</v>
@@ -1395,34 +1395,34 @@
         <v>1.32</v>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q4" t="n">
         <v>1.92</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W4" t="n">
         <v>1.77</v>
       </c>
       <c r="X4" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="Y4" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
         <v>500</v>
@@ -1437,13 +1437,13 @@
         <v>42</v>
       </c>
       <c r="AD4" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
         <v>500</v>
       </c>
       <c r="AF4" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
         <v>36</v>
@@ -1455,13 +1455,13 @@
         <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK4" t="n">
         <v>500</v>
       </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
@@ -1479,10 +1479,10 @@
         <v>7.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AT4" t="n">
         <v>7.2</v>
@@ -1494,7 +1494,7 @@
         <v>8.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AX4" t="n">
         <v>7</v>
@@ -1506,28 +1506,28 @@
         <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BB4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC4" t="n">
         <v>5.8</v>
       </c>
-      <c r="BC4" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BD4" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BF4" t="n">
         <v>11</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="BI4" t="n">
         <v>2.68</v>
@@ -1536,16 +1536,16 @@
         <v>12</v>
       </c>
       <c r="BK4" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>5.2</v>
+        <v>1.2</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.9</v>
+        <v>970</v>
       </c>
       <c r="BO4" t="n">
         <v>3.85</v>
@@ -1554,13 +1554,13 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>4.8</v>
+        <v>1.67</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.7</v>
+        <v>1.76</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.8</v>
+        <v>1.18</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.7</v>
+        <v>1.52</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
         <v>5.1</v>
       </c>
       <c r="K5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
         <v>1.26</v>
@@ -1700,7 +1700,7 @@
         <v>540</v>
       </c>
       <c r="AG5" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AH5" t="n">
         <v>36</v>
@@ -1751,7 +1751,7 @@
         <v>12.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AY5" t="n">
         <v>16</v>
@@ -1766,13 +1766,13 @@
         <v>4.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD5" t="n">
         <v>4.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF5" t="n">
         <v>15</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -1879,16 +1879,16 @@
         <v>1.24</v>
       </c>
       <c r="H6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="K6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.24</v>
@@ -1903,19 +1903,19 @@
         <v>1.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="R6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U6" t="n">
         <v>1.58</v>
@@ -1924,7 +1924,7 @@
         <v>1.04</v>
       </c>
       <c r="W6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="X6" t="n">
         <v>30</v>
@@ -1948,7 +1948,7 @@
         <v>80</v>
       </c>
       <c r="AE6" t="n">
-        <v>440</v>
+        <v>540</v>
       </c>
       <c r="AF6" t="n">
         <v>8.800000000000001</v>
@@ -1963,7 +1963,7 @@
         <v>300</v>
       </c>
       <c r="AJ6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AK6" t="n">
         <v>18</v>
@@ -1975,7 +1975,7 @@
         <v>330</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AT6" t="n">
         <v>7.6</v>
@@ -1999,10 +1999,10 @@
         <v>12</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AX6" t="n">
         <v>6.2</v>
@@ -2011,10 +2011,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BB6" t="n">
         <v>7.2</v>
@@ -2023,28 +2023,28 @@
         <v>12.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BH6" t="n">
         <v>4.6</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BK6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2235,7 @@
         <v>85</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AQ7" t="n">
         <v>4</v>
@@ -2247,7 +2247,7 @@
         <v>5.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AU7" t="n">
         <v>3.3</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -2486,13 +2486,13 @@
         <v>15.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AR8" t="n">
         <v>6.2</v>
@@ -2507,7 +2507,7 @@
         <v>4.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AW8" t="n">
         <v>6.6</v>
@@ -2519,16 +2519,16 @@
         <v>7</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BA8" t="n">
         <v>6.8</v>
       </c>
       <c r="BB8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC8" t="n">
         <v>5.9</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>5.7</v>
       </c>
       <c r="BD8" t="n">
         <v>6.4</v>
@@ -2537,10 +2537,10 @@
         <v>7</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH8" t="n">
         <v>3.7</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="G9" t="n">
         <v>1.65</v>
@@ -2656,28 +2656,28 @@
         <v>1.31</v>
       </c>
       <c r="M9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="T9" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="U9" t="n">
         <v>2.02</v>
@@ -2692,7 +2692,7 @@
         <v>500</v>
       </c>
       <c r="Y9" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z9" t="n">
         <v>500</v>
@@ -2701,7 +2701,7 @@
         <v>700</v>
       </c>
       <c r="AB9" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC9" t="n">
         <v>14</v>
@@ -2743,28 +2743,28 @@
         <v>700</v>
       </c>
       <c r="AP9" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>11.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AV9" t="n">
         <v>13</v>
       </c>
       <c r="AW9" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX9" t="n">
         <v>8</v>
@@ -2773,7 +2773,7 @@
         <v>5.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BA9" t="n">
         <v>28</v>
@@ -2785,7 +2785,7 @@
         <v>8.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BE9" t="n">
         <v>24</v>
@@ -2800,65 +2800,65 @@
         <v>3.85</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ9" t="n">
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN9" t="n">
         <v>4.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP9" t="n">
         <v>11</v>
       </c>
       <c r="BQ9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
         <v>5.1</v>
       </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>5</v>
-      </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v>1.51</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I10" t="n">
         <v>9.4</v>
@@ -2904,7 +2904,7 @@
         <v>4.5</v>
       </c>
       <c r="K10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L10" t="n">
         <v>1.26</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -3143,46 +3143,46 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G11" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="H11" t="n">
         <v>3.45</v>
       </c>
       <c r="I11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O11" t="n">
         <v>1.38</v>
       </c>
       <c r="P11" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T11" t="n">
         <v>1.82</v>
@@ -3191,31 +3191,31 @@
         <v>2.04</v>
       </c>
       <c r="V11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y11" t="n">
         <v>12.5</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>13.5</v>
       </c>
       <c r="Z11" t="n">
         <v>29</v>
       </c>
       <c r="AA11" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE11" t="n">
         <v>55</v>
@@ -3233,13 +3233,13 @@
         <v>60</v>
       </c>
       <c r="AJ11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL11" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM11" t="n">
         <v>580</v>
@@ -3254,13 +3254,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR11" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT11" t="n">
         <v>8</v>
@@ -3272,7 +3272,7 @@
         <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX11" t="n">
         <v>11</v>
@@ -3281,31 +3281,31 @@
         <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI11" t="n">
         <v>2.7</v>
@@ -3314,13 +3314,13 @@
         <v>10</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN11" t="n">
         <v>5.2</v>
@@ -3332,13 +3332,13 @@
         <v>17.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR11" t="n">
         <v>34</v>
       </c>
       <c r="BS11" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT11" t="n">
         <v>6.8</v>
@@ -3350,23 +3350,23 @@
         <v>30</v>
       </c>
       <c r="BW11" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX11" t="n">
         <v>44</v>
       </c>
       <c r="BY11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ11" t="n">
         <v>32</v>
       </c>
       <c r="CA11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G12" t="n">
         <v>2.82</v>
       </c>
       <c r="H12" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I12" t="n">
         <v>3.1</v>
@@ -3412,7 +3412,7 @@
         <v>3.2</v>
       </c>
       <c r="K12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.37</v>
@@ -3430,13 +3430,13 @@
         <v>1.78</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R12" t="n">
         <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T12" t="n">
         <v>1.82</v>
@@ -3484,7 +3484,7 @@
         <v>18.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>130</v>
+        <v>290</v>
       </c>
       <c r="AJ12" t="n">
         <v>50</v>
@@ -3493,7 +3493,7 @@
         <v>40</v>
       </c>
       <c r="AL12" t="n">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
@@ -3502,13 +3502,13 @@
         <v>32</v>
       </c>
       <c r="AO12" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AP12" t="n">
         <v>10</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR12" t="n">
         <v>16.5</v>
@@ -3541,7 +3541,7 @@
         <v>6.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="BC12" t="n">
         <v>14.5</v>
@@ -3553,16 +3553,16 @@
         <v>26</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH12" t="n">
         <v>3.3</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ12" t="n">
         <v>10.5</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -3693,10 +3693,10 @@
         <v>1.48</v>
       </c>
       <c r="T13" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="U13" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="V13" t="n">
         <v>1.37</v>
@@ -3744,10 +3744,10 @@
         <v>500</v>
       </c>
       <c r="AK13" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AL13" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AM13" t="n">
         <v>580</v>
@@ -3756,10 +3756,10 @@
         <v>4.6</v>
       </c>
       <c r="AO13" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AQ13" t="n">
         <v>8.199999999999999</v>
@@ -3798,10 +3798,10 @@
         <v>14.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BD13" t="n">
-        <v>12.5</v>
+        <v>6.2</v>
       </c>
       <c r="BE13" t="n">
         <v>14.5</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>3.3</v>
       </c>
       <c r="G14" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H14" t="n">
         <v>2.34</v>
@@ -3923,7 +3923,7 @@
         <v>3.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
@@ -3956,7 +3956,7 @@
         <v>1.72</v>
       </c>
       <c r="W14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X14" t="n">
         <v>14</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G15" t="n">
         <v>1.95</v>
@@ -4177,34 +4177,34 @@
         <v>4.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M15" t="n">
         <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R15" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S15" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T15" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U15" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="V15" t="n">
         <v>1.3</v>
@@ -4213,118 +4213,118 @@
         <v>2.04</v>
       </c>
       <c r="X15" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Y15" t="n">
         <v>21</v>
       </c>
       <c r="Z15" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="AA15" t="n">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="AB15" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC15" t="n">
         <v>11</v>
       </c>
       <c r="AD15" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AF15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AJ15" t="n">
         <v>22</v>
       </c>
       <c r="AK15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM15" t="n">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="AN15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ15" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AS15" t="n">
         <v>28</v>
       </c>
       <c r="AT15" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AU15" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX15" t="n">
         <v>13</v>
       </c>
-      <c r="AW15" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>11</v>
-      </c>
       <c r="AY15" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.8</v>
+        <v>38</v>
       </c>
       <c r="BB15" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BD15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BE15" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="BF15" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH15" t="n">
         <v>4.3</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BJ15" t="n">
         <v>9</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
         <v>2.34</v>
       </c>
       <c r="U16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V16" t="n">
         <v>1.3</v>
@@ -4494,7 +4494,7 @@
         <v>13</v>
       </c>
       <c r="AG16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH16" t="n">
         <v>32</v>
@@ -4530,7 +4530,7 @@
         <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT16" t="n">
         <v>5.9</v>
@@ -4542,7 +4542,7 @@
         <v>14.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX16" t="n">
         <v>10</v>
@@ -4554,25 +4554,25 @@
         <v>21</v>
       </c>
       <c r="BA16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BD16" t="n">
         <v>10.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF16" t="n">
         <v>32</v>
       </c>
       <c r="BG16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH16" t="n">
         <v>2.5</v>
@@ -4614,7 +4614,7 @@
         <v>7.2</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV16" t="n">
         <v>55</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -4793,7 +4793,7 @@
         <v>4.9</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AW17" t="n">
         <v>6.4</v>
@@ -4811,10 +4811,10 @@
         <v>6.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BD17" t="n">
         <v>6.2</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>4.7</v>
+        <v>2.12</v>
       </c>
       <c r="BN18" t="n">
         <v>3.85</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -5178,19 +5178,19 @@
         <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H19" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="I19" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K19" t="n">
         <v>3.4</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.45</v>
       </c>
       <c r="L19" t="n">
         <v>1.45</v>
@@ -5211,37 +5211,37 @@
         <v>2.12</v>
       </c>
       <c r="R19" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S19" t="n">
         <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U19" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V19" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W19" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X19" t="n">
         <v>12.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AB19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC19" t="n">
         <v>7.4</v>
@@ -5250,10 +5250,10 @@
         <v>12</v>
       </c>
       <c r="AE19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF19" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG19" t="n">
         <v>13.5</v>
@@ -5265,28 +5265,28 @@
         <v>46</v>
       </c>
       <c r="AJ19" t="n">
-        <v>55</v>
+        <v>340</v>
       </c>
       <c r="AK19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL19" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AM19" t="n">
         <v>110</v>
       </c>
       <c r="AN19" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="AO19" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AP19" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR19" t="n">
         <v>14.5</v>
@@ -5304,13 +5304,13 @@
         <v>11</v>
       </c>
       <c r="AW19" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AX19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ19" t="n">
         <v>16.5</v>
@@ -5319,7 +5319,7 @@
         <v>40</v>
       </c>
       <c r="BB19" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="BC19" t="n">
         <v>32</v>
@@ -5328,10 +5328,10 @@
         <v>42</v>
       </c>
       <c r="BE19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BG19" t="n">
         <v>23</v>
@@ -5346,59 +5346,59 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK19" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BN19" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP19" t="n">
         <v>32</v>
       </c>
       <c r="BQ19" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BR19" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
         <v>8.6</v>
       </c>
       <c r="BT19" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV19" t="n">
         <v>25</v>
       </c>
       <c r="BW19" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BX19" t="n">
         <v>44</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BZ19" t="n">
         <v>40</v>
       </c>
       <c r="CA19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -5435,7 +5435,7 @@
         <v>3.25</v>
       </c>
       <c r="H20" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I20" t="n">
         <v>2.48</v>
@@ -5447,7 +5447,7 @@
         <v>4.3</v>
       </c>
       <c r="L20" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M20" t="n">
         <v>1.03</v>
@@ -5459,10 +5459,10 @@
         <v>1.16</v>
       </c>
       <c r="P20" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R20" t="n">
         <v>1.74</v>
@@ -5471,7 +5471,7 @@
         <v>2.16</v>
       </c>
       <c r="T20" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="U20" t="n">
         <v>2.84</v>
@@ -5480,10 +5480,10 @@
         <v>1.67</v>
       </c>
       <c r="W20" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X20" t="n">
-        <v>950</v>
+        <v>90</v>
       </c>
       <c r="Y20" t="n">
         <v>19.5</v>
@@ -5498,7 +5498,7 @@
         <v>22</v>
       </c>
       <c r="AC20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD20" t="n">
         <v>14.5</v>
@@ -5537,19 +5537,19 @@
         <v>13</v>
       </c>
       <c r="AP20" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AQ20" t="n">
         <v>10.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AT20" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AU20" t="n">
         <v>8.800000000000001</v>
@@ -5558,10 +5558,10 @@
         <v>7</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AX20" t="n">
-        <v>5.4</v>
+        <v>11.5</v>
       </c>
       <c r="AY20" t="n">
         <v>7</v>
@@ -5570,34 +5570,34 @@
         <v>7.6</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BC20" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BE20" t="n">
         <v>5.7</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="BH20" t="n">
         <v>4.8</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BJ20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BK20" t="n">
         <v>3.5</v>
@@ -5606,7 +5606,7 @@
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BN20" t="n">
         <v>7.8</v>
@@ -5624,7 +5624,7 @@
         <v>29</v>
       </c>
       <c r="BS20" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BT20" t="n">
         <v>7.2</v>
@@ -5636,13 +5636,13 @@
         <v>19.5</v>
       </c>
       <c r="BW20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BX20" t="n">
         <v>27</v>
       </c>
       <c r="BY20" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BZ20" t="n">
         <v>17</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -5683,166 +5683,166 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="G21" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="H21" t="n">
         <v>2.64</v>
       </c>
       <c r="I21" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J21" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K21" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L21" t="n">
         <v>1.25</v>
       </c>
       <c r="M21" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P21" t="n">
         <v>2.42</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R21" t="n">
         <v>1.57</v>
       </c>
       <c r="S21" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T21" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="U21" t="n">
         <v>2.54</v>
       </c>
       <c r="V21" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W21" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="X21" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Y21" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="Z21" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AA21" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AB21" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AC21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD21" t="n">
         <v>13.5</v>
       </c>
       <c r="AE21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI21" t="n">
         <v>34</v>
       </c>
-      <c r="AF21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>75</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="AK21" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AL21" t="n">
         <v>32</v>
       </c>
       <c r="AM21" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="AN21" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AO21" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AP21" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AR21" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.4</v>
+        <v>32</v>
       </c>
       <c r="AT21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU21" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AV21" t="n">
         <v>11</v>
       </c>
       <c r="AW21" t="n">
-        <v>19</v>
+        <v>7.8</v>
       </c>
       <c r="AX21" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE21" t="n">
         <v>9</v>
       </c>
-      <c r="AZ21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BF21" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BH21" t="n">
         <v>4.4</v>
@@ -5851,62 +5851,62 @@
         <v>3.35</v>
       </c>
       <c r="BJ21" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK21" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="BN21" t="n">
         <v>6.2</v>
       </c>
       <c r="BO21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP21" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BR21" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BT21" t="n">
         <v>6.4</v>
       </c>
       <c r="BU21" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV21" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BW21" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BX21" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="BZ21" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="CA21" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -5937,76 +5937,76 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="G22" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="H22" t="n">
         <v>36</v>
       </c>
       <c r="I22" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="J22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K22" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="L22" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="M22" t="n">
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P22" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="R22" t="n">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="S22" t="n">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="T22" t="n">
-        <v>2.34</v>
+        <v>1.11</v>
       </c>
       <c r="U22" t="n">
-        <v>1.61</v>
+        <v>1.11</v>
       </c>
       <c r="V22" t="n">
         <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="X22" t="n">
         <v>950</v>
       </c>
       <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
         <v>950</v>
       </c>
-      <c r="Z22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AC22" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AD22" t="n">
         <v>950</v>
@@ -6015,10 +6015,10 @@
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>17.5</v>
+        <v>950</v>
       </c>
       <c r="AH22" t="n">
         <v>950</v>
@@ -6030,70 +6030,70 @@
         <v>9</v>
       </c>
       <c r="AK22" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="AL22" t="n">
         <v>250</v>
       </c>
       <c r="AM22" t="n">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.54</v>
+        <v>29</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>7.6</v>
+        <v>1.94</v>
       </c>
       <c r="AQ22" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="AR22" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.6</v>
+        <v>1.81</v>
       </c>
       <c r="AU22" t="n">
-        <v>7</v>
+        <v>1.82</v>
       </c>
       <c r="AV22" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AY22" t="n">
-        <v>6.8</v>
+        <v>1.7</v>
       </c>
       <c r="AZ22" t="n">
-        <v>7.8</v>
+        <v>1.91</v>
       </c>
       <c r="BA22" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.5</v>
+        <v>1.58</v>
       </c>
       <c r="BC22" t="n">
-        <v>5.8</v>
+        <v>1.7</v>
       </c>
       <c r="BD22" t="n">
-        <v>7.4</v>
+        <v>1.68</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.4</v>
+        <v>1.92</v>
       </c>
       <c r="BF22" t="n">
-        <v>2.3</v>
+        <v>1.56</v>
       </c>
       <c r="BG22" t="n">
         <v>10.5</v>
@@ -6102,65 +6102,65 @@
         <v>7.6</v>
       </c>
       <c r="BI22" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BJ22" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN22" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BP22" t="n">
         <v>5.2</v>
       </c>
       <c r="BQ22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT22" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ22" t="n">
         <v>5.5</v>
       </c>
       <c r="CA22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -6197,10 +6197,10 @@
         <v>15.5</v>
       </c>
       <c r="H23" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="I23" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="J23" t="n">
         <v>7.4</v>
@@ -6224,10 +6224,10 @@
         <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R23" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="S23" t="n">
         <v>2.08</v>
@@ -6239,7 +6239,7 @@
         <v>1.88</v>
       </c>
       <c r="V23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="W23" t="n">
         <v>1.07</v>
@@ -6251,13 +6251,13 @@
         <v>12.5</v>
       </c>
       <c r="Z23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA23" t="n">
         <v>10</v>
       </c>
-      <c r="AA23" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AB23" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AC23" t="n">
         <v>18.5</v>
@@ -6266,7 +6266,7 @@
         <v>12</v>
       </c>
       <c r="AE23" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AF23" t="n">
         <v>150</v>
@@ -6278,22 +6278,22 @@
         <v>36</v>
       </c>
       <c r="AI23" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AJ23" t="n">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="AK23" t="n">
         <v>210</v>
       </c>
       <c r="AL23" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AM23" t="n">
         <v>170</v>
       </c>
       <c r="AN23" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AO23" t="n">
         <v>3.6</v>
@@ -6323,7 +6323,7 @@
         <v>11.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY23" t="n">
         <v>40</v>
@@ -6332,22 +6332,22 @@
         <v>26</v>
       </c>
       <c r="BA23" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB23" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BF23" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG23" t="n">
         <v>3.2</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -6445,64 +6445,64 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="G24" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H24" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I24" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K24" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="L24" t="n">
         <v>1.25</v>
       </c>
       <c r="M24" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N24" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P24" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="R24" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="T24" t="n">
         <v>1.83</v>
       </c>
       <c r="U24" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V24" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W24" t="n">
         <v>3.15</v>
       </c>
       <c r="X24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y24" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="Z24" t="n">
         <v>540</v>
@@ -6514,16 +6514,16 @@
         <v>12.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD24" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AE24" t="n">
         <v>480</v>
       </c>
       <c r="AF24" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AG24" t="n">
         <v>12</v>
@@ -6538,10 +6538,10 @@
         <v>15.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL24" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AM24" t="n">
         <v>380</v>
@@ -6562,7 +6562,7 @@
         <v>6.4</v>
       </c>
       <c r="AS24" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT24" t="n">
         <v>8.199999999999999</v>
@@ -6577,16 +6577,16 @@
         <v>7</v>
       </c>
       <c r="AX24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AY24" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ24" t="n">
         <v>17</v>
       </c>
       <c r="BA24" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB24" t="n">
         <v>10</v>
@@ -6598,77 +6598,77 @@
         <v>16</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BG24" t="n">
         <v>14</v>
       </c>
       <c r="BH24" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI24" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BJ24" t="n">
         <v>12</v>
       </c>
       <c r="BK24" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN24" t="n">
         <v>4.2</v>
       </c>
       <c r="BO24" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BP24" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BQ24" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BR24" t="n">
         <v>24</v>
       </c>
       <c r="BS24" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BT24" t="n">
         <v>13</v>
       </c>
       <c r="BU24" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BZ24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CA24" t="n">
         <v>5.1</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G25" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="H25" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="I25" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="J25" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L25" t="n">
         <v>1.25</v>
@@ -6729,28 +6729,28 @@
         <v>1.22</v>
       </c>
       <c r="P25" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="R25" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S25" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="T25" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="U25" t="n">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="V25" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W25" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X25" t="n">
         <v>26</v>
@@ -6759,10 +6759,10 @@
         <v>14</v>
       </c>
       <c r="Z25" t="n">
-        <v>16</v>
+        <v>500</v>
       </c>
       <c r="AA25" t="n">
-        <v>42</v>
+        <v>900</v>
       </c>
       <c r="AB25" t="n">
         <v>23</v>
@@ -6771,7 +6771,7 @@
         <v>11.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="AE25" t="n">
         <v>65</v>
@@ -6807,34 +6807,34 @@
         <v>10.5</v>
       </c>
       <c r="AP25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS25" t="n">
         <v>15.5</v>
       </c>
-      <c r="AQ25" t="n">
+      <c r="AT25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV25" t="n">
         <v>4</v>
       </c>
-      <c r="AR25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AW25" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AX25" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AY25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ25" t="n">
         <v>12</v>
@@ -6843,28 +6843,28 @@
         <v>21</v>
       </c>
       <c r="BB25" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BC25" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BD25" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BE25" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BH25" t="n">
         <v>4.9</v>
       </c>
       <c r="BI25" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ25" t="n">
         <v>11</v>
@@ -6882,7 +6882,7 @@
         <v>9.4</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.15</v>
+        <v>6</v>
       </c>
       <c r="BP25" t="n">
         <v>38</v>
@@ -6900,7 +6900,7 @@
         <v>5.7</v>
       </c>
       <c r="BU25" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BV25" t="n">
         <v>15</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -6956,19 +6956,19 @@
         <v>1.41</v>
       </c>
       <c r="G26" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="J26" t="n">
         <v>4.5</v>
       </c>
       <c r="K26" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -6977,7 +6977,7 @@
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="O26" t="n">
         <v>1.13</v>
@@ -6989,28 +6989,28 @@
         <v>1.43</v>
       </c>
       <c r="R26" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S26" t="n">
-        <v>1.05</v>
+        <v>2.02</v>
       </c>
       <c r="T26" t="n">
         <v>1.37</v>
       </c>
       <c r="U26" t="n">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="V26" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="W26" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z26" t="n">
         <v>1000</v>
@@ -7061,58 +7061,58 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.05</v>
+        <v>4.2</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.05</v>
+        <v>4.2</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.05</v>
+        <v>4.2</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.05</v>
+        <v>4.2</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.05</v>
+        <v>4.2</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.05</v>
+        <v>4.2</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="BH26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -7210,10 +7210,10 @@
         <v>1.9</v>
       </c>
       <c r="G27" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H27" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I27" t="n">
         <v>4.3</v>
@@ -7222,7 +7222,7 @@
         <v>3.9</v>
       </c>
       <c r="K27" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L27" t="n">
         <v>1.25</v>
@@ -7237,10 +7237,10 @@
         <v>1.19</v>
       </c>
       <c r="P27" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R27" t="n">
         <v>1.6</v>
@@ -7258,7 +7258,7 @@
         <v>1.3</v>
       </c>
       <c r="W27" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X27" t="n">
         <v>90</v>
@@ -7318,7 +7318,7 @@
         <v>5.7</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AR27" t="n">
         <v>5.8</v>
@@ -7351,7 +7351,7 @@
         <v>6</v>
       </c>
       <c r="BB27" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BC27" t="n">
         <v>13</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="G28" t="n">
         <v>8.6</v>
@@ -7470,10 +7470,10 @@
         <v>1.41</v>
       </c>
       <c r="I28" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="J28" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K28" t="n">
         <v>5.9</v>
@@ -7491,7 +7491,7 @@
         <v>1.14</v>
       </c>
       <c r="P28" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
         <v>1.43</v>
@@ -7503,10 +7503,10 @@
         <v>2.12</v>
       </c>
       <c r="T28" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U28" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V28" t="n">
         <v>3.3</v>
@@ -7524,43 +7524,43 @@
         <v>11.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AB28" t="n">
         <v>46</v>
       </c>
       <c r="AC28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AD28" t="n">
         <v>10.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AF28" t="n">
-        <v>540</v>
+        <v>85</v>
       </c>
       <c r="AG28" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AH28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI28" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AJ28" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AK28" t="n">
-        <v>210</v>
+        <v>95</v>
       </c>
       <c r="AL28" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM28" t="n">
-        <v>320</v>
+        <v>85</v>
       </c>
       <c r="AN28" t="n">
         <v>80</v>
@@ -7569,7 +7569,7 @@
         <v>4.4</v>
       </c>
       <c r="AP28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ28" t="n">
         <v>12.5</v>
@@ -7587,7 +7587,7 @@
         <v>12</v>
       </c>
       <c r="AV28" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW28" t="n">
         <v>12</v>
@@ -7596,7 +7596,7 @@
         <v>30</v>
       </c>
       <c r="AY28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ28" t="n">
         <v>17</v>
@@ -7611,80 +7611,80 @@
         <v>29</v>
       </c>
       <c r="BD28" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="BE28" t="n">
         <v>30</v>
       </c>
       <c r="BF28" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BG28" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BH28" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BI28" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BJ28" t="n">
         <v>10</v>
       </c>
       <c r="BK28" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL28" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN28" t="n">
         <v>12</v>
       </c>
       <c r="BO28" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BP28" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BQ28" t="n">
         <v>10.5</v>
       </c>
       <c r="BR28" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT28" t="n">
         <v>4.5</v>
       </c>
       <c r="BU28" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BV28" t="n">
         <v>8</v>
       </c>
       <c r="BW28" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BX28" t="n">
         <v>21</v>
       </c>
       <c r="BY28" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ28" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="CA28" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
         <v>4.6</v>
       </c>
       <c r="G29" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H29" t="n">
         <v>1.85</v>
@@ -7727,13 +7727,13 @@
         <v>1.86</v>
       </c>
       <c r="J29" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K29" t="n">
         <v>4.2</v>
       </c>
       <c r="L29" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M29" t="n">
         <v>1.06</v>
@@ -7745,10 +7745,10 @@
         <v>1.32</v>
       </c>
       <c r="P29" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R29" t="n">
         <v>1.36</v>
@@ -7757,7 +7757,7 @@
         <v>3.5</v>
       </c>
       <c r="T29" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="U29" t="n">
         <v>2</v>
@@ -7766,7 +7766,7 @@
         <v>2.16</v>
       </c>
       <c r="W29" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X29" t="n">
         <v>18.5</v>
@@ -7778,7 +7778,7 @@
         <v>13.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AB29" t="n">
         <v>16.5</v>
@@ -7796,7 +7796,7 @@
         <v>38</v>
       </c>
       <c r="AG29" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AH29" t="n">
         <v>22</v>
@@ -7814,7 +7814,7 @@
         <v>70</v>
       </c>
       <c r="AM29" t="n">
-        <v>200</v>
+        <v>390</v>
       </c>
       <c r="AN29" t="n">
         <v>90</v>
@@ -7823,7 +7823,7 @@
         <v>13.5</v>
       </c>
       <c r="AP29" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AQ29" t="n">
         <v>7.4</v>
@@ -7850,28 +7850,28 @@
         <v>16</v>
       </c>
       <c r="AY29" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AZ29" t="n">
         <v>17.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB29" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF29" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG29" t="n">
         <v>9.199999999999999</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
         <v>2.28</v>
       </c>
       <c r="G30" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H30" t="n">
         <v>3.1</v>
@@ -8005,7 +8005,7 @@
         <v>1.63</v>
       </c>
       <c r="R30" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S30" t="n">
         <v>2.56</v>
@@ -8014,13 +8014,13 @@
         <v>1.57</v>
       </c>
       <c r="U30" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V30" t="n">
         <v>1.43</v>
       </c>
       <c r="W30" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="X30" t="n">
         <v>27</v>
@@ -8032,7 +8032,7 @@
         <v>30</v>
       </c>
       <c r="AA30" t="n">
-        <v>440</v>
+        <v>120</v>
       </c>
       <c r="AB30" t="n">
         <v>16</v>
@@ -8050,7 +8050,7 @@
         <v>20</v>
       </c>
       <c r="AG30" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH30" t="n">
         <v>18</v>
@@ -8077,7 +8077,7 @@
         <v>25</v>
       </c>
       <c r="AP30" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AQ30" t="n">
         <v>14.5</v>
@@ -8086,7 +8086,7 @@
         <v>11.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT30" t="n">
         <v>10</v>
@@ -8098,7 +8098,7 @@
         <v>10</v>
       </c>
       <c r="AW30" t="n">
-        <v>5.1</v>
+        <v>27</v>
       </c>
       <c r="AX30" t="n">
         <v>15</v>
@@ -8110,7 +8110,7 @@
         <v>11</v>
       </c>
       <c r="BA30" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="BB30" t="n">
         <v>5.1</v>
@@ -8122,7 +8122,7 @@
         <v>21</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF30" t="n">
         <v>9.4</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -8229,10 +8229,10 @@
         <v>1.73</v>
       </c>
       <c r="H31" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="I31" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J31" t="n">
         <v>3.4</v>
@@ -8244,7 +8244,7 @@
         <v>1.4</v>
       </c>
       <c r="M31" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N31" t="n">
         <v>2.84</v>
@@ -8253,10 +8253,10 @@
         <v>1.39</v>
       </c>
       <c r="P31" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R31" t="n">
         <v>1.26</v>
@@ -8265,10 +8265,10 @@
         <v>1.05</v>
       </c>
       <c r="T31" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U31" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="V31" t="n">
         <v>1.14</v>
@@ -8292,7 +8292,7 @@
         <v>27</v>
       </c>
       <c r="AC31" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="AD31" t="n">
         <v>950</v>
@@ -8313,7 +8313,7 @@
         <v>700</v>
       </c>
       <c r="AJ31" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AK31" t="n">
         <v>65</v>
@@ -8334,13 +8334,13 @@
         <v>6.2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.96</v>
+        <v>2.72</v>
       </c>
       <c r="AT31" t="n">
         <v>4.2</v>
@@ -8349,10 +8349,10 @@
         <v>5.1</v>
       </c>
       <c r="AV31" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AW31" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="AX31" t="n">
         <v>4.4</v>
@@ -8361,28 +8361,28 @@
         <v>6.2</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="BB31" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BC31" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BD31" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="BE31" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BF31" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="BG31" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="BH31" t="n">
         <v>5.1</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -8603,13 +8603,13 @@
         <v>4.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AW32" t="n">
         <v>7.2</v>
       </c>
       <c r="AX32" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY32" t="n">
         <v>6</v>
@@ -8642,7 +8642,7 @@
         <v>3</v>
       </c>
       <c r="BI32" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="BJ32" t="n">
         <v>11</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -8758,7 +8758,7 @@
         <v>3.45</v>
       </c>
       <c r="O33" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P33" t="n">
         <v>1.86</v>
@@ -8773,7 +8773,7 @@
         <v>3.4</v>
       </c>
       <c r="T33" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U33" t="n">
         <v>2.08</v>
@@ -8878,7 +8878,7 @@
         <v>4.9</v>
       </c>
       <c r="BC33" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD33" t="n">
         <v>4.6</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -8985,25 +8985,25 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G34" t="n">
         <v>2.06</v>
       </c>
       <c r="H34" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I34" t="n">
         <v>3.95</v>
       </c>
       <c r="J34" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K34" t="n">
         <v>3.95</v>
       </c>
       <c r="L34" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M34" t="n">
         <v>1.05</v>
@@ -9015,22 +9015,22 @@
         <v>1.25</v>
       </c>
       <c r="P34" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q34" t="n">
         <v>1.78</v>
       </c>
       <c r="R34" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S34" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="T34" t="n">
         <v>1.68</v>
       </c>
       <c r="U34" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V34" t="n">
         <v>1.33</v>
@@ -9039,10 +9039,10 @@
         <v>1.94</v>
       </c>
       <c r="X34" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y34" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="Z34" t="n">
         <v>30</v>
@@ -9063,7 +9063,7 @@
         <v>42</v>
       </c>
       <c r="AF34" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AG34" t="n">
         <v>10.5</v>
@@ -9078,7 +9078,7 @@
         <v>25</v>
       </c>
       <c r="AK34" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL34" t="n">
         <v>32</v>
@@ -9090,10 +9090,10 @@
         <v>12</v>
       </c>
       <c r="AO34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AP34" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ34" t="n">
         <v>15.5</v>
@@ -9102,7 +9102,7 @@
         <v>27</v>
       </c>
       <c r="AS34" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT34" t="n">
         <v>10.5</v>
@@ -9120,25 +9120,25 @@
         <v>12.5</v>
       </c>
       <c r="AY34" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ34" t="n">
         <v>15</v>
       </c>
       <c r="BA34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB34" t="n">
         <v>22</v>
       </c>
       <c r="BC34" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD34" t="n">
         <v>27</v>
       </c>
       <c r="BE34" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BF34" t="n">
         <v>10.5</v>
@@ -9150,7 +9150,7 @@
         <v>3.9</v>
       </c>
       <c r="BI34" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BJ34" t="n">
         <v>9.199999999999999</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -9239,19 +9239,19 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G35" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="H35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I35" t="n">
         <v>1.44</v>
       </c>
-      <c r="I35" t="n">
-        <v>1.51</v>
-      </c>
       <c r="J35" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="K35" t="n">
         <v>8.800000000000001</v>
@@ -9260,7 +9260,7 @@
         <v>1.18</v>
       </c>
       <c r="M35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N35" t="n">
         <v>1.1</v>
@@ -9269,43 +9269,43 @@
         <v>1.1</v>
       </c>
       <c r="P35" t="n">
-        <v>2.92</v>
+        <v>1.25</v>
       </c>
       <c r="Q35" t="n">
         <v>1.31</v>
       </c>
       <c r="R35" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="S35" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="T35" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="U35" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="V35" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="W35" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X35" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z35" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AA35" t="n">
         <v>500</v>
       </c>
       <c r="AB35" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="AC35" t="n">
         <v>42</v>
@@ -9314,16 +9314,16 @@
         <v>500</v>
       </c>
       <c r="AE35" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AF35" t="n">
-        <v>370</v>
+        <v>220</v>
       </c>
       <c r="AG35" t="n">
         <v>100</v>
       </c>
       <c r="AH35" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="AI35" t="n">
         <v>500</v>
@@ -9332,13 +9332,13 @@
         <v>1000</v>
       </c>
       <c r="AK35" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AL35" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AM35" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN35" t="n">
         <v>60</v>
@@ -9347,28 +9347,28 @@
         <v>15</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="AQ35" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AR35" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AS35" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT35" t="n">
         <v>4.2</v>
       </c>
       <c r="AU35" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW35" t="n">
         <v>5.7</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>5.5</v>
       </c>
       <c r="AX35" t="n">
         <v>4.2</v>
@@ -9377,10 +9377,10 @@
         <v>4.2</v>
       </c>
       <c r="AZ35" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="BB35" t="n">
         <v>4.2</v>
@@ -9392,67 +9392,67 @@
         <v>4.2</v>
       </c>
       <c r="BE35" t="n">
-        <v>2.36</v>
+        <v>1.69</v>
       </c>
       <c r="BF35" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="BH35" t="n">
         <v>1000</v>
       </c>
       <c r="BI35" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="BJ35" t="n">
         <v>1000</v>
       </c>
       <c r="BK35" t="n">
-        <v>1.66</v>
+        <v>1.41</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="BN35" t="n">
         <v>1000</v>
       </c>
       <c r="BO35" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="BP35" t="n">
         <v>1000</v>
       </c>
       <c r="BQ35" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="BR35" t="n">
         <v>1000</v>
       </c>
       <c r="BS35" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="BT35" t="n">
         <v>1000</v>
       </c>
       <c r="BU35" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="BV35" t="n">
         <v>1000</v>
       </c>
       <c r="BW35" t="n">
-        <v>1.96</v>
+        <v>1.63</v>
       </c>
       <c r="BX35" t="n">
         <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="BZ35" t="n">
         <v>0</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G36" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H36" t="n">
         <v>6.8</v>
@@ -9544,7 +9544,7 @@
         <v>1.11</v>
       </c>
       <c r="W36" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="X36" t="n">
         <v>15.5</v>
@@ -9622,7 +9622,7 @@
         <v>5</v>
       </c>
       <c r="AW36" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX36" t="n">
         <v>6.6</v>
@@ -9643,7 +9643,7 @@
         <v>13</v>
       </c>
       <c r="BD36" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE36" t="n">
         <v>5.2</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -9747,22 +9747,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G37" t="n">
         <v>5.4</v>
       </c>
       <c r="H37" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="I37" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="J37" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K37" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L37" t="n">
         <v>1.54</v>
@@ -9795,7 +9795,7 @@
         <v>1.73</v>
       </c>
       <c r="V37" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W37" t="n">
         <v>1.23</v>
@@ -9873,7 +9873,7 @@
         <v>7.6</v>
       </c>
       <c r="AV37" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AW37" t="n">
         <v>18</v>
@@ -9888,7 +9888,7 @@
         <v>14.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB37" t="n">
         <v>5.5</v>
@@ -9900,7 +9900,7 @@
         <v>5.4</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF37" t="n">
         <v>5.5</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -10046,7 +10046,7 @@
         <v>2.02</v>
       </c>
       <c r="U38" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="V38" t="n">
         <v>1.19</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -10273,25 +10273,25 @@
         <v>3.3</v>
       </c>
       <c r="L39" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M39" t="n">
         <v>1.12</v>
       </c>
       <c r="N39" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O39" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P39" t="n">
         <v>1.53</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="R39" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S39" t="n">
         <v>5.5</v>
@@ -10300,7 +10300,7 @@
         <v>2.14</v>
       </c>
       <c r="U39" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="V39" t="n">
         <v>1.45</v>
@@ -10309,7 +10309,7 @@
         <v>1.57</v>
       </c>
       <c r="X39" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y39" t="n">
         <v>9.199999999999999</v>
@@ -10357,7 +10357,7 @@
         <v>210</v>
       </c>
       <c r="AN39" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO39" t="n">
         <v>65</v>
@@ -10372,7 +10372,7 @@
         <v>16.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT39" t="n">
         <v>7</v>
@@ -10384,7 +10384,7 @@
         <v>12.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX39" t="n">
         <v>13.5</v>
@@ -10396,28 +10396,28 @@
         <v>19.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB39" t="n">
         <v>38</v>
       </c>
       <c r="BC39" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BD39" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE39" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF39" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG39" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH39" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BI39" t="n">
         <v>2.3</v>
@@ -10426,13 +10426,13 @@
         <v>11.5</v>
       </c>
       <c r="BK39" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN39" t="n">
         <v>5.7</v>
@@ -10444,13 +10444,13 @@
         <v>26</v>
       </c>
       <c r="BQ39" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR39" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS39" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT39" t="n">
         <v>6.2</v>
@@ -10462,23 +10462,23 @@
         <v>32</v>
       </c>
       <c r="BW39" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX39" t="n">
         <v>55</v>
       </c>
       <c r="BY39" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ39" t="n">
         <v>55</v>
       </c>
       <c r="CA39" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -10509,22 +10509,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="G40" t="n">
-        <v>1000</v>
+        <v>1.66</v>
       </c>
       <c r="H40" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="I40" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="J40" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="K40" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
@@ -10533,22 +10533,22 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="O40" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P40" t="n">
-        <v>1.24</v>
+        <v>1.86</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.21</v>
+        <v>1.69</v>
       </c>
       <c r="R40" t="n">
         <v>1.13</v>
       </c>
       <c r="S40" t="n">
-        <v>1.21</v>
+        <v>1.69</v>
       </c>
       <c r="T40" t="n">
         <v>1.01</v>
@@ -10560,7 +10560,7 @@
         <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
         <v>1.09</v>
       </c>
       <c r="G41" t="n">
-        <v>990</v>
+        <v>600</v>
       </c>
       <c r="H41" t="n">
         <v>1.09</v>
@@ -10778,7 +10778,7 @@
         <v>1.09</v>
       </c>
       <c r="K41" t="n">
-        <v>440</v>
+        <v>100</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
         <v>5.6</v>
       </c>
       <c r="J42" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K42" t="n">
         <v>5</v>
@@ -11050,7 +11050,7 @@
         <v>2.12</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="R42" t="n">
         <v>1.44</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-20 19:23:18</t>
+          <t>2026-05-20 21:39:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="G2" t="n">
         <v>1.34</v>
@@ -869,10 +869,10 @@
         <v>16.5</v>
       </c>
       <c r="J2" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K2" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="L2" t="n">
         <v>1.31</v>
@@ -881,37 +881,37 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="U2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V2" t="n">
         <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="X2" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="Y2" t="n">
         <v>40</v>
@@ -923,10 +923,10 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AD2" t="n">
         <v>150</v>
@@ -935,7 +935,7 @@
         <v>410</v>
       </c>
       <c r="AF2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AG2" t="n">
         <v>11.5</v>
@@ -950,43 +950,43 @@
         <v>9.4</v>
       </c>
       <c r="AK2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL2" t="n">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AN2" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15.5</v>
+        <v>27</v>
       </c>
       <c r="AR2" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT2" t="n">
         <v>6.4</v>
       </c>
       <c r="AU2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW2" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="AX2" t="n">
         <v>6.2</v>
@@ -995,37 +995,37 @@
         <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="BA2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB2" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB2" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.4</v>
+        <v>44</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="BJ2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BK2" t="n">
         <v>6.4</v>
@@ -1037,13 +1037,13 @@
         <v>10.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BO2" t="n">
         <v>2.76</v>
       </c>
       <c r="BP2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BQ2" t="n">
         <v>5.7</v>
@@ -1058,19 +1058,19 @@
         <v>17</v>
       </c>
       <c r="BU2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>15.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="H3" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="K3" t="n">
         <v>5.9</v>
@@ -1135,58 +1135,58 @@
         <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O3" t="n">
         <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="T3" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W3" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="X3" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="Y3" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="Z3" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AA3" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AB3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD3" t="n">
         <v>75</v>
       </c>
       <c r="AE3" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AF3" t="n">
         <v>9.199999999999999</v>
@@ -1201,7 +1201,7 @@
         <v>260</v>
       </c>
       <c r="AJ3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK3" t="n">
         <v>15.5</v>
@@ -1213,22 +1213,22 @@
         <v>150</v>
       </c>
       <c r="AN3" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AP3" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AQ3" t="n">
         <v>14.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT3" t="n">
         <v>8</v>
@@ -1240,19 +1240,19 @@
         <v>16</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX3" t="n">
         <v>7</v>
       </c>
       <c r="AY3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
         <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB3" t="n">
         <v>9.6</v>
@@ -1261,80 +1261,80 @@
         <v>12.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>16</v>
+        <v>7.2</v>
       </c>
       <c r="BE3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="BJ3" t="n">
         <v>12</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="BP3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BR3" t="n">
         <v>24</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT3" t="n">
         <v>13.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BZ3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L4" t="n">
         <v>1.42</v>
@@ -1398,19 +1398,19 @@
         <v>1.93</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R4" t="n">
         <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
         <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V4" t="n">
         <v>1.34</v>
@@ -1425,13 +1425,13 @@
         <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AA4" t="n">
         <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="AC4" t="n">
         <v>42</v>
@@ -1449,7 +1449,7 @@
         <v>36</v>
       </c>
       <c r="AH4" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AI4" t="n">
         <v>500</v>
@@ -1461,16 +1461,16 @@
         <v>500</v>
       </c>
       <c r="AL4" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AO4" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP4" t="n">
         <v>7</v>
@@ -1479,10 +1479,10 @@
         <v>7.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="AT4" t="n">
         <v>7.2</v>
@@ -1494,37 +1494,37 @@
         <v>8.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AX4" t="n">
         <v>7</v>
       </c>
       <c r="AY4" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AZ4" t="n">
         <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.2</v>
+        <v>3.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF4" t="n">
         <v>11</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH4" t="n">
         <v>3.4</v>
@@ -1560,7 +1560,7 @@
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
@@ -1572,7 +1572,7 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.76</v>
+        <v>1.59</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1649,10 @@
         <v>1.22</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R5" t="n">
         <v>1.48</v>
@@ -1673,28 +1673,28 @@
         <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AB5" t="n">
         <v>42</v>
       </c>
       <c r="AC5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AF5" t="n">
         <v>540</v>
@@ -1730,7 +1730,7 @@
         <v>18</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR5" t="n">
         <v>7.2</v>
@@ -1739,52 +1739,52 @@
         <v>9.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AU5" t="n">
         <v>10.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW5" t="n">
         <v>12.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="AY5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>16</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BA5" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BF5" t="n">
         <v>15</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH5" t="n">
         <v>4.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ5" t="n">
         <v>12.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         <v>1.24</v>
       </c>
       <c r="H6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="I6" t="n">
         <v>24</v>
@@ -1906,7 +1906,7 @@
         <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="R6" t="n">
         <v>1.55</v>
@@ -1918,7 +1918,7 @@
         <v>2.42</v>
       </c>
       <c r="U6" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="V6" t="n">
         <v>1.04</v>
@@ -1927,7 +1927,7 @@
         <v>5.3</v>
       </c>
       <c r="X6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y6" t="n">
         <v>60</v>
@@ -1939,22 +1939,22 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AD6" t="n">
         <v>80</v>
       </c>
       <c r="AE6" t="n">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH6" t="n">
         <v>55</v>
@@ -1963,10 +1963,10 @@
         <v>300</v>
       </c>
       <c r="AJ6" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AK6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL6" t="n">
         <v>60</v>
@@ -1981,16 +1981,16 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.4</v>
+        <v>36</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AT6" t="n">
         <v>7.6</v>
@@ -1999,46 +1999,46 @@
         <v>12</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AX6" t="n">
         <v>6.2</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.3</v>
+        <v>32</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB6" t="n">
         <v>7.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.4</v>
+        <v>36</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF6" t="n">
         <v>3.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="BH6" t="n">
         <v>4.6</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="BJ6" t="n">
         <v>16</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
         <v>2.52</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="P7" t="n">
         <v>1.52</v>
@@ -2229,34 +2229,34 @@
         <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AO7" t="n">
-        <v>85</v>
+        <v>600</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT7" t="n">
         <v>3.45</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AV7" t="n">
         <v>4.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX7" t="n">
         <v>4.3</v>
@@ -2265,22 +2265,22 @@
         <v>4.1</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC7" t="n">
         <v>5.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF7" t="n">
         <v>5.2</v>
@@ -2304,10 +2304,10 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO7" t="n">
         <v>4</v>
@@ -2322,7 +2322,7 @@
         <v>46</v>
       </c>
       <c r="BS7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BT7" t="n">
         <v>7.6</v>
@@ -2334,23 +2334,23 @@
         <v>36</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BX7" t="n">
         <v>60</v>
       </c>
       <c r="BY7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
         <v>5.7</v>
       </c>
-      <c r="BZ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>5.6</v>
-      </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
         <v>2.06</v>
       </c>
       <c r="V8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
         <v>1.83</v>
@@ -2489,7 +2489,7 @@
         <v>110</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AQ8" t="n">
         <v>5.9</v>
@@ -2540,7 +2540,7 @@
         <v>5.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH8" t="n">
         <v>3.7</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="G9" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H9" t="n">
         <v>6</v>
@@ -2647,7 +2647,7 @@
         <v>7</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
         <v>4.6</v>
@@ -2659,40 +2659,40 @@
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
         <v>1.26</v>
       </c>
       <c r="P9" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U9" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V9" t="n">
         <v>1.17</v>
       </c>
       <c r="W9" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X9" t="n">
         <v>500</v>
       </c>
       <c r="Y9" t="n">
-        <v>950</v>
+        <v>29</v>
       </c>
       <c r="Z9" t="n">
         <v>500</v>
@@ -2704,7 +2704,7 @@
         <v>11.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
         <v>500</v>
@@ -2737,7 +2737,7 @@
         <v>700</v>
       </c>
       <c r="AN9" t="n">
-        <v>29</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO9" t="n">
         <v>700</v>
@@ -2749,43 +2749,43 @@
         <v>11.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV9" t="n">
         <v>13</v>
       </c>
       <c r="AW9" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AY9" t="n">
         <v>5.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="BA9" t="n">
         <v>28</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="BC9" t="n">
         <v>8.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BE9" t="n">
         <v>24</v>
@@ -2794,13 +2794,13 @@
         <v>7.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="BH9" t="n">
         <v>3.85</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="BJ9" t="n">
         <v>11</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -3146,16 +3146,16 @@
         <v>2.28</v>
       </c>
       <c r="G11" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H11" t="n">
         <v>3.45</v>
       </c>
       <c r="I11" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J11" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K11" t="n">
         <v>3.45</v>
@@ -3182,19 +3182,19 @@
         <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T11" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U11" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
         <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X11" t="n">
         <v>12</v>
@@ -3203,7 +3203,7 @@
         <v>12.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AA11" t="n">
         <v>160</v>
@@ -3215,7 +3215,7 @@
         <v>7.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE11" t="n">
         <v>55</v>
@@ -3254,13 +3254,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AR11" t="n">
         <v>21</v>
       </c>
       <c r="AS11" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT11" t="n">
         <v>8</v>
@@ -3272,7 +3272,7 @@
         <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX11" t="n">
         <v>11</v>
@@ -3281,28 +3281,28 @@
         <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BF11" t="n">
         <v>19</v>
       </c>
       <c r="BG11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH11" t="n">
         <v>3.25</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -3397,25 +3397,25 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="G12" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="H12" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I12" t="n">
         <v>3.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K12" t="n">
         <v>3.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
@@ -3427,7 +3427,7 @@
         <v>1.39</v>
       </c>
       <c r="P12" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
         <v>2.1</v>
@@ -3436,7 +3436,7 @@
         <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="T12" t="n">
         <v>1.82</v>
@@ -3508,13 +3508,13 @@
         <v>10</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR12" t="n">
         <v>16.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="AT12" t="n">
         <v>8.800000000000001</v>
@@ -3538,25 +3538,25 @@
         <v>15.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.6</v>
+        <v>23</v>
       </c>
       <c r="BB12" t="n">
-        <v>32</v>
+        <v>18.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.6</v>
+        <v>23</v>
       </c>
       <c r="BE12" t="n">
         <v>26</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="BG12" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="BH12" t="n">
         <v>3.3</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>3.7</v>
       </c>
       <c r="J13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K13" t="n">
         <v>6.2</v>
@@ -3681,7 +3681,7 @@
         <v>1.06</v>
       </c>
       <c r="P13" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="Q13" t="n">
         <v>1.19</v>
@@ -3690,7 +3690,7 @@
         <v>2.6</v>
       </c>
       <c r="S13" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T13" t="n">
         <v>1.27</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G14" t="n">
         <v>3.5</v>
@@ -3929,28 +3929,28 @@
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="O14" t="n">
         <v>1.31</v>
       </c>
       <c r="P14" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
         <v>1.95</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
         <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="U14" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="V14" t="n">
         <v>1.72</v>
@@ -3974,7 +3974,7 @@
         <v>14.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="AD14" t="n">
         <v>11</v>
@@ -4016,7 +4016,7 @@
         <v>13.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR14" t="n">
         <v>13.5</v>
@@ -4058,7 +4058,7 @@
         <v>40</v>
       </c>
       <c r="BE14" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BF14" t="n">
         <v>30</v>
@@ -4106,7 +4106,7 @@
         <v>5.3</v>
       </c>
       <c r="BU14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV14" t="n">
         <v>21</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G15" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H15" t="n">
         <v>4.1</v>
@@ -4189,7 +4189,7 @@
         <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
         <v>1.63</v>
@@ -4198,19 +4198,19 @@
         <v>1.6</v>
       </c>
       <c r="S15" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U15" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W15" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X15" t="n">
         <v>24</v>
@@ -4219,16 +4219,16 @@
         <v>21</v>
       </c>
       <c r="Z15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA15" t="n">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="AB15" t="n">
         <v>13</v>
       </c>
       <c r="AC15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD15" t="n">
         <v>17.5</v>
@@ -4237,7 +4237,7 @@
         <v>44</v>
       </c>
       <c r="AF15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG15" t="n">
         <v>10.5</v>
@@ -4261,7 +4261,7 @@
         <v>65</v>
       </c>
       <c r="AN15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO15" t="n">
         <v>34</v>
@@ -4285,7 +4285,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
         <v>38</v>
@@ -4294,7 +4294,7 @@
         <v>13</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
         <v>14</v>
@@ -4306,7 +4306,7 @@
         <v>19</v>
       </c>
       <c r="BC15" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD15" t="n">
         <v>24</v>
@@ -4330,13 +4330,13 @@
         <v>9</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BL15" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="BM15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN15" t="n">
         <v>5</v>
@@ -4348,13 +4348,13 @@
         <v>12.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR15" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BS15" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT15" t="n">
         <v>7.8</v>
@@ -4363,26 +4363,26 @@
         <v>6</v>
       </c>
       <c r="BV15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BX15" t="n">
         <v>40</v>
       </c>
       <c r="BY15" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BZ15" t="n">
         <v>16</v>
       </c>
       <c r="CA15" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G16" t="n">
         <v>2.42</v>
@@ -4425,7 +4425,7 @@
         <v>4.3</v>
       </c>
       <c r="J16" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K16" t="n">
         <v>3.1</v>
@@ -4482,7 +4482,7 @@
         <v>6.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD16" t="n">
         <v>21</v>
@@ -4497,7 +4497,7 @@
         <v>13</v>
       </c>
       <c r="AH16" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AI16" t="n">
         <v>500</v>
@@ -4521,7 +4521,7 @@
         <v>500</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ16" t="n">
         <v>8.800000000000001</v>
@@ -4530,7 +4530,7 @@
         <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT16" t="n">
         <v>5.9</v>
@@ -4542,7 +4542,7 @@
         <v>14.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX16" t="n">
         <v>10</v>
@@ -4554,25 +4554,25 @@
         <v>21</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BC16" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BD16" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BE16" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BF16" t="n">
         <v>32</v>
       </c>
       <c r="BG16" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BH16" t="n">
         <v>2.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
         <v>32</v>
       </c>
       <c r="J18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="K18" t="n">
         <v>12</v>
@@ -4972,7 +4972,7 @@
         <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="X18" t="n">
         <v>950</v>
@@ -5002,7 +5002,7 @@
         <v>7.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH18" t="n">
         <v>950</v>
@@ -5011,10 +5011,10 @@
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AK18" t="n">
-        <v>29</v>
+        <v>970</v>
       </c>
       <c r="AL18" t="n">
         <v>250</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G19" t="n">
         <v>3.05</v>
@@ -5190,7 +5190,7 @@
         <v>3.35</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L19" t="n">
         <v>1.45</v>
@@ -5217,13 +5217,13 @@
         <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U19" t="n">
         <v>2.12</v>
       </c>
       <c r="V19" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W19" t="n">
         <v>1.49</v>
@@ -5235,31 +5235,31 @@
         <v>10.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA19" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AB19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC19" t="n">
         <v>7.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE19" t="n">
         <v>32</v>
       </c>
       <c r="AF19" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI19" t="n">
         <v>46</v>
@@ -5280,7 +5280,7 @@
         <v>34</v>
       </c>
       <c r="AO19" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AP19" t="n">
         <v>11.5</v>
@@ -5313,16 +5313,16 @@
         <v>11.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA19" t="n">
         <v>40</v>
       </c>
       <c r="BB19" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BC19" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="BD19" t="n">
         <v>42</v>
@@ -5337,25 +5337,25 @@
         <v>23</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BJ19" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BN19" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO19" t="n">
         <v>4.5</v>
@@ -5364,13 +5364,13 @@
         <v>32</v>
       </c>
       <c r="BQ19" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT19" t="n">
         <v>5.6</v>
@@ -5382,23 +5382,23 @@
         <v>25</v>
       </c>
       <c r="BW19" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BX19" t="n">
         <v>44</v>
       </c>
       <c r="BY19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BZ19" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="CA19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -5432,16 +5432,16 @@
         <v>2.92</v>
       </c>
       <c r="G20" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="H20" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="I20" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="J20" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K20" t="n">
         <v>4.3</v>
@@ -5453,7 +5453,7 @@
         <v>1.03</v>
       </c>
       <c r="N20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O20" t="n">
         <v>1.16</v>
@@ -5462,7 +5462,7 @@
         <v>2.76</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R20" t="n">
         <v>1.74</v>
@@ -5474,16 +5474,16 @@
         <v>1.45</v>
       </c>
       <c r="U20" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="V20" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W20" t="n">
         <v>1.45</v>
       </c>
       <c r="X20" t="n">
-        <v>90</v>
+        <v>950</v>
       </c>
       <c r="Y20" t="n">
         <v>19.5</v>
@@ -5528,7 +5528,7 @@
         <v>34</v>
       </c>
       <c r="AM20" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN20" t="n">
         <v>17.5</v>
@@ -5546,7 +5546,7 @@
         <v>5.6</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AT20" t="n">
         <v>5.4</v>
@@ -5573,16 +5573,16 @@
         <v>5.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BC20" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BD20" t="n">
         <v>5.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BF20" t="n">
         <v>4.7</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G21" t="n">
         <v>2.74</v>
@@ -5698,7 +5698,7 @@
         <v>3.75</v>
       </c>
       <c r="K21" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L21" t="n">
         <v>1.25</v>
@@ -5833,7 +5833,7 @@
         <v>8</v>
       </c>
       <c r="BD21" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="BE21" t="n">
         <v>9</v>
@@ -5848,7 +5848,7 @@
         <v>4.4</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ21" t="n">
         <v>8.800000000000001</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -5937,64 +5937,64 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="G22" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="H22" t="n">
         <v>36</v>
       </c>
       <c r="I22" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J22" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K22" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="L22" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="M22" t="n">
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P22" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="R22" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="S22" t="n">
-        <v>1.46</v>
+        <v>1.9</v>
       </c>
       <c r="T22" t="n">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="U22" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="V22" t="n">
         <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="X22" t="n">
         <v>950</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z22" t="n">
         <v>1000</v>
@@ -6003,10 +6003,10 @@
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>950</v>
+        <v>15</v>
       </c>
       <c r="AC22" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AD22" t="n">
         <v>950</v>
@@ -6015,10 +6015,10 @@
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AG22" t="n">
-        <v>950</v>
+        <v>17.5</v>
       </c>
       <c r="AH22" t="n">
         <v>950</v>
@@ -6027,97 +6027,97 @@
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AK22" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AL22" t="n">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN22" t="n">
-        <v>29</v>
+        <v>2.78</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.94</v>
+        <v>6.8</v>
       </c>
       <c r="AQ22" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS22" t="n">
         <v>4.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.81</v>
+        <v>11</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.82</v>
+        <v>6.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="AW22" t="n">
         <v>4.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.7</v>
+        <v>5.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.91</v>
+        <v>7</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.58</v>
+        <v>7.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.7</v>
+        <v>5.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.68</v>
+        <v>40</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.92</v>
+        <v>7.8</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.56</v>
+        <v>2.52</v>
       </c>
       <c r="BG22" t="n">
         <v>10.5</v>
       </c>
       <c r="BH22" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BI22" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BJ22" t="n">
         <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN22" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BO22" t="n">
         <v>3</v>
@@ -6132,35 +6132,35 @@
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT22" t="n">
         <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ22" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="CA22" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -6197,16 +6197,16 @@
         <v>15.5</v>
       </c>
       <c r="H23" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="I23" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="J23" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="K23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="L23" t="n">
         <v>1.23</v>
@@ -6221,7 +6221,7 @@
         <v>1.14</v>
       </c>
       <c r="P23" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="Q23" t="n">
         <v>1.43</v>
@@ -6230,19 +6230,19 @@
         <v>1.78</v>
       </c>
       <c r="S23" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T23" t="n">
         <v>1.98</v>
       </c>
       <c r="U23" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
         <v>38</v>
@@ -6266,28 +6266,28 @@
         <v>12</v>
       </c>
       <c r="AE23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AF23" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AG23" t="n">
         <v>50</v>
       </c>
       <c r="AH23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI23" t="n">
         <v>36</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>42</v>
       </c>
       <c r="AJ23" t="n">
         <v>720</v>
       </c>
       <c r="AK23" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="AL23" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AM23" t="n">
         <v>170</v>
@@ -6302,7 +6302,7 @@
         <v>28</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR23" t="n">
         <v>8.199999999999999</v>
@@ -6323,7 +6323,7 @@
         <v>11.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AY23" t="n">
         <v>40</v>
@@ -6332,19 +6332,19 @@
         <v>26</v>
       </c>
       <c r="BA23" t="n">
-        <v>9.6</v>
+        <v>26</v>
       </c>
       <c r="BB23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC23" t="n">
         <v>10.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF23" t="n">
         <v>12.5</v>
@@ -6362,31 +6362,31 @@
         <v>13</v>
       </c>
       <c r="BK23" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN23" t="n">
         <v>19.5</v>
       </c>
       <c r="BO23" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BR23" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT23" t="n">
         <v>4</v>
@@ -6401,20 +6401,20 @@
         <v>5.1</v>
       </c>
       <c r="BX23" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BY23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ23" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="CA23" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -6448,19 +6448,19 @@
         <v>1.4</v>
       </c>
       <c r="G24" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="H24" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="I24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J24" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K24" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="L24" t="n">
         <v>1.25</v>
@@ -6496,7 +6496,7 @@
         <v>1.12</v>
       </c>
       <c r="W24" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="X24" t="n">
         <v>28</v>
@@ -6535,7 +6535,7 @@
         <v>390</v>
       </c>
       <c r="AJ24" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK24" t="n">
         <v>17</v>
@@ -6547,7 +6547,7 @@
         <v>380</v>
       </c>
       <c r="AN24" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AO24" t="n">
         <v>120</v>
@@ -6559,10 +6559,10 @@
         <v>14</v>
       </c>
       <c r="AR24" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AS24" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT24" t="n">
         <v>8.199999999999999</v>
@@ -6571,10 +6571,10 @@
         <v>10.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AW24" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AX24" t="n">
         <v>8.4</v>
@@ -6583,28 +6583,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ24" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BA24" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB24" t="n">
         <v>10</v>
       </c>
       <c r="BC24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD24" t="n">
         <v>16</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF24" t="n">
         <v>4.8</v>
       </c>
       <c r="BG24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BH24" t="n">
         <v>4.5</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -6702,25 +6702,25 @@
         <v>4.2</v>
       </c>
       <c r="G25" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H25" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="I25" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L25" t="n">
         <v>1.25</v>
       </c>
       <c r="M25" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N25" t="n">
         <v>4.8</v>
@@ -6735,19 +6735,19 @@
         <v>1.55</v>
       </c>
       <c r="R25" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S25" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="T25" t="n">
         <v>1.62</v>
       </c>
       <c r="U25" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="V25" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="W25" t="n">
         <v>1.28</v>
@@ -6759,7 +6759,7 @@
         <v>14</v>
       </c>
       <c r="Z25" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AA25" t="n">
         <v>900</v>
@@ -6771,7 +6771,7 @@
         <v>11.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE25" t="n">
         <v>65</v>
@@ -6807,34 +6807,34 @@
         <v>10.5</v>
       </c>
       <c r="AP25" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS25" t="n">
-        <v>15.5</v>
+        <v>5</v>
       </c>
       <c r="AT25" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV25" t="n">
         <v>4</v>
       </c>
       <c r="AW25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY25" t="n">
         <v>13</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>12.5</v>
       </c>
       <c r="AZ25" t="n">
         <v>12</v>
@@ -6843,25 +6843,25 @@
         <v>21</v>
       </c>
       <c r="BB25" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD25" t="n">
         <v>5.9</v>
       </c>
-      <c r="BC25" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BE25" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF25" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH25" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BI25" t="n">
         <v>3.3</v>
@@ -6870,13 +6870,13 @@
         <v>11</v>
       </c>
       <c r="BK25" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BN25" t="n">
         <v>9.4</v>
@@ -6888,41 +6888,41 @@
         <v>38</v>
       </c>
       <c r="BQ25" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BT25" t="n">
         <v>5.7</v>
       </c>
       <c r="BU25" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BV25" t="n">
         <v>15</v>
       </c>
       <c r="BW25" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BX25" t="n">
         <v>27</v>
       </c>
       <c r="BY25" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BZ25" t="n">
         <v>20</v>
       </c>
       <c r="CA25" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>4.5</v>
       </c>
       <c r="K26" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -6977,13 +6977,13 @@
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>2.42</v>
+        <v>1.1</v>
       </c>
       <c r="O26" t="n">
         <v>1.13</v>
       </c>
       <c r="P26" t="n">
-        <v>2.42</v>
+        <v>1.25</v>
       </c>
       <c r="Q26" t="n">
         <v>1.43</v>
@@ -6995,7 +6995,7 @@
         <v>2.02</v>
       </c>
       <c r="T26" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="U26" t="n">
         <v>1.8</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -7216,10 +7216,10 @@
         <v>3.85</v>
       </c>
       <c r="I27" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J27" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K27" t="n">
         <v>4.7</v>
@@ -7255,7 +7255,7 @@
         <v>2.44</v>
       </c>
       <c r="V27" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W27" t="n">
         <v>2</v>
@@ -7264,7 +7264,7 @@
         <v>90</v>
       </c>
       <c r="Y27" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="Z27" t="n">
         <v>500</v>
@@ -7273,19 +7273,19 @@
         <v>900</v>
       </c>
       <c r="AB27" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AC27" t="n">
         <v>42</v>
       </c>
       <c r="AD27" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE27" t="n">
         <v>500</v>
       </c>
       <c r="AF27" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG27" t="n">
         <v>13</v>
@@ -7315,16 +7315,16 @@
         <v>500</v>
       </c>
       <c r="AP27" t="n">
-        <v>5.7</v>
+        <v>20</v>
       </c>
       <c r="AQ27" t="n">
         <v>5.7</v>
       </c>
       <c r="AR27" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT27" t="n">
         <v>10.5</v>
@@ -7336,7 +7336,7 @@
         <v>13</v>
       </c>
       <c r="AW27" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX27" t="n">
         <v>11.5</v>
@@ -7348,10 +7348,10 @@
         <v>11.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB27" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BC27" t="n">
         <v>13</v>
@@ -7360,7 +7360,7 @@
         <v>19.5</v>
       </c>
       <c r="BE27" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF27" t="n">
         <v>6.2</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -7461,25 +7461,25 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="I28" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="J28" t="n">
         <v>5.7</v>
       </c>
       <c r="K28" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L28" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="M28" t="n">
         <v>1.02</v>
@@ -7491,28 +7491,28 @@
         <v>1.14</v>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R28" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="S28" t="n">
         <v>2.12</v>
       </c>
       <c r="T28" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U28" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V28" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="W28" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X28" t="n">
         <v>34</v>
@@ -7521,13 +7521,13 @@
         <v>16</v>
       </c>
       <c r="Z28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AB28" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AC28" t="n">
         <v>14</v>
@@ -7539,52 +7539,52 @@
         <v>16</v>
       </c>
       <c r="AF28" t="n">
-        <v>85</v>
+        <v>540</v>
       </c>
       <c r="AG28" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AH28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI28" t="n">
         <v>29</v>
       </c>
       <c r="AJ28" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AK28" t="n">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AL28" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM28" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN28" t="n">
         <v>85</v>
       </c>
-      <c r="AN28" t="n">
-        <v>80</v>
-      </c>
       <c r="AO28" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AP28" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="AQ28" t="n">
         <v>12.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AT28" t="n">
         <v>34</v>
       </c>
       <c r="AU28" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AV28" t="n">
         <v>10</v>
@@ -7596,13 +7596,13 @@
         <v>30</v>
       </c>
       <c r="AY28" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="AZ28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA28" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB28" t="n">
         <v>12</v>
@@ -7611,7 +7611,7 @@
         <v>29</v>
       </c>
       <c r="BD28" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="BE28" t="n">
         <v>30</v>
@@ -7620,19 +7620,19 @@
         <v>55</v>
       </c>
       <c r="BG28" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BH28" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BI28" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BJ28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK28" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
@@ -7644,25 +7644,25 @@
         <v>12</v>
       </c>
       <c r="BO28" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BP28" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BQ28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR28" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS28" t="n">
         <v>10.5</v>
       </c>
       <c r="BT28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BU28" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BV28" t="n">
         <v>8</v>
@@ -7677,14 +7677,14 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BZ28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CA28" t="n">
         <v>5.5</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -7715,19 +7715,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G29" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="H29" t="n">
         <v>1.85</v>
       </c>
       <c r="I29" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K29" t="n">
         <v>4.2</v>
@@ -7739,7 +7739,7 @@
         <v>1.06</v>
       </c>
       <c r="N29" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O29" t="n">
         <v>1.32</v>
@@ -7748,7 +7748,7 @@
         <v>1.96</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R29" t="n">
         <v>1.36</v>
@@ -7757,16 +7757,16 @@
         <v>3.5</v>
       </c>
       <c r="T29" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V29" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="W29" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
         <v>18.5</v>
@@ -7802,7 +7802,7 @@
         <v>22</v>
       </c>
       <c r="AI29" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ29" t="n">
         <v>900</v>
@@ -7829,7 +7829,7 @@
         <v>7.4</v>
       </c>
       <c r="AR29" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS29" t="n">
         <v>17</v>
@@ -7859,7 +7859,7 @@
         <v>6.4</v>
       </c>
       <c r="BB29" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC29" t="n">
         <v>6.2</v>
@@ -7868,7 +7868,7 @@
         <v>6.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF29" t="n">
         <v>6.6</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -7969,19 +7969,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="G30" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="H30" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I30" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J30" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K30" t="n">
         <v>4.1</v>
@@ -8017,16 +8017,16 @@
         <v>2.54</v>
       </c>
       <c r="V30" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W30" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="X30" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y30" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Z30" t="n">
         <v>30</v>
@@ -8035,7 +8035,7 @@
         <v>120</v>
       </c>
       <c r="AB30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC30" t="n">
         <v>10.5</v>
@@ -8062,7 +8062,7 @@
         <v>38</v>
       </c>
       <c r="AK30" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL30" t="n">
         <v>36</v>
@@ -8071,22 +8071,22 @@
         <v>75</v>
       </c>
       <c r="AN30" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP30" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR30" t="n">
         <v>11.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT30" t="n">
         <v>10</v>
@@ -8113,7 +8113,7 @@
         <v>25</v>
       </c>
       <c r="BB30" t="n">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="BC30" t="n">
         <v>19</v>
@@ -8122,13 +8122,13 @@
         <v>21</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF30" t="n">
         <v>9.4</v>
       </c>
       <c r="BG30" t="n">
-        <v>15.5</v>
+        <v>4.9</v>
       </c>
       <c r="BH30" t="n">
         <v>4.2</v>
@@ -8140,16 +8140,16 @@
         <v>10.5</v>
       </c>
       <c r="BK30" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BN30" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO30" t="n">
         <v>4.2</v>
@@ -8158,13 +8158,13 @@
         <v>18.5</v>
       </c>
       <c r="BQ30" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR30" t="n">
         <v>29</v>
       </c>
       <c r="BS30" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BT30" t="n">
         <v>6.8</v>
@@ -8182,17 +8182,17 @@
         <v>36</v>
       </c>
       <c r="BY30" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ30" t="n">
         <v>21</v>
       </c>
       <c r="CA30" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -8226,22 +8226,22 @@
         <v>1.62</v>
       </c>
       <c r="G31" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="H31" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="I31" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="J31" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K31" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L31" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M31" t="n">
         <v>1.09</v>
@@ -8253,7 +8253,7 @@
         <v>1.39</v>
       </c>
       <c r="P31" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q31" t="n">
         <v>2.16</v>
@@ -8262,25 +8262,25 @@
         <v>1.26</v>
       </c>
       <c r="S31" t="n">
-        <v>1.05</v>
+        <v>3.75</v>
       </c>
       <c r="T31" t="n">
         <v>2.08</v>
       </c>
       <c r="U31" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V31" t="n">
         <v>1.14</v>
       </c>
       <c r="W31" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X31" t="n">
         <v>90</v>
       </c>
       <c r="Y31" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z31" t="n">
         <v>500</v>
@@ -8301,7 +8301,7 @@
         <v>700</v>
       </c>
       <c r="AF31" t="n">
-        <v>18.5</v>
+        <v>40</v>
       </c>
       <c r="AG31" t="n">
         <v>36</v>
@@ -8334,13 +8334,13 @@
         <v>6.2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="AT31" t="n">
         <v>4.2</v>
@@ -8349,10 +8349,10 @@
         <v>5.1</v>
       </c>
       <c r="AV31" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="AW31" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="AX31" t="n">
         <v>4.4</v>
@@ -8361,31 +8361,31 @@
         <v>6.2</v>
       </c>
       <c r="AZ31" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BA31" t="n">
-        <v>3.15</v>
+        <v>2.56</v>
       </c>
       <c r="BB31" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC31" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD31" t="n">
         <v>3.05</v>
       </c>
       <c r="BE31" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="BF31" t="n">
         <v>3.25</v>
       </c>
       <c r="BG31" t="n">
-        <v>2.72</v>
+        <v>2.34</v>
       </c>
       <c r="BH31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BI31" t="n">
         <v>2.6</v>
@@ -8394,59 +8394,59 @@
         <v>1000</v>
       </c>
       <c r="BK31" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA31" t="n">
         <v>1.35</v>
       </c>
-      <c r="BN31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO31" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BP31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ31" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BR31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BT31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BV31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BX31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BZ31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA31" t="n">
-        <v>1.31</v>
-      </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
         <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O32" t="n">
         <v>1.44</v>
@@ -8516,7 +8516,7 @@
         <v>1.23</v>
       </c>
       <c r="S32" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="T32" t="n">
         <v>1.91</v>
@@ -8600,7 +8600,7 @@
         <v>5.1</v>
       </c>
       <c r="AU32" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV32" t="n">
         <v>5.9</v>
@@ -8642,7 +8642,7 @@
         <v>3</v>
       </c>
       <c r="BI32" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="BJ32" t="n">
         <v>11</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
         <v>3.9</v>
       </c>
       <c r="I34" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="J34" t="n">
         <v>3.85</v>
@@ -9021,10 +9021,10 @@
         <v>1.78</v>
       </c>
       <c r="R34" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S34" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T34" t="n">
         <v>1.68</v>
@@ -9033,7 +9033,7 @@
         <v>2.4</v>
       </c>
       <c r="V34" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W34" t="n">
         <v>1.94</v>
@@ -9048,22 +9048,22 @@
         <v>30</v>
       </c>
       <c r="AA34" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AB34" t="n">
         <v>11.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD34" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>42</v>
+        <v>190</v>
       </c>
       <c r="AF34" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AG34" t="n">
         <v>10.5</v>
@@ -9072,13 +9072,13 @@
         <v>16</v>
       </c>
       <c r="AI34" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ34" t="n">
         <v>25</v>
       </c>
       <c r="AK34" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL34" t="n">
         <v>32</v>
@@ -9090,7 +9090,7 @@
         <v>12</v>
       </c>
       <c r="AO34" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP34" t="n">
         <v>16.5</v>
@@ -9108,7 +9108,7 @@
         <v>10.5</v>
       </c>
       <c r="AU34" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV34" t="n">
         <v>14.5</v>
@@ -9132,13 +9132,13 @@
         <v>22</v>
       </c>
       <c r="BC34" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD34" t="n">
         <v>27</v>
       </c>
       <c r="BE34" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="BF34" t="n">
         <v>10.5</v>
@@ -9147,13 +9147,13 @@
         <v>30</v>
       </c>
       <c r="BH34" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI34" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ34" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK34" t="n">
         <v>4.9</v>
@@ -9162,7 +9162,7 @@
         <v>120</v>
       </c>
       <c r="BM34" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN34" t="n">
         <v>5</v>
@@ -9174,41 +9174,41 @@
         <v>13.5</v>
       </c>
       <c r="BQ34" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR34" t="n">
         <v>32</v>
       </c>
       <c r="BS34" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT34" t="n">
         <v>7.4</v>
       </c>
       <c r="BU34" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV34" t="n">
         <v>36</v>
       </c>
       <c r="BW34" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX34" t="n">
         <v>46</v>
       </c>
       <c r="BY34" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BZ34" t="n">
         <v>24</v>
       </c>
       <c r="CA34" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -9756,46 +9756,46 @@
         <v>1.87</v>
       </c>
       <c r="I37" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="J37" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K37" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L37" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M37" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N37" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="O37" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="P37" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="R37" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="T37" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="U37" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="V37" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="W37" t="n">
         <v>1.23</v>
@@ -9816,7 +9816,7 @@
         <v>13</v>
       </c>
       <c r="AC37" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD37" t="n">
         <v>13</v>
@@ -9855,7 +9855,7 @@
         <v>25</v>
       </c>
       <c r="AP37" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ37" t="n">
         <v>5.8</v>
@@ -9867,7 +9867,7 @@
         <v>19</v>
       </c>
       <c r="AT37" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU37" t="n">
         <v>7.6</v>
@@ -9891,58 +9891,58 @@
         <v>5.4</v>
       </c>
       <c r="BB37" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC37" t="n">
         <v>5.5</v>
       </c>
-      <c r="BC37" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BD37" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF37" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG37" t="n">
         <v>17.5</v>
       </c>
       <c r="BH37" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BI37" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="BJ37" t="n">
         <v>14</v>
       </c>
       <c r="BK37" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL37" t="n">
         <v>1000</v>
       </c>
       <c r="BM37" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BN37" t="n">
         <v>10.5</v>
       </c>
       <c r="BO37" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP37" t="n">
         <v>1000</v>
       </c>
       <c r="BQ37" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR37" t="n">
         <v>1000</v>
       </c>
       <c r="BS37" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT37" t="n">
         <v>4.3</v>
@@ -9954,23 +9954,23 @@
         <v>18</v>
       </c>
       <c r="BW37" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BX37" t="n">
         <v>46</v>
       </c>
       <c r="BY37" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BZ37" t="n">
         <v>46</v>
       </c>
       <c r="CA37" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -10001,64 +10001,64 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="G38" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="H38" t="n">
         <v>5.4</v>
       </c>
       <c r="I38" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="J38" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K38" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L38" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M38" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="O38" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="P38" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="R38" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T38" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="U38" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="V38" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W38" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X38" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y38" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Z38" t="n">
         <v>55</v>
@@ -10067,10 +10067,10 @@
         <v>210</v>
       </c>
       <c r="AB38" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC38" t="n">
         <v>8.6</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>10.5</v>
       </c>
       <c r="AD38" t="n">
         <v>28</v>
@@ -10103,7 +10103,7 @@
         <v>200</v>
       </c>
       <c r="AN38" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO38" t="n">
         <v>170</v>
@@ -10115,116 +10115,116 @@
         <v>12</v>
       </c>
       <c r="AR38" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AS38" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AT38" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AU38" t="n">
         <v>6.2</v>
       </c>
       <c r="AV38" t="n">
-        <v>16.5</v>
+        <v>5</v>
       </c>
       <c r="AW38" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AX38" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY38" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AZ38" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BA38" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BB38" t="n">
         <v>13.5</v>
       </c>
       <c r="BC38" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BE38" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BF38" t="n">
         <v>10.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BH38" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI38" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="BJ38" t="n">
         <v>11.5</v>
       </c>
       <c r="BK38" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BL38" t="n">
         <v>1000</v>
       </c>
       <c r="BM38" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BN38" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO38" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BP38" t="n">
         <v>13</v>
       </c>
       <c r="BQ38" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BR38" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BS38" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BT38" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BU38" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BV38" t="n">
         <v>60</v>
       </c>
       <c r="BW38" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BZ38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA38" t="n">
         <v>10</v>
       </c>
-      <c r="BX38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY38" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BZ38" t="n">
-        <v>29</v>
-      </c>
-      <c r="CA38" t="n">
-        <v>8.6</v>
-      </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -10255,13 +10255,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G39" t="n">
         <v>2.76</v>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I39" t="n">
         <v>3.25</v>
@@ -10270,7 +10270,7 @@
         <v>3.2</v>
       </c>
       <c r="K39" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L39" t="n">
         <v>1.57</v>
@@ -10285,25 +10285,25 @@
         <v>1.55</v>
       </c>
       <c r="P39" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="R39" t="n">
         <v>1.18</v>
       </c>
       <c r="S39" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T39" t="n">
         <v>2.14</v>
       </c>
       <c r="U39" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="V39" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W39" t="n">
         <v>1.57</v>
@@ -10357,7 +10357,7 @@
         <v>210</v>
       </c>
       <c r="AN39" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO39" t="n">
         <v>65</v>
@@ -10366,7 +10366,7 @@
         <v>7</v>
       </c>
       <c r="AQ39" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AR39" t="n">
         <v>16.5</v>
@@ -10396,7 +10396,7 @@
         <v>19.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB39" t="n">
         <v>38</v>
@@ -10405,7 +10405,7 @@
         <v>7.8</v>
       </c>
       <c r="BD39" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE39" t="n">
         <v>9.199999999999999</v>
@@ -10426,13 +10426,13 @@
         <v>11.5</v>
       </c>
       <c r="BK39" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN39" t="n">
         <v>5.7</v>
@@ -10444,13 +10444,13 @@
         <v>26</v>
       </c>
       <c r="BQ39" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR39" t="n">
         <v>1000</v>
       </c>
       <c r="BS39" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT39" t="n">
         <v>6.2</v>
@@ -10459,7 +10459,7 @@
         <v>5.2</v>
       </c>
       <c r="BV39" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW39" t="n">
         <v>8.6</v>
@@ -10468,17 +10468,17 @@
         <v>55</v>
       </c>
       <c r="BY39" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ39" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA39" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="G40" t="n">
         <v>1.66</v>
@@ -10518,13 +10518,13 @@
         <v>6.2</v>
       </c>
       <c r="I40" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="J40" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K40" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
@@ -10557,7 +10557,7 @@
         <v>1.01</v>
       </c>
       <c r="V40" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W40" t="n">
         <v>2.5</v>
@@ -10617,52 +10617,52 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF40" t="n">
         <v>1.01</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -10871,52 +10871,52 @@
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF41" t="n">
         <v>1.01</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>
@@ -11017,166 +11017,166 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="G42" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="H42" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I42" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="J42" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K42" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
       </c>
       <c r="M42" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N42" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O42" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P42" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q42" t="n">
         <v>1.79</v>
       </c>
       <c r="R42" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S42" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="T42" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="U42" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V42" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W42" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="X42" t="n">
         <v>22</v>
       </c>
       <c r="Y42" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Z42" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA42" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB42" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AC42" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF42" t="n">
         <v>12.5</v>
       </c>
-      <c r="AD42" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF42" t="n">
+      <c r="AG42" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ42" t="n">
         <v>15.5</v>
       </c>
-      <c r="AG42" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU42" t="n">
+      <c r="BA42" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD42" t="n">
         <v>7</v>
       </c>
-      <c r="AV42" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BE42" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF42" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH42" t="n">
         <v>1000</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-20 21:39:56</t>
+          <t>2026-05-20 23:55:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>CONMEBOL Copa Libertadores</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,244 +843,244 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>Univ Catolica (Chile)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bogota</t>
+          <t>Barcelona (ECU)</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O2" t="n">
         <v>1.42</v>
       </c>
-      <c r="G2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="H2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2</v>
-      </c>
       <c r="P2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.27</v>
       </c>
-      <c r="Q2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.07</v>
-      </c>
       <c r="S2" t="n">
-        <v>13.5</v>
+        <v>4.4</v>
       </c>
       <c r="T2" t="n">
-        <v>5.2</v>
+        <v>2.08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="V2" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="W2" t="n">
-        <v>3.2</v>
+        <v>2.22</v>
       </c>
       <c r="X2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Y2" t="n">
-        <v>27</v>
+        <v>15.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>250</v>
+        <v>46</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.45</v>
+        <v>6.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>16.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>160</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AF2" t="n">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="AG2" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="AH2" t="n">
-        <v>260</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AJ2" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AK2" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="AL2" t="n">
-        <v>600</v>
+        <v>46</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN2" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="AQ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>140</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>90</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC2" t="n">
         <v>20</v>
       </c>
-      <c r="AR2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>36</v>
-      </c>
       <c r="BD2" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BE2" t="n">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="BF2" t="n">
         <v>13.5</v>
       </c>
       <c r="BG2" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>11.5</v>
       </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-21 19:15:14</t>
+          <t>2026-05-21 21:43:59</t>
         </is>
       </c>
     </row>
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Deportivo La Guaira</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5.2</v>
+        <v>2.52</v>
       </c>
       <c r="G3" t="n">
-        <v>5.3</v>
+        <v>2.54</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="I3" t="n">
-        <v>1.92</v>
+        <v>3.75</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>2.94</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="L3" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="M3" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="P3" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="S3" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="U3" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="V3" t="n">
-        <v>2.08</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>1.23</v>
+        <v>1.64</v>
       </c>
       <c r="X3" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.4</v>
+        <v>24</v>
       </c>
       <c r="AA3" t="n">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="AB3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG3" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD3" t="n">
+      <c r="AH3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>80</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>36</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>150</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>44</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>80</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>240</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>11</v>
       </c>
-      <c r="AE3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>200</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>26</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>120</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>90</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>100</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>140</v>
-      </c>
-      <c r="BF3" t="n">
+      <c r="BR3" t="n">
+        <v>46</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BV3" t="n">
         <v>38</v>
       </c>
-      <c r="BG3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>170</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>65</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>85</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BV3" t="n">
+      <c r="BW3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY3" t="n">
         <v>15</v>
       </c>
-      <c r="BW3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>42</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>21</v>
-      </c>
       <c r="BZ3" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="CA3" t="n">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-21 19:15:14</t>
+          <t>2026-05-21 21:43:59</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1356,246 +1356,246 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Univ Catolica (Chile)</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Barcelona (ECU)</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.81</v>
+        <v>1.27</v>
       </c>
       <c r="G4" t="n">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="H4" t="n">
-        <v>5.4</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
-        <v>5.6</v>
+        <v>17.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="P4" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="S4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>170</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>990</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>360</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>270</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>290</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>34</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>90</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>130</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BH4" t="n">
         <v>4.4</v>
       </c>
-      <c r="T4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X4" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>2.98</v>
-      </c>
       <c r="BI4" t="n">
-        <v>2.56</v>
+        <v>3.9</v>
       </c>
       <c r="BJ4" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>16.5</v>
+        <v>150</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="BP4" t="n">
-        <v>13.5</v>
+        <v>6.4</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="BR4" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BS4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
         <v>11.5</v>
       </c>
-      <c r="BT4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>60</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BX4" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="CA4" t="n">
-        <v>11.5</v>
+        <v>5.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-21 19:15:14</t>
+          <t>2026-05-21 21:43:59</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CONMEBOL Copa Libertadores</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>23:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>CD Marathon</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>CD Motagua</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="H5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="K5" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="M5" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="O5" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.96</v>
+        <v>2.24</v>
       </c>
       <c r="R5" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="S5" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="U5" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X5" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AA5" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AB5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC5" t="n">
         <v>7</v>
       </c>
-      <c r="AC5" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AD5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF5" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>14.5</v>
       </c>
       <c r="AG5" t="n">
         <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AI5" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AJ5" t="n">
         <v>42</v>
       </c>
       <c r="AK5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL5" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM5" t="n">
-        <v>220</v>
+        <v>880</v>
       </c>
       <c r="AN5" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AO5" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AP5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT5" t="n">
         <v>7.2</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD5" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AR5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>24</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>36</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>60</v>
-      </c>
       <c r="BE5" t="n">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="BF5" t="n">
-        <v>42</v>
+        <v>7.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>75</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>13</v>
+        <v>130</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BQ5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BR5" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BT5" t="n">
         <v>6.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="BV5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BW5" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="BZ5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-21 19:15:14</t>
+          <t>2026-05-21 21:43:59</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Mexican Liga MX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,752 +1859,244 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>23:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Pumas UNAM</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="G6" t="n">
-        <v>1.33</v>
+        <v>1.84</v>
       </c>
       <c r="H6" t="n">
-        <v>13.5</v>
+        <v>4.8</v>
       </c>
       <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X6" t="n">
         <v>16.5</v>
       </c>
-      <c r="J6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>21</v>
-      </c>
       <c r="Y6" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="Z6" t="n">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA6" t="n">
         <v>60</v>
       </c>
-      <c r="AE6" t="n">
-        <v>360</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>270</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL6" t="n">
+      <c r="BB6" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>85</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG6" t="n">
         <v>55</v>
       </c>
-      <c r="AM6" t="n">
-        <v>290</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>610</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>26</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BH6" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="BI6" t="n">
         <v>3.2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>13.5</v>
+        <v>110</v>
       </c>
       <c r="BN6" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="BP6" t="n">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BR6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>16.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU6" t="n">
-        <v>7.8</v>
+        <v>5.2</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW6" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY6" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-21 19:15:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Honduras Liga Nacional</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>23:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CD Marathon</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CD Motagua</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="X7" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-05-21 19:15:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Mexican Liga MX</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>23:00:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Cruz Azul</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Pumas UNAM</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X8" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>16</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>55</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>46</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>55</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>23</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>8</v>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>2026-05-21 19:15:14</t>
+          <t>2026-05-21 21:43:59</t>
         </is>
       </c>
     </row>
